--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -43,43 +43,43 @@
     <x:t>cuongnhhe186494</x:t>
   </x:si>
   <x:si>
+    <x:t>Success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 11:52:31</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 11:54:24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dongnvhe172649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 11:52:34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 11:53:29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hoangbsthe186345</x:t>
+  </x:si>
+  <x:si>
     <x:t>Failed</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>03-12-2025 23:22:16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03-12-2025 23:23:26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dongnvhe172649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03-12-2025 23:22:17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03-12-2025 23:23:17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hoangbsthe186345</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03-12-2025 23:25:48</x:t>
+    <x:t>04-12-2025 11:56:02</x:t>
   </x:si>
   <x:si>
     <x:t>Not Run</x:t>
@@ -144,12 +144,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FF90EE90"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -546,76 +546,76 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F2" s="2" t="s">
+      <x:c r="G2" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G2" s="2" t="s">
+    </x:row>
+    <x:row r="3" spans="1:7">
+      <x:c r="A3" s="2" t="s">
         <x:v>12</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="3" t="s">
+      <x:c r="B3" s="2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="s">
+      <x:c r="C3" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="s">
+      <x:c r="F3" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G3" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B4" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
+      <x:c r="D4" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E4" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F4" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G3" s="3" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C4" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G4" s="2" t="s">
+      <x:c r="G4" s="3" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>23</x:v>
@@ -629,16 +629,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>23</x:v>
@@ -652,16 +652,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>23</x:v>
@@ -678,13 +678,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>23</x:v>
@@ -701,13 +701,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>23</x:v>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -46,49 +46,49 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>04-12-2025 11:52:31</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04-12-2025 11:54:24</x:t>
-  </x:si>
-  <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
+    <x:t>04-12-2025 12:43:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 12:45:05</x:t>
+  </x:si>
+  <x:si>
     <x:t>dongnvhe172649</x:t>
   </x:si>
   <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 12:43:21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 12:45:01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hoangbsthe186345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 12:43:22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 12:45:07</x:t>
+  </x:si>
+  <x:si>
     <x:t>4</x:t>
   </x:si>
   <x:si>
-    <x:t>04-12-2025 11:52:34</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04-12-2025 11:53:29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hoangbsthe186345</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Failed</x:t>
+    <x:t>Not Run</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>04-12-2025 11:56:02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
     <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
   </x:si>
   <x:si>
     <x:t>6</x:t>
@@ -130,7 +130,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -145,11 +145,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -172,7 +167,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -182,11 +177,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -196,10 +188,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -546,18 +534,18 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
         <x:v>13</x:v>
@@ -579,72 +567,72 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
-      <x:c r="A4" s="3" t="s">
+      <x:c r="A4" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="s">
+      <x:c r="B4" s="2" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="s">
+      <x:c r="C4" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="s">
+      <x:c r="D4" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E4" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F4" s="2" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="s">
+      <x:c r="G4" s="2" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="F4" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G4" s="3" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
@@ -655,19 +643,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
@@ -678,19 +666,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
@@ -701,19 +689,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -43,52 +43,49 @@
     <x:t>cuongnhhe186494</x:t>
   </x:si>
   <x:si>
-    <x:t>Success</x:t>
+    <x:t>Failed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 13:48:17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 13:49:00</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
   </x:si>
   <x:si>
-    <x:t>04-12-2025 12:43:20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04-12-2025 12:45:05</x:t>
-  </x:si>
-  <x:si>
     <x:t>dongnvhe172649</x:t>
   </x:si>
   <x:si>
+    <x:t>04-12-2025 13:48:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hoangbsthe186345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>InProgress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 13:48:25</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Not Run</x:t>
+  </x:si>
+  <x:si>
     <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04-12-2025 12:43:21</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04-12-2025 12:45:01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hoangbsthe186345</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04-12-2025 12:43:22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04-12-2025 12:45:07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
   </x:si>
   <x:si>
     <x:t>6</x:t>
@@ -130,7 +127,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -144,7 +141,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
+        <x:fgColor rgb="FFFFB6C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFE0"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -167,7 +169,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -177,8 +179,11 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -188,6 +193,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -492,7 +501,7 @@
     <x:col min="1" max="1" width="3.424911" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="18.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="10.853482" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.282054" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.424911" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="10.567768" style="0" customWidth="1"/>
     <x:col min="6" max="7" width="18.567768" style="0" customWidth="1"/>
   </x:cols>
@@ -545,10 +554,10 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
         <x:v>7</x:v>
@@ -557,35 +566,35 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="2" t="s">
+      <x:c r="B4" s="3" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B4" s="2" t="s">
+      <x:c r="C4" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D4" s="3" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C4" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F4" s="2" t="s">
+      <x:c r="E4" s="3" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F4" s="3" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G4" s="2" t="s">
+      <x:c r="G4" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -597,111 +606,111 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="C6" s="0" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>04-12-2025 13:48:17</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04-12-2025 13:49:00</x:t>
+    <x:t>04-12-2025 15:09:17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 15:10:27</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -61,7 +61,10 @@
     <x:t>dongnvhe172649</x:t>
   </x:si>
   <x:si>
-    <x:t>04-12-2025 13:48:20</x:t>
+    <x:t>04-12-2025 15:09:23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 15:10:28</x:t>
   </x:si>
   <x:si>
     <x:t>3</x:t>
@@ -70,19 +73,19 @@
     <x:t>hoangbsthe186345</x:t>
   </x:si>
   <x:si>
-    <x:t>InProgress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04-12-2025 13:48:25</x:t>
+    <x:t>04-12-2025 15:09:41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04-12-2025 15:10:37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Not Run</x:t>
   </x:si>
   <x:si>
     <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Not Run</x:t>
   </x:si>
   <x:si>
     <x:t>5</x:t>
@@ -127,7 +130,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -142,11 +145,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFFE0"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -169,7 +167,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -179,11 +177,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -193,10 +188,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -501,7 +492,7 @@
     <x:col min="1" max="1" width="3.424911" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="18.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="10.853482" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="10.424911" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.282054" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="10.567768" style="0" customWidth="1"/>
     <x:col min="6" max="7" width="18.567768" style="0" customWidth="1"/>
   </x:cols>
@@ -572,29 +563,29 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
-      <x:c r="A4" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
+      <x:c r="A4" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="s">
+      <x:c r="B4" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="E4" s="3" t="s">
+      <x:c r="D4" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E4" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="s">
+      <x:c r="F4" s="2" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="G4" s="3" t="s">
+      <x:c r="G4" s="2" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
@@ -615,15 +606,15 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>14</x:v>
@@ -638,18 +629,18 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>13</x:v>
@@ -661,18 +652,18 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>13</x:v>
@@ -684,18 +675,18 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>13</x:v>
@@ -707,10 +698,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -85,10 +85,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 02:26:38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08-12-2025 02:28:18</x:t>
+    <x:t>08-12-2025 02:55:36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 02:57:09</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -85,10 +85,13 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 02:55:36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08-12-2025 02:57:09</x:t>
+    <x:t>1.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 09:02:29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 09:04:04</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>
@@ -1954,21 +1957,21 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E7" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F7" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>7</x:v>
@@ -1988,10 +1991,10 @@
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>7</x:v>
@@ -2011,10 +2014,10 @@
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>7</x:v>
@@ -2034,10 +2037,10 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>7</x:v>
@@ -2057,10 +2060,10 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
@@ -2080,10 +2083,10 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
@@ -2103,10 +2106,10 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
@@ -2126,10 +2129,10 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
@@ -2149,10 +2152,10 @@
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
@@ -2172,10 +2175,10 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
@@ -2195,10 +2198,10 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
@@ -2218,10 +2221,10 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
@@ -2241,10 +2244,10 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>7</x:v>
@@ -2264,10 +2267,10 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>7</x:v>
@@ -2287,10 +2290,10 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>7</x:v>
@@ -2310,10 +2313,10 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>7</x:v>
@@ -2333,10 +2336,10 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>7</x:v>
@@ -2356,10 +2359,10 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>7</x:v>
@@ -2379,10 +2382,10 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>7</x:v>
@@ -2402,10 +2405,10 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>12</x:v>
@@ -2425,10 +2428,10 @@
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>12</x:v>
@@ -2448,10 +2451,10 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>12</x:v>
@@ -2471,10 +2474,10 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>12</x:v>
@@ -2494,10 +2497,10 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>12</x:v>
@@ -2517,10 +2520,10 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>12</x:v>
@@ -2540,10 +2543,10 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>12</x:v>
@@ -2563,10 +2566,10 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>12</x:v>
@@ -2586,10 +2589,10 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>12</x:v>
@@ -2609,10 +2612,10 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>12</x:v>
@@ -2632,10 +2635,10 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>12</x:v>
@@ -2655,10 +2658,10 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>12</x:v>
@@ -2678,10 +2681,10 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>12</x:v>
@@ -2701,10 +2704,10 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>12</x:v>
@@ -2724,10 +2727,10 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>12</x:v>
@@ -2747,10 +2750,10 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>12</x:v>
@@ -2770,10 +2773,10 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>12</x:v>
@@ -2793,10 +2796,10 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>12</x:v>
@@ -2816,10 +2819,10 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>12</x:v>
@@ -2839,10 +2842,10 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>12</x:v>
@@ -2862,10 +2865,10 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>12</x:v>
@@ -2885,10 +2888,10 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>12</x:v>
@@ -2908,10 +2911,10 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>12</x:v>
@@ -2931,10 +2934,10 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>12</x:v>
@@ -2954,10 +2957,10 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>12</x:v>
@@ -2977,10 +2980,10 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>12</x:v>
@@ -3000,10 +3003,10 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>12</x:v>
@@ -3023,10 +3026,10 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>12</x:v>
@@ -3046,10 +3049,10 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>12</x:v>
@@ -3069,10 +3072,10 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>14</x:v>
@@ -3092,10 +3095,10 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>14</x:v>
@@ -3115,10 +3118,10 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>14</x:v>
@@ -3138,10 +3141,10 @@
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>14</x:v>
@@ -3161,10 +3164,10 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>14</x:v>
@@ -3184,10 +3187,10 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>14</x:v>
@@ -3207,10 +3210,10 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
         <x:v>14</x:v>
@@ -3230,10 +3233,10 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
         <x:v>14</x:v>
@@ -3253,10 +3256,10 @@
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
         <x:v>14</x:v>
@@ -3276,10 +3279,10 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>14</x:v>
@@ -3299,10 +3302,10 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>14</x:v>
@@ -3322,10 +3325,10 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>14</x:v>
@@ -3345,10 +3348,10 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>14</x:v>
@@ -3368,10 +3371,10 @@
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>14</x:v>
@@ -3391,10 +3394,10 @@
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
         <x:v>14</x:v>
@@ -3414,10 +3417,10 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
         <x:v>14</x:v>
@@ -3437,10 +3440,10 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
         <x:v>14</x:v>
@@ -3460,10 +3463,10 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>14</x:v>
@@ -3483,10 +3486,10 @@
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>14</x:v>
@@ -3506,10 +3509,10 @@
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>14</x:v>
@@ -3529,10 +3532,10 @@
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
         <x:v>14</x:v>
@@ -3552,10 +3555,10 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>14</x:v>
@@ -3575,10 +3578,10 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>14</x:v>
@@ -3598,10 +3601,10 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>14</x:v>
@@ -3621,10 +3624,10 @@
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
         <x:v>14</x:v>
@@ -3644,10 +3647,10 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
         <x:v>14</x:v>
@@ -3667,10 +3670,10 @@
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
         <x:v>14</x:v>
@@ -3690,10 +3693,10 @@
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
         <x:v>14</x:v>
@@ -3713,10 +3716,10 @@
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
         <x:v>14</x:v>
@@ -3736,10 +3739,10 @@
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>16</x:v>
@@ -3759,10 +3762,10 @@
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>16</x:v>
@@ -3782,10 +3785,10 @@
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>16</x:v>
@@ -3805,10 +3808,10 @@
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
         <x:v>16</x:v>
@@ -3828,10 +3831,10 @@
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
         <x:v>16</x:v>
@@ -3851,10 +3854,10 @@
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>16</x:v>
@@ -3874,10 +3877,10 @@
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>16</x:v>
@@ -3897,10 +3900,10 @@
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
         <x:v>16</x:v>
@@ -3920,10 +3923,10 @@
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>16</x:v>
@@ -3943,10 +3946,10 @@
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>16</x:v>
@@ -3966,10 +3969,10 @@
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>16</x:v>
@@ -3989,10 +3992,10 @@
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>16</x:v>
@@ -4012,10 +4015,10 @@
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>16</x:v>
@@ -4035,10 +4038,10 @@
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>16</x:v>
@@ -4058,10 +4061,10 @@
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>16</x:v>
@@ -4081,10 +4084,10 @@
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>16</x:v>
@@ -4104,10 +4107,10 @@
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>16</x:v>
@@ -4127,10 +4130,10 @@
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>16</x:v>
@@ -4150,10 +4153,10 @@
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>16</x:v>
@@ -4173,10 +4176,10 @@
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
         <x:v>16</x:v>
@@ -4196,10 +4199,10 @@
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>16</x:v>
@@ -4219,10 +4222,10 @@
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>16</x:v>
@@ -4242,10 +4245,10 @@
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>16</x:v>
@@ -4265,10 +4268,10 @@
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>16</x:v>
@@ -4288,10 +4291,10 @@
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>16</x:v>
@@ -4311,10 +4314,10 @@
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
         <x:v>16</x:v>
@@ -4334,10 +4337,10 @@
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>16</x:v>
@@ -4357,10 +4360,10 @@
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
         <x:v>16</x:v>
@@ -4380,10 +4383,10 @@
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>16</x:v>
@@ -4403,10 +4406,10 @@
     </x:row>
     <x:row r="114" spans="1:7">
       <x:c r="A114" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>16</x:v>
@@ -4426,10 +4429,10 @@
     </x:row>
     <x:row r="115" spans="1:7">
       <x:c r="A115" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
         <x:v>16</x:v>
@@ -4449,10 +4452,10 @@
     </x:row>
     <x:row r="116" spans="1:7">
       <x:c r="A116" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>18</x:v>
@@ -4472,10 +4475,10 @@
     </x:row>
     <x:row r="117" spans="1:7">
       <x:c r="A117" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>18</x:v>
@@ -4495,10 +4498,10 @@
     </x:row>
     <x:row r="118" spans="1:7">
       <x:c r="A118" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>18</x:v>
@@ -4518,10 +4521,10 @@
     </x:row>
     <x:row r="119" spans="1:7">
       <x:c r="A119" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>18</x:v>
@@ -4541,10 +4544,10 @@
     </x:row>
     <x:row r="120" spans="1:7">
       <x:c r="A120" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>18</x:v>
@@ -4564,10 +4567,10 @@
     </x:row>
     <x:row r="121" spans="1:7">
       <x:c r="A121" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
         <x:v>18</x:v>
@@ -4587,10 +4590,10 @@
     </x:row>
     <x:row r="122" spans="1:7">
       <x:c r="A122" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
         <x:v>18</x:v>
@@ -4610,10 +4613,10 @@
     </x:row>
     <x:row r="123" spans="1:7">
       <x:c r="A123" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
         <x:v>18</x:v>
@@ -4633,10 +4636,10 @@
     </x:row>
     <x:row r="124" spans="1:7">
       <x:c r="A124" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
         <x:v>18</x:v>
@@ -4656,10 +4659,10 @@
     </x:row>
     <x:row r="125" spans="1:7">
       <x:c r="A125" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
         <x:v>18</x:v>
@@ -4679,10 +4682,10 @@
     </x:row>
     <x:row r="126" spans="1:7">
       <x:c r="A126" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
         <x:v>18</x:v>
@@ -4702,10 +4705,10 @@
     </x:row>
     <x:row r="127" spans="1:7">
       <x:c r="A127" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>18</x:v>
@@ -4725,10 +4728,10 @@
     </x:row>
     <x:row r="128" spans="1:7">
       <x:c r="A128" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>18</x:v>
@@ -4748,10 +4751,10 @@
     </x:row>
     <x:row r="129" spans="1:7">
       <x:c r="A129" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>18</x:v>
@@ -4771,10 +4774,10 @@
     </x:row>
     <x:row r="130" spans="1:7">
       <x:c r="A130" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
         <x:v>18</x:v>
@@ -4794,10 +4797,10 @@
     </x:row>
     <x:row r="131" spans="1:7">
       <x:c r="A131" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
         <x:v>18</x:v>
@@ -4817,10 +4820,10 @@
     </x:row>
     <x:row r="132" spans="1:7">
       <x:c r="A132" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
         <x:v>18</x:v>
@@ -4840,10 +4843,10 @@
     </x:row>
     <x:row r="133" spans="1:7">
       <x:c r="A133" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
         <x:v>18</x:v>
@@ -4863,10 +4866,10 @@
     </x:row>
     <x:row r="134" spans="1:7">
       <x:c r="A134" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
         <x:v>18</x:v>
@@ -4886,10 +4889,10 @@
     </x:row>
     <x:row r="135" spans="1:7">
       <x:c r="A135" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
         <x:v>18</x:v>
@@ -4909,10 +4912,10 @@
     </x:row>
     <x:row r="136" spans="1:7">
       <x:c r="A136" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
         <x:v>18</x:v>
@@ -4932,10 +4935,10 @@
     </x:row>
     <x:row r="137" spans="1:7">
       <x:c r="A137" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
         <x:v>18</x:v>
@@ -4955,10 +4958,10 @@
     </x:row>
     <x:row r="138" spans="1:7">
       <x:c r="A138" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>18</x:v>
@@ -4978,10 +4981,10 @@
     </x:row>
     <x:row r="139" spans="1:7">
       <x:c r="A139" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
         <x:v>18</x:v>
@@ -5001,10 +5004,10 @@
     </x:row>
     <x:row r="140" spans="1:7">
       <x:c r="A140" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
         <x:v>18</x:v>
@@ -5024,10 +5027,10 @@
     </x:row>
     <x:row r="141" spans="1:7">
       <x:c r="A141" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
         <x:v>18</x:v>
@@ -5047,10 +5050,10 @@
     </x:row>
     <x:row r="142" spans="1:7">
       <x:c r="A142" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
         <x:v>20</x:v>
@@ -5070,10 +5073,10 @@
     </x:row>
     <x:row r="143" spans="1:7">
       <x:c r="A143" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
         <x:v>20</x:v>
@@ -5093,10 +5096,10 @@
     </x:row>
     <x:row r="144" spans="1:7">
       <x:c r="A144" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
         <x:v>20</x:v>
@@ -5116,10 +5119,10 @@
     </x:row>
     <x:row r="145" spans="1:7">
       <x:c r="A145" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
         <x:v>20</x:v>
@@ -5139,10 +5142,10 @@
     </x:row>
     <x:row r="146" spans="1:7">
       <x:c r="A146" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
         <x:v>20</x:v>
@@ -5162,10 +5165,10 @@
     </x:row>
     <x:row r="147" spans="1:7">
       <x:c r="A147" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
         <x:v>20</x:v>
@@ -5185,10 +5188,10 @@
     </x:row>
     <x:row r="148" spans="1:7">
       <x:c r="A148" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
         <x:v>20</x:v>
@@ -5208,10 +5211,10 @@
     </x:row>
     <x:row r="149" spans="1:7">
       <x:c r="A149" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
         <x:v>20</x:v>
@@ -5231,10 +5234,10 @@
     </x:row>
     <x:row r="150" spans="1:7">
       <x:c r="A150" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
         <x:v>20</x:v>
@@ -5254,10 +5257,10 @@
     </x:row>
     <x:row r="151" spans="1:7">
       <x:c r="A151" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
         <x:v>20</x:v>
@@ -5277,10 +5280,10 @@
     </x:row>
     <x:row r="152" spans="1:7">
       <x:c r="A152" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
         <x:v>20</x:v>
@@ -5300,10 +5303,10 @@
     </x:row>
     <x:row r="153" spans="1:7">
       <x:c r="A153" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
         <x:v>20</x:v>
@@ -5323,10 +5326,10 @@
     </x:row>
     <x:row r="154" spans="1:7">
       <x:c r="A154" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
         <x:v>20</x:v>
@@ -5346,10 +5349,10 @@
     </x:row>
     <x:row r="155" spans="1:7">
       <x:c r="A155" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
         <x:v>20</x:v>
@@ -5369,10 +5372,10 @@
     </x:row>
     <x:row r="156" spans="1:7">
       <x:c r="A156" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
         <x:v>20</x:v>
@@ -5392,10 +5395,10 @@
     </x:row>
     <x:row r="157" spans="1:7">
       <x:c r="A157" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
         <x:v>20</x:v>
@@ -5415,10 +5418,10 @@
     </x:row>
     <x:row r="158" spans="1:7">
       <x:c r="A158" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
         <x:v>20</x:v>
@@ -5438,10 +5441,10 @@
     </x:row>
     <x:row r="159" spans="1:7">
       <x:c r="A159" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
         <x:v>20</x:v>
@@ -5461,10 +5464,10 @@
     </x:row>
     <x:row r="160" spans="1:7">
       <x:c r="A160" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
         <x:v>20</x:v>
@@ -5484,10 +5487,10 @@
     </x:row>
     <x:row r="161" spans="1:7">
       <x:c r="A161" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C161" s="0" t="s">
         <x:v>20</x:v>
@@ -5507,10 +5510,10 @@
     </x:row>
     <x:row r="162" spans="1:7">
       <x:c r="A162" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
         <x:v>20</x:v>
@@ -5530,10 +5533,10 @@
     </x:row>
     <x:row r="163" spans="1:7">
       <x:c r="A163" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
         <x:v>20</x:v>
@@ -5553,10 +5556,10 @@
     </x:row>
     <x:row r="164" spans="1:7">
       <x:c r="A164" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
         <x:v>20</x:v>
@@ -5576,10 +5579,10 @@
     </x:row>
     <x:row r="165" spans="1:7">
       <x:c r="A165" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
         <x:v>20</x:v>
@@ -5599,10 +5602,10 @@
     </x:row>
     <x:row r="166" spans="1:7">
       <x:c r="A166" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C166" s="0" t="s">
         <x:v>20</x:v>
@@ -5622,10 +5625,10 @@
     </x:row>
     <x:row r="167" spans="1:7">
       <x:c r="A167" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C167" s="0" t="s">
         <x:v>20</x:v>
@@ -5645,13 +5648,13 @@
     </x:row>
     <x:row r="168" spans="1:7">
       <x:c r="A168" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="C168" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
         <x:v>9</x:v>
@@ -5668,13 +5671,13 @@
     </x:row>
     <x:row r="169" spans="1:7">
       <x:c r="A169" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C169" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
         <x:v>9</x:v>
@@ -5691,13 +5694,13 @@
     </x:row>
     <x:row r="170" spans="1:7">
       <x:c r="A170" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="C170" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
         <x:v>9</x:v>
@@ -5714,13 +5717,13 @@
     </x:row>
     <x:row r="171" spans="1:7">
       <x:c r="A171" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C171" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
         <x:v>9</x:v>
@@ -5737,13 +5740,13 @@
     </x:row>
     <x:row r="172" spans="1:7">
       <x:c r="A172" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="C172" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
         <x:v>9</x:v>
@@ -5760,13 +5763,13 @@
     </x:row>
     <x:row r="173" spans="1:7">
       <x:c r="A173" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="C173" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
         <x:v>9</x:v>
@@ -5783,13 +5786,13 @@
     </x:row>
     <x:row r="174" spans="1:7">
       <x:c r="A174" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="C174" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
         <x:v>9</x:v>
@@ -5806,13 +5809,13 @@
     </x:row>
     <x:row r="175" spans="1:7">
       <x:c r="A175" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="C175" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
         <x:v>9</x:v>
@@ -5829,13 +5832,13 @@
     </x:row>
     <x:row r="176" spans="1:7">
       <x:c r="A176" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C176" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
         <x:v>9</x:v>
@@ -5852,13 +5855,13 @@
     </x:row>
     <x:row r="177" spans="1:7">
       <x:c r="A177" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="C177" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
         <x:v>9</x:v>
@@ -5875,13 +5878,13 @@
     </x:row>
     <x:row r="178" spans="1:7">
       <x:c r="A178" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C178" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
         <x:v>9</x:v>
@@ -5898,13 +5901,13 @@
     </x:row>
     <x:row r="179" spans="1:7">
       <x:c r="A179" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="C179" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
         <x:v>9</x:v>
@@ -5921,13 +5924,13 @@
     </x:row>
     <x:row r="180" spans="1:7">
       <x:c r="A180" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="C180" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
         <x:v>9</x:v>
@@ -5944,13 +5947,13 @@
     </x:row>
     <x:row r="181" spans="1:7">
       <x:c r="A181" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="C181" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
         <x:v>9</x:v>
@@ -5967,13 +5970,13 @@
     </x:row>
     <x:row r="182" spans="1:7">
       <x:c r="A182" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C182" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
         <x:v>9</x:v>
@@ -5990,13 +5993,13 @@
     </x:row>
     <x:row r="183" spans="1:7">
       <x:c r="A183" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C183" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
         <x:v>9</x:v>
@@ -6013,13 +6016,13 @@
     </x:row>
     <x:row r="184" spans="1:7">
       <x:c r="A184" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C184" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
         <x:v>9</x:v>
@@ -6036,13 +6039,13 @@
     </x:row>
     <x:row r="185" spans="1:7">
       <x:c r="A185" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="C185" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
         <x:v>9</x:v>
@@ -6059,13 +6062,13 @@
     </x:row>
     <x:row r="186" spans="1:7">
       <x:c r="A186" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="C186" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
         <x:v>9</x:v>
@@ -6082,13 +6085,13 @@
     </x:row>
     <x:row r="187" spans="1:7">
       <x:c r="A187" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C187" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
         <x:v>9</x:v>
@@ -6105,13 +6108,13 @@
     </x:row>
     <x:row r="188" spans="1:7">
       <x:c r="A188" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="C188" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
         <x:v>9</x:v>
@@ -6128,13 +6131,13 @@
     </x:row>
     <x:row r="189" spans="1:7">
       <x:c r="A189" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="C189" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
         <x:v>9</x:v>
@@ -6151,13 +6154,13 @@
     </x:row>
     <x:row r="190" spans="1:7">
       <x:c r="A190" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="C190" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D190" s="0" t="s">
         <x:v>9</x:v>
@@ -6174,13 +6177,13 @@
     </x:row>
     <x:row r="191" spans="1:7">
       <x:c r="A191" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="C191" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D191" s="0" t="s">
         <x:v>9</x:v>
@@ -6197,13 +6200,13 @@
     </x:row>
     <x:row r="192" spans="1:7">
       <x:c r="A192" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="C192" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D192" s="0" t="s">
         <x:v>9</x:v>
@@ -6220,13 +6223,13 @@
     </x:row>
     <x:row r="193" spans="1:7">
       <x:c r="A193" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C193" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D193" s="0" t="s">
         <x:v>9</x:v>
@@ -6243,13 +6246,13 @@
     </x:row>
     <x:row r="194" spans="1:7">
       <x:c r="A194" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="C194" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D194" s="0" t="s">
         <x:v>9</x:v>
@@ -6266,13 +6269,13 @@
     </x:row>
     <x:row r="195" spans="1:7">
       <x:c r="A195" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="C195" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D195" s="0" t="s">
         <x:v>9</x:v>
@@ -6289,13 +6292,13 @@
     </x:row>
     <x:row r="196" spans="1:7">
       <x:c r="A196" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C196" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D196" s="0" t="s">
         <x:v>9</x:v>
@@ -6312,13 +6315,13 @@
     </x:row>
     <x:row r="197" spans="1:7">
       <x:c r="A197" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C197" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D197" s="0" t="s">
         <x:v>9</x:v>
@@ -6335,13 +6338,13 @@
     </x:row>
     <x:row r="198" spans="1:7">
       <x:c r="A198" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="C198" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D198" s="0" t="s">
         <x:v>9</x:v>
@@ -6358,13 +6361,13 @@
     </x:row>
     <x:row r="199" spans="1:7">
       <x:c r="A199" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="C199" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D199" s="0" t="s">
         <x:v>9</x:v>
@@ -6381,13 +6384,13 @@
     </x:row>
     <x:row r="200" spans="1:7">
       <x:c r="A200" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="C200" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D200" s="0" t="s">
         <x:v>9</x:v>
@@ -6404,13 +6407,13 @@
     </x:row>
     <x:row r="201" spans="1:7">
       <x:c r="A201" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="C201" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
         <x:v>9</x:v>
@@ -6427,13 +6430,13 @@
     </x:row>
     <x:row r="202" spans="1:7">
       <x:c r="A202" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="C202" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D202" s="0" t="s">
         <x:v>9</x:v>
@@ -6450,13 +6453,13 @@
     </x:row>
     <x:row r="203" spans="1:7">
       <x:c r="A203" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="C203" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
         <x:v>9</x:v>
@@ -6473,13 +6476,13 @@
     </x:row>
     <x:row r="204" spans="1:7">
       <x:c r="A204" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="C204" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D204" s="0" t="s">
         <x:v>9</x:v>
@@ -6496,13 +6499,13 @@
     </x:row>
     <x:row r="205" spans="1:7">
       <x:c r="A205" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="C205" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D205" s="0" t="s">
         <x:v>9</x:v>
@@ -6519,13 +6522,13 @@
     </x:row>
     <x:row r="206" spans="1:7">
       <x:c r="A206" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="C206" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D206" s="0" t="s">
         <x:v>9</x:v>
@@ -6542,13 +6545,13 @@
     </x:row>
     <x:row r="207" spans="1:7">
       <x:c r="A207" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="C207" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D207" s="0" t="s">
         <x:v>9</x:v>
@@ -6565,13 +6568,13 @@
     </x:row>
     <x:row r="208" spans="1:7">
       <x:c r="A208" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="C208" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D208" s="0" t="s">
         <x:v>9</x:v>
@@ -6588,13 +6591,13 @@
     </x:row>
     <x:row r="209" spans="1:7">
       <x:c r="A209" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="C209" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D209" s="0" t="s">
         <x:v>9</x:v>
@@ -6611,13 +6614,13 @@
     </x:row>
     <x:row r="210" spans="1:7">
       <x:c r="A210" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="C210" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D210" s="0" t="s">
         <x:v>9</x:v>
@@ -6634,13 +6637,13 @@
     </x:row>
     <x:row r="211" spans="1:7">
       <x:c r="A211" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C211" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D211" s="0" t="s">
         <x:v>9</x:v>
@@ -6657,13 +6660,13 @@
     </x:row>
     <x:row r="212" spans="1:7">
       <x:c r="A212" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="C212" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D212" s="0" t="s">
         <x:v>9</x:v>
@@ -6680,13 +6683,13 @@
     </x:row>
     <x:row r="213" spans="1:7">
       <x:c r="A213" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="C213" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D213" s="0" t="s">
         <x:v>9</x:v>
@@ -6703,13 +6706,13 @@
     </x:row>
     <x:row r="214" spans="1:7">
       <x:c r="A214" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="C214" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D214" s="0" t="s">
         <x:v>9</x:v>
@@ -6726,13 +6729,13 @@
     </x:row>
     <x:row r="215" spans="1:7">
       <x:c r="A215" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="C215" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D215" s="0" t="s">
         <x:v>9</x:v>
@@ -6749,13 +6752,13 @@
     </x:row>
     <x:row r="216" spans="1:7">
       <x:c r="A216" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C216" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
         <x:v>9</x:v>
@@ -6772,13 +6775,13 @@
     </x:row>
     <x:row r="217" spans="1:7">
       <x:c r="A217" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="C217" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
         <x:v>9</x:v>
@@ -6795,13 +6798,13 @@
     </x:row>
     <x:row r="218" spans="1:7">
       <x:c r="A218" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="C218" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
         <x:v>9</x:v>
@@ -6818,13 +6821,13 @@
     </x:row>
     <x:row r="219" spans="1:7">
       <x:c r="A219" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="C219" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
         <x:v>9</x:v>
@@ -6841,13 +6844,13 @@
     </x:row>
     <x:row r="220" spans="1:7">
       <x:c r="A220" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="C220" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D220" s="0" t="s">
         <x:v>9</x:v>
@@ -6864,13 +6867,13 @@
     </x:row>
     <x:row r="221" spans="1:7">
       <x:c r="A221" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="C221" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D221" s="0" t="s">
         <x:v>9</x:v>
@@ -6887,13 +6890,13 @@
     </x:row>
     <x:row r="222" spans="1:7">
       <x:c r="A222" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="C222" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D222" s="0" t="s">
         <x:v>9</x:v>
@@ -6910,13 +6913,13 @@
     </x:row>
     <x:row r="223" spans="1:7">
       <x:c r="A223" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C223" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D223" s="0" t="s">
         <x:v>9</x:v>
@@ -6933,13 +6936,13 @@
     </x:row>
     <x:row r="224" spans="1:7">
       <x:c r="A224" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C224" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D224" s="0" t="s">
         <x:v>9</x:v>
@@ -6956,13 +6959,13 @@
     </x:row>
     <x:row r="225" spans="1:7">
       <x:c r="A225" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="C225" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D225" s="0" t="s">
         <x:v>9</x:v>
@@ -6979,13 +6982,13 @@
     </x:row>
     <x:row r="226" spans="1:7">
       <x:c r="A226" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C226" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D226" s="0" t="s">
         <x:v>9</x:v>
@@ -7002,13 +7005,13 @@
     </x:row>
     <x:row r="227" spans="1:7">
       <x:c r="A227" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C227" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
         <x:v>9</x:v>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -88,10 +88,10 @@
     <x:t>1.5</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 09:02:29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08-12-2025 09:04:04</x:t>
+    <x:t>08-12-2025 09:32:55</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 09:34:28</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -88,10 +88,10 @@
     <x:t>1.5</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 09:32:55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08-12-2025 09:34:28</x:t>
+    <x:t>08-12-2025 10:22:29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 10:24:07</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -43,85 +43,103 @@
     <x:t>AnhDThe187386</x:t>
   </x:si>
   <x:si>
+    <x:t>Failed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 11:20:08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 11:23:12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>anlpvhe187047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 11:23:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cuongnvhe181200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 11:22:54</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ducnthe180869</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 11:21:08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungdvhe181404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 11:23:14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungtdhe186461</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 11:23:08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duongnthe186310</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DuyCNHE187327</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 11:23:13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duyldhe176352</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 11:23:16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>duynthe180374</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GiangPTHE171781</x:t>
+  </x:si>
+  <x:si>
     <x:t>Not Run</x:t>
   </x:si>
   <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
     <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>anlpvhe187047</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cuongnvhe181200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ducnthe180869</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dungdvhe181404</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dungtdhe186461</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08-12-2025 10:22:29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08-12-2025 10:24:07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duongnthe186310</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DuyCNHE187327</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duyldhe176352</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>duynthe180374</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GiangPTHE171781</x:t>
   </x:si>
   <x:si>
     <x:t>12</x:t>
@@ -1452,7 +1470,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -1829,5201 +1847,5201 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:7">
-      <x:c r="A2" s="0" t="s">
+      <x:c r="A2" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" s="2" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="C2" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="D2" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
+      <x:c r="E2" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
+      <x:c r="G2" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7">
+      <x:c r="A3" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="G3" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="D4" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
+      <x:c r="E4" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F4" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="G4" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:7">
+      <x:c r="A5" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E5" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F5" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="G5" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7">
+      <x:c r="A6" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B6" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C6" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="D6" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
+      <x:c r="E6" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F6" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:7">
-      <x:c r="A5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>11</x:v>
+      <x:c r="G6" s="2" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E7" s="2" t="s">
-        <x:v>23</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F7" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
-      <x:c r="A8" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
+      <x:c r="A8" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C8" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="D8" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
+      <x:c r="E8" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G8" s="0" t="s">
+      <x:c r="G8" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:7">
+      <x:c r="A9" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C9" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D9" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E9" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F9" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:7">
-      <x:c r="A9" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
+      <x:c r="G9" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:7">
+      <x:c r="A10" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
+      <x:c r="D10" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
+      <x:c r="E10" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F10" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G9" s="0" t="s">
+      <x:c r="G10" s="2" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:7">
+      <x:c r="A11" s="2" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F11" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10" spans="1:7">
-      <x:c r="A10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:7">
-      <x:c r="A11" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>11</x:v>
+      <x:c r="G11" s="2" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G56" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G57" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G58" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G59" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G60" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G61" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G62" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G63" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G64" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G65" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G66" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G67" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G68" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G69" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G70" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G71" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G72" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G73" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G74" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G75" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G76" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G77" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G78" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G79" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G80" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G81" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G82" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G83" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G84" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G85" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G86" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G87" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G88" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G89" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G90" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G91" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G92" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G93" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G94" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G95" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G96" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G97" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G98" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G99" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G100" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G101" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G102" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G103" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G104" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G105" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G106" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G107" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G108" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G109" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G110" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G111" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G112" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G113" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:7">
       <x:c r="A114" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G114" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:7">
       <x:c r="A115" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G115" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7">
       <x:c r="A116" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G116" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:7">
       <x:c r="A117" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G117" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:7">
       <x:c r="A118" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G118" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:7">
       <x:c r="A119" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G119" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:7">
       <x:c r="A120" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G120" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:7">
       <x:c r="A121" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G121" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:7">
       <x:c r="A122" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G122" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:7">
       <x:c r="A123" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G123" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:7">
       <x:c r="A124" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G124" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:7">
       <x:c r="A125" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G125" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:7">
       <x:c r="A126" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G126" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:7">
       <x:c r="A127" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G127" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:7">
       <x:c r="A128" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G128" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:7">
       <x:c r="A129" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G129" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7">
       <x:c r="A130" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G130" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
       <x:c r="A131" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G131" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:7">
       <x:c r="A132" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G132" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:7">
       <x:c r="A133" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G133" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:7">
       <x:c r="A134" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G134" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:7">
       <x:c r="A135" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G135" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:7">
       <x:c r="A136" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G136" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:7">
       <x:c r="A137" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G137" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:7">
       <x:c r="A138" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G138" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:7">
       <x:c r="A139" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G139" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:7">
       <x:c r="A140" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G140" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:7">
       <x:c r="A141" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G141" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:7">
       <x:c r="A142" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G142" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:7">
       <x:c r="A143" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G143" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:7">
       <x:c r="A144" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G144" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:7">
       <x:c r="A145" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G145" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:7">
       <x:c r="A146" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G146" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:7">
       <x:c r="A147" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G147" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:7">
       <x:c r="A148" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G148" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:7">
       <x:c r="A149" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G149" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:7">
       <x:c r="A150" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G150" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:7">
       <x:c r="A151" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G151" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:7">
       <x:c r="A152" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G152" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:7">
       <x:c r="A153" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G153" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:7">
       <x:c r="A154" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G154" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:7">
       <x:c r="A155" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G155" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:7">
       <x:c r="A156" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G156" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:7">
       <x:c r="A157" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G157" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:7">
       <x:c r="A158" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G158" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:7">
       <x:c r="A159" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G159" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:7">
       <x:c r="A160" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G160" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:7">
       <x:c r="A161" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="C161" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E161" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G161" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:7">
       <x:c r="A162" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E162" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G162" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:7">
       <x:c r="A163" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E163" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G163" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:7">
       <x:c r="A164" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E164" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G164" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:7">
       <x:c r="A165" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E165" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G165" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:7">
       <x:c r="A166" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C166" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E166" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G166" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:7">
       <x:c r="A167" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="C167" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E167" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G167" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:7">
       <x:c r="A168" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C168" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E168" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G168" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:7">
       <x:c r="A169" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="C169" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E169" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G169" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:7">
       <x:c r="A170" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="C170" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E170" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F170" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G170" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:7">
       <x:c r="A171" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="C171" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E171" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F171" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G171" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:7">
       <x:c r="A172" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="C172" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E172" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F172" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G172" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:7">
       <x:c r="A173" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C173" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E173" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F173" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G173" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:7">
       <x:c r="A174" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="C174" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E174" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F174" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G174" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:7">
       <x:c r="A175" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C175" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E175" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F175" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G175" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:7">
       <x:c r="A176" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="C176" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E176" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F176" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G176" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:7">
       <x:c r="A177" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="C177" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E177" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F177" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G177" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:7">
       <x:c r="A178" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="C178" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E178" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F178" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G178" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:7">
       <x:c r="A179" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C179" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E179" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F179" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G179" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:7">
       <x:c r="A180" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C180" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E180" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F180" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G180" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:7">
       <x:c r="A181" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C181" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E181" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F181" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G181" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:7">
       <x:c r="A182" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="C182" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E182" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F182" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G182" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:7">
       <x:c r="A183" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="C183" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E183" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F183" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G183" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:7">
       <x:c r="A184" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C184" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E184" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F184" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G184" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:7">
       <x:c r="A185" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="C185" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E185" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F185" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G185" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:7">
       <x:c r="A186" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="C186" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E186" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F186" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G186" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:7">
       <x:c r="A187" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="C187" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E187" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F187" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G187" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:7">
       <x:c r="A188" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="C188" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E188" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F188" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G188" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:7">
       <x:c r="A189" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="C189" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E189" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F189" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G189" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:7">
       <x:c r="A190" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C190" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D190" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E190" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F190" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G190" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:7">
       <x:c r="A191" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="C191" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D191" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E191" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F191" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G191" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:7">
       <x:c r="A192" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="C192" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D192" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E192" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F192" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G192" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:7">
       <x:c r="A193" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C193" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D193" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E193" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F193" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G193" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:7">
       <x:c r="A194" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C194" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D194" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E194" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F194" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G194" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:7">
       <x:c r="A195" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="C195" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D195" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E195" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F195" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G195" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:7">
       <x:c r="A196" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="C196" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D196" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E196" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F196" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G196" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:7">
       <x:c r="A197" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="C197" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D197" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E197" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F197" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G197" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:7">
       <x:c r="A198" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="C198" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D198" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E198" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F198" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G198" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:7">
       <x:c r="A199" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="C199" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D199" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E199" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F199" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G199" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:7">
       <x:c r="A200" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="C200" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D200" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E200" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F200" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G200" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:7">
       <x:c r="A201" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="C201" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E201" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F201" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G201" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:7">
       <x:c r="A202" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="C202" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D202" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E202" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F202" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G202" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:7">
       <x:c r="A203" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="C203" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E203" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F203" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G203" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:7">
       <x:c r="A204" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="C204" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D204" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E204" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F204" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G204" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:7">
       <x:c r="A205" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="C205" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D205" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E205" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F205" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G205" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="206" spans="1:7">
       <x:c r="A206" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="C206" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D206" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E206" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F206" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G206" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:7">
       <x:c r="A207" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="C207" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D207" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E207" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F207" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G207" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:7">
       <x:c r="A208" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C208" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D208" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E208" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F208" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G208" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:7">
       <x:c r="A209" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="C209" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D209" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E209" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F209" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G209" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:7">
       <x:c r="A210" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="C210" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D210" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E210" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F210" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G210" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="211" spans="1:7">
       <x:c r="A211" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="C211" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D211" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E211" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F211" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G211" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="212" spans="1:7">
       <x:c r="A212" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="C212" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D212" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E212" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F212" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G212" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="213" spans="1:7">
       <x:c r="A213" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C213" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D213" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E213" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F213" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G213" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:7">
       <x:c r="A214" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="C214" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D214" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E214" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F214" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G214" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:7">
       <x:c r="A215" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="C215" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D215" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E215" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F215" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G215" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:7">
       <x:c r="A216" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="C216" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E216" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F216" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G216" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="217" spans="1:7">
       <x:c r="A217" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="C217" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E217" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F217" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G217" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:7">
       <x:c r="A218" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="C218" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E218" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F218" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G218" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:7">
       <x:c r="A219" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="C219" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E219" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F219" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G219" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="220" spans="1:7">
       <x:c r="A220" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C220" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D220" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E220" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F220" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G220" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="221" spans="1:7">
       <x:c r="A221" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C221" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D221" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E221" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F221" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G221" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="222" spans="1:7">
       <x:c r="A222" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="C222" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D222" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E222" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F222" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G222" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:7">
       <x:c r="A223" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C223" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D223" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E223" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F223" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G223" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="224" spans="1:7">
       <x:c r="A224" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C224" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D224" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E224" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F224" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G224" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:7">
       <x:c r="A225" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="C225" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D225" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E225" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F225" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G225" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="226" spans="1:7">
       <x:c r="A226" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="C226" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D226" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E226" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F226" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G226" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:7">
       <x:c r="A227" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="C227" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E227" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F227" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G227" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 11:20:08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08-12-2025 11:23:12</x:t>
+    <x:t>08-12-2025 11:57:13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 12:00:18</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -61,7 +61,7 @@
     <x:t>anlpvhe187047</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 11:23:20</x:t>
+    <x:t>08-12-2025 12:00:12</x:t>
   </x:si>
   <x:si>
     <x:t>3</x:t>
@@ -70,7 +70,7 @@
     <x:t>cuongnvhe181200</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 11:22:54</x:t>
+    <x:t>08-12-2025 12:00:15</x:t>
   </x:si>
   <x:si>
     <x:t>4</x:t>
@@ -79,7 +79,7 @@
     <x:t>ducnthe180869</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 11:21:08</x:t>
+    <x:t>08-12-2025 11:57:59</x:t>
   </x:si>
   <x:si>
     <x:t>5</x:t>
@@ -88,7 +88,10 @@
     <x:t>dungdvhe181404</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 11:23:14</x:t>
+    <x:t>08-12-2025 11:57:12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 12:00:11</x:t>
   </x:si>
   <x:si>
     <x:t>6</x:t>
@@ -97,39 +100,36 @@
     <x:t>dungtdhe186461</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 11:23:08</x:t>
-  </x:si>
-  <x:si>
     <x:t>7</x:t>
   </x:si>
   <x:si>
     <x:t>duongnthe186310</x:t>
   </x:si>
   <x:si>
+    <x:t>08-12-2025 12:00:25</x:t>
+  </x:si>
+  <x:si>
     <x:t>8</x:t>
   </x:si>
   <x:si>
     <x:t>DuyCNHE187327</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 11:23:13</x:t>
-  </x:si>
-  <x:si>
     <x:t>9</x:t>
   </x:si>
   <x:si>
     <x:t>duyldhe176352</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 11:23:16</x:t>
-  </x:si>
-  <x:si>
     <x:t>10</x:t>
   </x:si>
   <x:si>
     <x:t>duynthe180374</x:t>
   </x:si>
   <x:si>
+    <x:t>08-12-2025 12:00:10</x:t>
+  </x:si>
+  <x:si>
     <x:t>11</x:t>
   </x:si>
   <x:si>
@@ -1430,6 +1430,12 @@
   </x:si>
   <x:si>
     <x:t>vietddhe161942</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-12-08 12:00:25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.16s</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1823,7 +1829,7 @@
     <x:col min="6" max="7" width="18.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:7" s="1" customFormat="1">
+    <x:row r="1" spans="1:9" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1846,7 +1852,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:7">
+    <x:row r="2" spans="1:9" s="2" customFormat="1">
       <x:c r="A2" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1863,13 +1869,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
         <x:v>12</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
+      <x:c r="H2" s="2" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>473</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9">
       <x:c r="A3" s="2" t="s">
         <x:v>13</x:v>
       </x:c>
@@ -1892,7 +1904,7 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:7">
+    <x:row r="4" spans="1:9">
       <x:c r="A4" s="2" t="s">
         <x:v>16</x:v>
       </x:c>
@@ -1915,7 +1927,7 @@
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:7">
+    <x:row r="5" spans="1:9">
       <x:c r="A5" s="2" t="s">
         <x:v>19</x:v>
       </x:c>
@@ -1938,7 +1950,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:7">
+    <x:row r="6" spans="1:9">
       <x:c r="A6" s="2" t="s">
         <x:v>22</x:v>
       </x:c>
@@ -1955,18 +1967,18 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G6" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:7">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9">
       <x:c r="A7" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
         <x:v>7</x:v>
@@ -1981,10 +1993,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G7" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:7">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
       <x:c r="A8" s="2" t="s">
         <x:v>28</x:v>
       </x:c>
@@ -2004,15 +2016,15 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:7">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9">
       <x:c r="A9" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
         <x:v>7</x:v>
@@ -2027,10 +2039,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G9" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:7">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9">
       <x:c r="A10" s="2" t="s">
         <x:v>33</x:v>
       </x:c>
@@ -2050,15 +2062,15 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G10" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:9">
+      <x:c r="A11" s="2" t="s">
         <x:v>35</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11" spans="1:7">
-      <x:c r="A11" s="2" t="s">
+      <x:c r="B11" s="2" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="B11" s="2" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
         <x:v>7</x:v>
@@ -2070,13 +2082,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F11" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G11" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:7">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
@@ -2099,7 +2111,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:7">
+    <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
@@ -2122,7 +2134,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:7">
+    <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
@@ -2145,7 +2157,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:7">
+    <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
@@ -2168,7 +2180,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:7">
+    <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
@@ -2191,7 +2203,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:7">
+    <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
         <x:v>50</x:v>
       </x:c>
@@ -2214,7 +2226,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:7">
+    <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
@@ -2237,7 +2249,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:7">
+    <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
@@ -2260,7 +2272,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:7">
+    <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
@@ -2283,7 +2295,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:7">
+    <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
@@ -2306,7 +2318,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:7">
+    <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
         <x:v>60</x:v>
       </x:c>
@@ -2329,7 +2341,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:7">
+    <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
         <x:v>62</x:v>
       </x:c>
@@ -2352,7 +2364,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:7">
+    <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
@@ -2375,7 +2387,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:7">
+    <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
         <x:v>66</x:v>
       </x:c>
@@ -2398,7 +2410,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:7">
+    <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
@@ -2421,7 +2433,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:7">
+    <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
         <x:v>70</x:v>
       </x:c>
@@ -2444,7 +2456,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:7">
+    <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
@@ -2467,7 +2479,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:7">
+    <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
         <x:v>74</x:v>
       </x:c>
@@ -2490,7 +2502,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:7">
+    <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
         <x:v>76</x:v>
       </x:c>
@@ -2513,7 +2525,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:7">
+    <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
         <x:v>78</x:v>
       </x:c>
@@ -2536,7 +2548,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:7">
+    <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
@@ -2559,7 +2571,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:7">
+    <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
         <x:v>82</x:v>
       </x:c>
@@ -2582,7 +2594,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:7">
+    <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
@@ -2605,7 +2617,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:7">
+    <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
         <x:v>86</x:v>
       </x:c>
@@ -2628,7 +2640,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:7">
+    <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
@@ -2651,7 +2663,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:7">
+    <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
         <x:v>90</x:v>
       </x:c>
@@ -2674,7 +2686,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:7">
+    <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
         <x:v>92</x:v>
       </x:c>
@@ -2697,7 +2709,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:7">
+    <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
         <x:v>94</x:v>
       </x:c>
@@ -2720,7 +2732,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" spans="1:7">
+    <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
         <x:v>96</x:v>
       </x:c>
@@ -2743,7 +2755,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:7">
+    <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
         <x:v>98</x:v>
       </x:c>
@@ -2766,7 +2778,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:7">
+    <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
         <x:v>100</x:v>
       </x:c>
@@ -2789,7 +2801,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:7">
+    <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
         <x:v>102</x:v>
       </x:c>
@@ -2812,7 +2824,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" spans="1:7">
+    <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
         <x:v>104</x:v>
       </x:c>
@@ -2835,7 +2847,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" spans="1:7">
+    <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
         <x:v>106</x:v>
       </x:c>
@@ -2858,7 +2870,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" spans="1:7">
+    <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
         <x:v>108</x:v>
       </x:c>
@@ -2881,7 +2893,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" spans="1:7">
+    <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
@@ -2904,7 +2916,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" spans="1:7">
+    <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
         <x:v>112</x:v>
       </x:c>
@@ -2927,7 +2939,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:7">
+    <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
         <x:v>114</x:v>
       </x:c>
@@ -2950,7 +2962,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:7">
+    <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
         <x:v>116</x:v>
       </x:c>
@@ -2973,7 +2985,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:7">
+    <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
         <x:v>118</x:v>
       </x:c>
@@ -2996,7 +3008,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:7">
+    <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
         <x:v>120</x:v>
       </x:c>
@@ -3019,7 +3031,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" spans="1:7">
+    <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
         <x:v>122</x:v>
       </x:c>
@@ -3042,7 +3054,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" spans="1:7">
+    <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
         <x:v>124</x:v>
       </x:c>
@@ -3065,7 +3077,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" spans="1:7">
+    <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
         <x:v>126</x:v>
       </x:c>
@@ -3088,7 +3100,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" spans="1:7">
+    <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
         <x:v>128</x:v>
       </x:c>
@@ -3111,7 +3123,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" spans="1:7">
+    <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
         <x:v>130</x:v>
       </x:c>
@@ -3134,7 +3146,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" spans="1:7">
+    <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
         <x:v>132</x:v>
       </x:c>
@@ -3157,7 +3169,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" spans="1:7">
+    <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
         <x:v>134</x:v>
       </x:c>
@@ -3180,7 +3192,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:7">
+    <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
         <x:v>136</x:v>
       </x:c>
@@ -3203,7 +3215,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" spans="1:7">
+    <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
         <x:v>138</x:v>
       </x:c>
@@ -3226,7 +3238,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" spans="1:7">
+    <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
         <x:v>140</x:v>
       </x:c>
@@ -3249,7 +3261,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" spans="1:7">
+    <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
         <x:v>142</x:v>
       </x:c>
@@ -3272,7 +3284,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" spans="1:7">
+    <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
         <x:v>144</x:v>
       </x:c>
@@ -3295,7 +3307,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" spans="1:7">
+    <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
         <x:v>146</x:v>
       </x:c>
@@ -3318,7 +3330,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" spans="1:7">
+    <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
         <x:v>148</x:v>
       </x:c>
@@ -3341,7 +3353,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" spans="1:7">
+    <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
         <x:v>150</x:v>
       </x:c>
@@ -3364,7 +3376,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" spans="1:7">
+    <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
         <x:v>152</x:v>
       </x:c>
@@ -3387,7 +3399,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" spans="1:7">
+    <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
         <x:v>154</x:v>
       </x:c>
@@ -3410,7 +3422,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" spans="1:7">
+    <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
         <x:v>156</x:v>
       </x:c>
@@ -3433,7 +3445,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" spans="1:7">
+    <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
         <x:v>158</x:v>
       </x:c>
@@ -3456,7 +3468,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" spans="1:7">
+    <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
         <x:v>160</x:v>
       </x:c>
@@ -3479,7 +3491,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" spans="1:7">
+    <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
         <x:v>162</x:v>
       </x:c>
@@ -3502,7 +3514,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" spans="1:7">
+    <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
         <x:v>164</x:v>
       </x:c>
@@ -3525,7 +3537,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" spans="1:7">
+    <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
         <x:v>166</x:v>
       </x:c>
@@ -3548,7 +3560,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" spans="1:7">
+    <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
         <x:v>168</x:v>
       </x:c>
@@ -3571,7 +3583,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" spans="1:7">
+    <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
         <x:v>170</x:v>
       </x:c>
@@ -3594,7 +3606,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" spans="1:7">
+    <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
         <x:v>172</x:v>
       </x:c>
@@ -3617,7 +3629,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" spans="1:7">
+    <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
         <x:v>174</x:v>
       </x:c>
@@ -3640,7 +3652,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" spans="1:7">
+    <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
         <x:v>176</x:v>
       </x:c>
@@ -3663,7 +3675,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" spans="1:7">
+    <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
         <x:v>178</x:v>
       </x:c>
@@ -3686,7 +3698,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" spans="1:7">
+    <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
         <x:v>180</x:v>
       </x:c>
@@ -3709,7 +3721,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" spans="1:7">
+    <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
         <x:v>182</x:v>
       </x:c>
@@ -3732,7 +3744,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" spans="1:7">
+    <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
         <x:v>184</x:v>
       </x:c>
@@ -3755,7 +3767,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" spans="1:7">
+    <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
         <x:v>186</x:v>
       </x:c>
@@ -3778,7 +3790,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" spans="1:7">
+    <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
         <x:v>188</x:v>
       </x:c>
@@ -3801,7 +3813,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" spans="1:7">
+    <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
         <x:v>190</x:v>
       </x:c>
@@ -3824,7 +3836,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" spans="1:7">
+    <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
         <x:v>192</x:v>
       </x:c>
@@ -3847,7 +3859,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" spans="1:7">
+    <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
         <x:v>194</x:v>
       </x:c>
@@ -3870,7 +3882,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" spans="1:7">
+    <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
         <x:v>196</x:v>
       </x:c>
@@ -3893,7 +3905,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" spans="1:7">
+    <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
         <x:v>198</x:v>
       </x:c>
@@ -3916,7 +3928,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" spans="1:7">
+    <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
         <x:v>200</x:v>
       </x:c>
@@ -3939,7 +3951,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" spans="1:7">
+    <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
         <x:v>202</x:v>
       </x:c>
@@ -3962,7 +3974,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" spans="1:7">
+    <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
         <x:v>204</x:v>
       </x:c>
@@ -3985,7 +3997,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" spans="1:7">
+    <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
         <x:v>206</x:v>
       </x:c>
@@ -4008,7 +4020,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" spans="1:7">
+    <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
         <x:v>208</x:v>
       </x:c>
@@ -4031,7 +4043,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" spans="1:7">
+    <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
         <x:v>210</x:v>
       </x:c>
@@ -4054,7 +4066,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" spans="1:7">
+    <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
         <x:v>212</x:v>
       </x:c>
@@ -4077,7 +4089,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" spans="1:7">
+    <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
         <x:v>214</x:v>
       </x:c>
@@ -4100,7 +4112,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" spans="1:7">
+    <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
         <x:v>216</x:v>
       </x:c>
@@ -4123,7 +4135,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" spans="1:7">
+    <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
         <x:v>218</x:v>
       </x:c>
@@ -4146,7 +4158,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" spans="1:7">
+    <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
         <x:v>220</x:v>
       </x:c>
@@ -4169,7 +4181,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" spans="1:7">
+    <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
         <x:v>222</x:v>
       </x:c>
@@ -4192,7 +4204,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" spans="1:7">
+    <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
         <x:v>224</x:v>
       </x:c>
@@ -4215,7 +4227,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" spans="1:7">
+    <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
         <x:v>226</x:v>
       </x:c>
@@ -4238,7 +4250,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" spans="1:7">
+    <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
         <x:v>228</x:v>
       </x:c>
@@ -4261,7 +4273,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" spans="1:7">
+    <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
         <x:v>230</x:v>
       </x:c>
@@ -4284,7 +4296,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" spans="1:7">
+    <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
         <x:v>232</x:v>
       </x:c>
@@ -4307,7 +4319,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" spans="1:7">
+    <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
@@ -4330,7 +4342,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" spans="1:7">
+    <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
         <x:v>236</x:v>
       </x:c>
@@ -4353,7 +4365,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" spans="1:7">
+    <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
         <x:v>238</x:v>
       </x:c>
@@ -4376,7 +4388,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" spans="1:7">
+    <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
         <x:v>240</x:v>
       </x:c>
@@ -4399,7 +4411,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" spans="1:7">
+    <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
         <x:v>242</x:v>
       </x:c>
@@ -4422,7 +4434,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" spans="1:7">
+    <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
         <x:v>244</x:v>
       </x:c>
@@ -4445,7 +4457,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" spans="1:7">
+    <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
         <x:v>246</x:v>
       </x:c>
@@ -4468,7 +4480,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" spans="1:7">
+    <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
         <x:v>248</x:v>
       </x:c>
@@ -4491,7 +4503,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" spans="1:7">
+    <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
         <x:v>250</x:v>
       </x:c>
@@ -4514,7 +4526,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" spans="1:7">
+    <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
         <x:v>252</x:v>
       </x:c>
@@ -4537,7 +4549,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" spans="1:7">
+    <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
         <x:v>254</x:v>
       </x:c>
@@ -4560,7 +4572,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" spans="1:7">
+    <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
         <x:v>256</x:v>
       </x:c>
@@ -4583,7 +4595,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" spans="1:7">
+    <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
         <x:v>258</x:v>
       </x:c>
@@ -4606,7 +4618,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" spans="1:7">
+    <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
         <x:v>260</x:v>
       </x:c>
@@ -4629,7 +4641,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" spans="1:7">
+    <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
         <x:v>262</x:v>
       </x:c>
@@ -4652,7 +4664,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" spans="1:7">
+    <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
         <x:v>264</x:v>
       </x:c>
@@ -4675,7 +4687,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" spans="1:7">
+    <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
         <x:v>266</x:v>
       </x:c>
@@ -4698,7 +4710,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" spans="1:7">
+    <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
         <x:v>268</x:v>
       </x:c>
@@ -4721,7 +4733,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" spans="1:7">
+    <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
         <x:v>270</x:v>
       </x:c>
@@ -4744,7 +4756,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" spans="1:7">
+    <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
         <x:v>272</x:v>
       </x:c>
@@ -4767,7 +4779,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" spans="1:7">
+    <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
         <x:v>274</x:v>
       </x:c>
@@ -4790,7 +4802,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" spans="1:7">
+    <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
         <x:v>276</x:v>
       </x:c>
@@ -4813,7 +4825,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" spans="1:7">
+    <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
         <x:v>278</x:v>
       </x:c>
@@ -4836,7 +4848,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" spans="1:7">
+    <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
         <x:v>280</x:v>
       </x:c>
@@ -4859,7 +4871,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" spans="1:7">
+    <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
         <x:v>282</x:v>
       </x:c>
@@ -4882,7 +4894,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="134" spans="1:7">
+    <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
         <x:v>284</x:v>
       </x:c>
@@ -4905,7 +4917,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" spans="1:7">
+    <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
         <x:v>286</x:v>
       </x:c>
@@ -4928,7 +4940,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" spans="1:7">
+    <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
         <x:v>288</x:v>
       </x:c>
@@ -4951,7 +4963,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" spans="1:7">
+    <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
         <x:v>290</x:v>
       </x:c>
@@ -4974,7 +4986,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" spans="1:7">
+    <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
         <x:v>292</x:v>
       </x:c>
@@ -4997,7 +5009,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" spans="1:7">
+    <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
         <x:v>294</x:v>
       </x:c>
@@ -5020,7 +5032,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" spans="1:7">
+    <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
         <x:v>296</x:v>
       </x:c>
@@ -5043,7 +5055,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" spans="1:7">
+    <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
         <x:v>298</x:v>
       </x:c>
@@ -5066,7 +5078,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" spans="1:7">
+    <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
         <x:v>300</x:v>
       </x:c>
@@ -5074,7 +5086,7 @@
         <x:v>301</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
         <x:v>40</x:v>
@@ -5089,7 +5101,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" spans="1:7">
+    <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
         <x:v>302</x:v>
       </x:c>
@@ -5097,7 +5109,7 @@
         <x:v>303</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
         <x:v>40</x:v>
@@ -5112,7 +5124,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" spans="1:7">
+    <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
         <x:v>304</x:v>
       </x:c>
@@ -5120,7 +5132,7 @@
         <x:v>305</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
         <x:v>40</x:v>
@@ -5135,7 +5147,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" spans="1:7">
+    <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
         <x:v>306</x:v>
       </x:c>
@@ -5143,7 +5155,7 @@
         <x:v>307</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
         <x:v>40</x:v>
@@ -5158,7 +5170,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" spans="1:7">
+    <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
         <x:v>308</x:v>
       </x:c>
@@ -5166,7 +5178,7 @@
         <x:v>309</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
         <x:v>40</x:v>
@@ -5181,7 +5193,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" spans="1:7">
+    <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
         <x:v>310</x:v>
       </x:c>
@@ -5189,7 +5201,7 @@
         <x:v>311</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
         <x:v>40</x:v>
@@ -5204,7 +5216,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" spans="1:7">
+    <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
         <x:v>312</x:v>
       </x:c>
@@ -5212,7 +5224,7 @@
         <x:v>313</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>40</x:v>
@@ -5227,7 +5239,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" spans="1:7">
+    <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
         <x:v>314</x:v>
       </x:c>
@@ -5235,7 +5247,7 @@
         <x:v>315</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
         <x:v>40</x:v>
@@ -5250,7 +5262,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" spans="1:7">
+    <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
         <x:v>316</x:v>
       </x:c>
@@ -5258,7 +5270,7 @@
         <x:v>317</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>40</x:v>
@@ -5273,7 +5285,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" spans="1:7">
+    <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
         <x:v>318</x:v>
       </x:c>
@@ -5281,7 +5293,7 @@
         <x:v>319</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>40</x:v>
@@ -5296,7 +5308,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" spans="1:7">
+    <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
         <x:v>320</x:v>
       </x:c>
@@ -5304,7 +5316,7 @@
         <x:v>321</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
         <x:v>40</x:v>
@@ -5319,7 +5331,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" spans="1:7">
+    <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
         <x:v>322</x:v>
       </x:c>
@@ -5327,7 +5339,7 @@
         <x:v>323</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
         <x:v>40</x:v>
@@ -5342,7 +5354,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" spans="1:7">
+    <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
         <x:v>324</x:v>
       </x:c>
@@ -5350,7 +5362,7 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>40</x:v>
@@ -5365,7 +5377,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" spans="1:7">
+    <x:row r="155" spans="1:9">
       <x:c r="A155" s="0" t="s">
         <x:v>326</x:v>
       </x:c>
@@ -5373,7 +5385,7 @@
         <x:v>327</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
         <x:v>40</x:v>
@@ -5388,7 +5400,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" spans="1:7">
+    <x:row r="156" spans="1:9">
       <x:c r="A156" s="0" t="s">
         <x:v>328</x:v>
       </x:c>
@@ -5396,7 +5408,7 @@
         <x:v>329</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
         <x:v>40</x:v>
@@ -5411,7 +5423,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" spans="1:7">
+    <x:row r="157" spans="1:9">
       <x:c r="A157" s="0" t="s">
         <x:v>330</x:v>
       </x:c>
@@ -5419,7 +5431,7 @@
         <x:v>331</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
         <x:v>40</x:v>
@@ -5434,7 +5446,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" spans="1:7">
+    <x:row r="158" spans="1:9">
       <x:c r="A158" s="0" t="s">
         <x:v>332</x:v>
       </x:c>
@@ -5442,7 +5454,7 @@
         <x:v>333</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
         <x:v>40</x:v>
@@ -5457,7 +5469,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" spans="1:7">
+    <x:row r="159" spans="1:9">
       <x:c r="A159" s="0" t="s">
         <x:v>334</x:v>
       </x:c>
@@ -5465,7 +5477,7 @@
         <x:v>335</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
         <x:v>40</x:v>
@@ -5480,7 +5492,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" spans="1:7">
+    <x:row r="160" spans="1:9">
       <x:c r="A160" s="0" t="s">
         <x:v>336</x:v>
       </x:c>
@@ -5488,7 +5500,7 @@
         <x:v>337</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
         <x:v>40</x:v>
@@ -5503,7 +5515,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" spans="1:7">
+    <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
         <x:v>338</x:v>
       </x:c>
@@ -5511,7 +5523,7 @@
         <x:v>339</x:v>
       </x:c>
       <x:c r="C161" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
         <x:v>40</x:v>
@@ -5526,7 +5538,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" spans="1:7">
+    <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
         <x:v>340</x:v>
       </x:c>
@@ -5534,7 +5546,7 @@
         <x:v>341</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
         <x:v>40</x:v>
@@ -5549,7 +5561,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" spans="1:7">
+    <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
         <x:v>342</x:v>
       </x:c>
@@ -5557,7 +5569,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
         <x:v>40</x:v>
@@ -5572,7 +5584,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" spans="1:7">
+    <x:row r="164" spans="1:9">
       <x:c r="A164" s="0" t="s">
         <x:v>344</x:v>
       </x:c>
@@ -5580,7 +5592,7 @@
         <x:v>345</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>40</x:v>
@@ -5595,7 +5607,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" spans="1:7">
+    <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
         <x:v>346</x:v>
       </x:c>
@@ -5603,7 +5615,7 @@
         <x:v>347</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>40</x:v>
@@ -5618,7 +5630,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" spans="1:7">
+    <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
         <x:v>348</x:v>
       </x:c>
@@ -5626,7 +5638,7 @@
         <x:v>349</x:v>
       </x:c>
       <x:c r="C166" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
         <x:v>40</x:v>
@@ -5641,7 +5653,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" spans="1:7">
+    <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
         <x:v>350</x:v>
       </x:c>
@@ -5649,7 +5661,7 @@
         <x:v>351</x:v>
       </x:c>
       <x:c r="C167" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
         <x:v>40</x:v>
@@ -5664,7 +5676,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" spans="1:7">
+    <x:row r="168" spans="1:9">
       <x:c r="A168" s="0" t="s">
         <x:v>352</x:v>
       </x:c>
@@ -5687,7 +5699,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="169" spans="1:7">
+    <x:row r="169" spans="1:9">
       <x:c r="A169" s="0" t="s">
         <x:v>354</x:v>
       </x:c>
@@ -5710,7 +5722,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="170" spans="1:7">
+    <x:row r="170" spans="1:9">
       <x:c r="A170" s="0" t="s">
         <x:v>356</x:v>
       </x:c>
@@ -5733,7 +5745,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="171" spans="1:7">
+    <x:row r="171" spans="1:9">
       <x:c r="A171" s="0" t="s">
         <x:v>358</x:v>
       </x:c>
@@ -5756,7 +5768,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="172" spans="1:7">
+    <x:row r="172" spans="1:9">
       <x:c r="A172" s="0" t="s">
         <x:v>360</x:v>
       </x:c>
@@ -5779,7 +5791,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="173" spans="1:7">
+    <x:row r="173" spans="1:9">
       <x:c r="A173" s="0" t="s">
         <x:v>362</x:v>
       </x:c>
@@ -5802,7 +5814,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="174" spans="1:7">
+    <x:row r="174" spans="1:9">
       <x:c r="A174" s="0" t="s">
         <x:v>364</x:v>
       </x:c>
@@ -5825,7 +5837,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="175" spans="1:7">
+    <x:row r="175" spans="1:9">
       <x:c r="A175" s="0" t="s">
         <x:v>366</x:v>
       </x:c>
@@ -5848,7 +5860,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="176" spans="1:7">
+    <x:row r="176" spans="1:9">
       <x:c r="A176" s="0" t="s">
         <x:v>368</x:v>
       </x:c>
@@ -5871,7 +5883,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="177" spans="1:7">
+    <x:row r="177" spans="1:9">
       <x:c r="A177" s="0" t="s">
         <x:v>370</x:v>
       </x:c>
@@ -5894,7 +5906,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="178" spans="1:7">
+    <x:row r="178" spans="1:9">
       <x:c r="A178" s="0" t="s">
         <x:v>372</x:v>
       </x:c>
@@ -5917,7 +5929,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="179" spans="1:7">
+    <x:row r="179" spans="1:9">
       <x:c r="A179" s="0" t="s">
         <x:v>374</x:v>
       </x:c>
@@ -5940,7 +5952,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="180" spans="1:7">
+    <x:row r="180" spans="1:9">
       <x:c r="A180" s="0" t="s">
         <x:v>376</x:v>
       </x:c>
@@ -5963,7 +5975,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="181" spans="1:7">
+    <x:row r="181" spans="1:9">
       <x:c r="A181" s="0" t="s">
         <x:v>378</x:v>
       </x:c>
@@ -5986,7 +5998,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="182" spans="1:7">
+    <x:row r="182" spans="1:9">
       <x:c r="A182" s="0" t="s">
         <x:v>380</x:v>
       </x:c>
@@ -6009,7 +6021,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="183" spans="1:7">
+    <x:row r="183" spans="1:9">
       <x:c r="A183" s="0" t="s">
         <x:v>382</x:v>
       </x:c>
@@ -6032,7 +6044,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="184" spans="1:7">
+    <x:row r="184" spans="1:9">
       <x:c r="A184" s="0" t="s">
         <x:v>384</x:v>
       </x:c>
@@ -6055,7 +6067,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="185" spans="1:7">
+    <x:row r="185" spans="1:9">
       <x:c r="A185" s="0" t="s">
         <x:v>386</x:v>
       </x:c>
@@ -6078,7 +6090,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="186" spans="1:7">
+    <x:row r="186" spans="1:9">
       <x:c r="A186" s="0" t="s">
         <x:v>388</x:v>
       </x:c>
@@ -6101,7 +6113,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="187" spans="1:7">
+    <x:row r="187" spans="1:9">
       <x:c r="A187" s="0" t="s">
         <x:v>390</x:v>
       </x:c>
@@ -6124,7 +6136,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="188" spans="1:7">
+    <x:row r="188" spans="1:9">
       <x:c r="A188" s="0" t="s">
         <x:v>392</x:v>
       </x:c>
@@ -6147,7 +6159,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="189" spans="1:7">
+    <x:row r="189" spans="1:9">
       <x:c r="A189" s="0" t="s">
         <x:v>394</x:v>
       </x:c>
@@ -6170,7 +6182,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" spans="1:7">
+    <x:row r="190" spans="1:9">
       <x:c r="A190" s="0" t="s">
         <x:v>396</x:v>
       </x:c>
@@ -6193,7 +6205,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="191" spans="1:7">
+    <x:row r="191" spans="1:9">
       <x:c r="A191" s="0" t="s">
         <x:v>398</x:v>
       </x:c>
@@ -6216,7 +6228,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="192" spans="1:7">
+    <x:row r="192" spans="1:9">
       <x:c r="A192" s="0" t="s">
         <x:v>400</x:v>
       </x:c>
@@ -6239,7 +6251,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="193" spans="1:7">
+    <x:row r="193" spans="1:9">
       <x:c r="A193" s="0" t="s">
         <x:v>402</x:v>
       </x:c>
@@ -6262,7 +6274,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="194" spans="1:7">
+    <x:row r="194" spans="1:9">
       <x:c r="A194" s="0" t="s">
         <x:v>404</x:v>
       </x:c>
@@ -6285,7 +6297,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="195" spans="1:7">
+    <x:row r="195" spans="1:9">
       <x:c r="A195" s="0" t="s">
         <x:v>406</x:v>
       </x:c>
@@ -6308,7 +6320,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="196" spans="1:7">
+    <x:row r="196" spans="1:9">
       <x:c r="A196" s="0" t="s">
         <x:v>408</x:v>
       </x:c>
@@ -6331,7 +6343,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="197" spans="1:7">
+    <x:row r="197" spans="1:9">
       <x:c r="A197" s="0" t="s">
         <x:v>410</x:v>
       </x:c>
@@ -6339,7 +6351,7 @@
         <x:v>411</x:v>
       </x:c>
       <x:c r="C197" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D197" s="0" t="s">
         <x:v>40</x:v>
@@ -6354,7 +6366,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="198" spans="1:7">
+    <x:row r="198" spans="1:9">
       <x:c r="A198" s="0" t="s">
         <x:v>412</x:v>
       </x:c>
@@ -6362,7 +6374,7 @@
         <x:v>413</x:v>
       </x:c>
       <x:c r="C198" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D198" s="0" t="s">
         <x:v>40</x:v>
@@ -6377,7 +6389,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="199" spans="1:7">
+    <x:row r="199" spans="1:9">
       <x:c r="A199" s="0" t="s">
         <x:v>414</x:v>
       </x:c>
@@ -6385,7 +6397,7 @@
         <x:v>415</x:v>
       </x:c>
       <x:c r="C199" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D199" s="0" t="s">
         <x:v>40</x:v>
@@ -6400,7 +6412,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="200" spans="1:7">
+    <x:row r="200" spans="1:9">
       <x:c r="A200" s="0" t="s">
         <x:v>416</x:v>
       </x:c>
@@ -6408,7 +6420,7 @@
         <x:v>417</x:v>
       </x:c>
       <x:c r="C200" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D200" s="0" t="s">
         <x:v>40</x:v>
@@ -6423,7 +6435,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="201" spans="1:7">
+    <x:row r="201" spans="1:9">
       <x:c r="A201" s="0" t="s">
         <x:v>418</x:v>
       </x:c>
@@ -6431,7 +6443,7 @@
         <x:v>419</x:v>
       </x:c>
       <x:c r="C201" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
         <x:v>40</x:v>
@@ -6446,7 +6458,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="202" spans="1:7">
+    <x:row r="202" spans="1:9">
       <x:c r="A202" s="0" t="s">
         <x:v>420</x:v>
       </x:c>
@@ -6454,7 +6466,7 @@
         <x:v>421</x:v>
       </x:c>
       <x:c r="C202" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D202" s="0" t="s">
         <x:v>40</x:v>
@@ -6469,7 +6481,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="203" spans="1:7">
+    <x:row r="203" spans="1:9">
       <x:c r="A203" s="0" t="s">
         <x:v>422</x:v>
       </x:c>
@@ -6477,7 +6489,7 @@
         <x:v>423</x:v>
       </x:c>
       <x:c r="C203" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
         <x:v>40</x:v>
@@ -6492,7 +6504,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="204" spans="1:7">
+    <x:row r="204" spans="1:9">
       <x:c r="A204" s="0" t="s">
         <x:v>424</x:v>
       </x:c>
@@ -6500,7 +6512,7 @@
         <x:v>425</x:v>
       </x:c>
       <x:c r="C204" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D204" s="0" t="s">
         <x:v>40</x:v>
@@ -6515,7 +6527,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="205" spans="1:7">
+    <x:row r="205" spans="1:9">
       <x:c r="A205" s="0" t="s">
         <x:v>426</x:v>
       </x:c>
@@ -6523,7 +6535,7 @@
         <x:v>427</x:v>
       </x:c>
       <x:c r="C205" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D205" s="0" t="s">
         <x:v>40</x:v>
@@ -6538,7 +6550,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="206" spans="1:7">
+    <x:row r="206" spans="1:9">
       <x:c r="A206" s="0" t="s">
         <x:v>428</x:v>
       </x:c>
@@ -6546,7 +6558,7 @@
         <x:v>429</x:v>
       </x:c>
       <x:c r="C206" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D206" s="0" t="s">
         <x:v>40</x:v>
@@ -6561,7 +6573,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="207" spans="1:7">
+    <x:row r="207" spans="1:9">
       <x:c r="A207" s="0" t="s">
         <x:v>430</x:v>
       </x:c>
@@ -6569,7 +6581,7 @@
         <x:v>431</x:v>
       </x:c>
       <x:c r="C207" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D207" s="0" t="s">
         <x:v>40</x:v>
@@ -6584,7 +6596,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="208" spans="1:7">
+    <x:row r="208" spans="1:9">
       <x:c r="A208" s="0" t="s">
         <x:v>432</x:v>
       </x:c>
@@ -6592,7 +6604,7 @@
         <x:v>433</x:v>
       </x:c>
       <x:c r="C208" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D208" s="0" t="s">
         <x:v>40</x:v>
@@ -6607,7 +6619,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="209" spans="1:7">
+    <x:row r="209" spans="1:9">
       <x:c r="A209" s="0" t="s">
         <x:v>434</x:v>
       </x:c>
@@ -6615,7 +6627,7 @@
         <x:v>435</x:v>
       </x:c>
       <x:c r="C209" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D209" s="0" t="s">
         <x:v>40</x:v>
@@ -6630,7 +6642,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="210" spans="1:7">
+    <x:row r="210" spans="1:9">
       <x:c r="A210" s="0" t="s">
         <x:v>436</x:v>
       </x:c>
@@ -6638,7 +6650,7 @@
         <x:v>437</x:v>
       </x:c>
       <x:c r="C210" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D210" s="0" t="s">
         <x:v>40</x:v>
@@ -6653,7 +6665,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="211" spans="1:7">
+    <x:row r="211" spans="1:9">
       <x:c r="A211" s="0" t="s">
         <x:v>438</x:v>
       </x:c>
@@ -6661,7 +6673,7 @@
         <x:v>439</x:v>
       </x:c>
       <x:c r="C211" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D211" s="0" t="s">
         <x:v>40</x:v>
@@ -6676,7 +6688,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="212" spans="1:7">
+    <x:row r="212" spans="1:9">
       <x:c r="A212" s="0" t="s">
         <x:v>440</x:v>
       </x:c>
@@ -6684,7 +6696,7 @@
         <x:v>441</x:v>
       </x:c>
       <x:c r="C212" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D212" s="0" t="s">
         <x:v>40</x:v>
@@ -6699,7 +6711,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="213" spans="1:7">
+    <x:row r="213" spans="1:9">
       <x:c r="A213" s="0" t="s">
         <x:v>442</x:v>
       </x:c>
@@ -6707,7 +6719,7 @@
         <x:v>443</x:v>
       </x:c>
       <x:c r="C213" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D213" s="0" t="s">
         <x:v>40</x:v>
@@ -6722,7 +6734,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="214" spans="1:7">
+    <x:row r="214" spans="1:9">
       <x:c r="A214" s="0" t="s">
         <x:v>444</x:v>
       </x:c>
@@ -6730,7 +6742,7 @@
         <x:v>445</x:v>
       </x:c>
       <x:c r="C214" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D214" s="0" t="s">
         <x:v>40</x:v>
@@ -6745,7 +6757,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="215" spans="1:7">
+    <x:row r="215" spans="1:9">
       <x:c r="A215" s="0" t="s">
         <x:v>446</x:v>
       </x:c>
@@ -6753,7 +6765,7 @@
         <x:v>447</x:v>
       </x:c>
       <x:c r="C215" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D215" s="0" t="s">
         <x:v>40</x:v>
@@ -6768,7 +6780,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="216" spans="1:7">
+    <x:row r="216" spans="1:9">
       <x:c r="A216" s="0" t="s">
         <x:v>448</x:v>
       </x:c>
@@ -6776,7 +6788,7 @@
         <x:v>449</x:v>
       </x:c>
       <x:c r="C216" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
         <x:v>40</x:v>
@@ -6791,7 +6803,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="217" spans="1:7">
+    <x:row r="217" spans="1:9">
       <x:c r="A217" s="0" t="s">
         <x:v>450</x:v>
       </x:c>
@@ -6799,7 +6811,7 @@
         <x:v>451</x:v>
       </x:c>
       <x:c r="C217" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
         <x:v>40</x:v>
@@ -6814,7 +6826,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="218" spans="1:7">
+    <x:row r="218" spans="1:9">
       <x:c r="A218" s="0" t="s">
         <x:v>452</x:v>
       </x:c>
@@ -6822,7 +6834,7 @@
         <x:v>453</x:v>
       </x:c>
       <x:c r="C218" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
         <x:v>40</x:v>
@@ -6837,7 +6849,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="219" spans="1:7">
+    <x:row r="219" spans="1:9">
       <x:c r="A219" s="0" t="s">
         <x:v>454</x:v>
       </x:c>
@@ -6845,7 +6857,7 @@
         <x:v>455</x:v>
       </x:c>
       <x:c r="C219" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
         <x:v>40</x:v>
@@ -6860,7 +6872,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="220" spans="1:7">
+    <x:row r="220" spans="1:9">
       <x:c r="A220" s="0" t="s">
         <x:v>456</x:v>
       </x:c>
@@ -6868,7 +6880,7 @@
         <x:v>457</x:v>
       </x:c>
       <x:c r="C220" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D220" s="0" t="s">
         <x:v>40</x:v>
@@ -6883,7 +6895,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="221" spans="1:7">
+    <x:row r="221" spans="1:9">
       <x:c r="A221" s="0" t="s">
         <x:v>458</x:v>
       </x:c>
@@ -6891,7 +6903,7 @@
         <x:v>459</x:v>
       </x:c>
       <x:c r="C221" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D221" s="0" t="s">
         <x:v>40</x:v>
@@ -6906,7 +6918,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="222" spans="1:7">
+    <x:row r="222" spans="1:9">
       <x:c r="A222" s="0" t="s">
         <x:v>460</x:v>
       </x:c>
@@ -6914,7 +6926,7 @@
         <x:v>461</x:v>
       </x:c>
       <x:c r="C222" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D222" s="0" t="s">
         <x:v>40</x:v>
@@ -6929,7 +6941,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="223" spans="1:7">
+    <x:row r="223" spans="1:9">
       <x:c r="A223" s="0" t="s">
         <x:v>462</x:v>
       </x:c>
@@ -6937,7 +6949,7 @@
         <x:v>463</x:v>
       </x:c>
       <x:c r="C223" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D223" s="0" t="s">
         <x:v>40</x:v>
@@ -6952,7 +6964,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="224" spans="1:7">
+    <x:row r="224" spans="1:9">
       <x:c r="A224" s="0" t="s">
         <x:v>464</x:v>
       </x:c>
@@ -6960,7 +6972,7 @@
         <x:v>465</x:v>
       </x:c>
       <x:c r="C224" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D224" s="0" t="s">
         <x:v>40</x:v>
@@ -6975,7 +6987,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="225" spans="1:7">
+    <x:row r="225" spans="1:9">
       <x:c r="A225" s="0" t="s">
         <x:v>466</x:v>
       </x:c>
@@ -6983,7 +6995,7 @@
         <x:v>467</x:v>
       </x:c>
       <x:c r="C225" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D225" s="0" t="s">
         <x:v>40</x:v>
@@ -6998,7 +7010,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="226" spans="1:7">
+    <x:row r="226" spans="1:9">
       <x:c r="A226" s="0" t="s">
         <x:v>468</x:v>
       </x:c>
@@ -7006,7 +7018,7 @@
         <x:v>469</x:v>
       </x:c>
       <x:c r="C226" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D226" s="0" t="s">
         <x:v>40</x:v>
@@ -7021,7 +7033,7 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
-    <x:row r="227" spans="1:7">
+    <x:row r="227" spans="1:9">
       <x:c r="A227" s="0" t="s">
         <x:v>470</x:v>
       </x:c>
@@ -7029,7 +7041,7 @@
         <x:v>471</x:v>
       </x:c>
       <x:c r="C227" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
         <x:v>40</x:v>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 11:57:13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08-12-2025 12:00:18</x:t>
+    <x:t>08-12-2025 12:09:48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 12:12:39</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -61,7 +61,7 @@
     <x:t>anlpvhe187047</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:00:12</x:t>
+    <x:t>08-12-2025 12:12:40</x:t>
   </x:si>
   <x:si>
     <x:t>3</x:t>
@@ -70,7 +70,7 @@
     <x:t>cuongnvhe181200</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:00:15</x:t>
+    <x:t>08-12-2025 12:12:36</x:t>
   </x:si>
   <x:si>
     <x:t>4</x:t>
@@ -79,7 +79,7 @@
     <x:t>ducnthe180869</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 11:57:59</x:t>
+    <x:t>08-12-2025 12:10:52</x:t>
   </x:si>
   <x:si>
     <x:t>5</x:t>
@@ -88,10 +88,7 @@
     <x:t>dungdvhe181404</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 11:57:12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08-12-2025 12:00:11</x:t>
+    <x:t>08-12-2025 12:12:37</x:t>
   </x:si>
   <x:si>
     <x:t>6</x:t>
@@ -106,7 +103,7 @@
     <x:t>duongnthe186310</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:00:25</x:t>
+    <x:t>08-12-2025 12:12:26</x:t>
   </x:si>
   <x:si>
     <x:t>8</x:t>
@@ -121,15 +118,15 @@
     <x:t>duyldhe176352</x:t>
   </x:si>
   <x:si>
+    <x:t>08-12-2025 12:12:48</x:t>
+  </x:si>
+  <x:si>
     <x:t>10</x:t>
   </x:si>
   <x:si>
     <x:t>duynthe180374</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:00:10</x:t>
-  </x:si>
-  <x:si>
     <x:t>11</x:t>
   </x:si>
   <x:si>
@@ -1432,10 +1429,10 @@
     <x:t>vietddhe161942</x:t>
   </x:si>
   <x:si>
-    <x:t>2025-12-08 12:00:25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.16s</x:t>
+    <x:t>2025-12-08 12:12:48</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.17s</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1875,10 +1872,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
         <x:v>472</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>473</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -1967,18 +1964,18 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G6" s="2" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="G6" s="2" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
       <x:c r="A7" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B7" s="2" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="B7" s="2" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="2" t="s">
         <x:v>7</x:v>
@@ -1998,10 +1995,10 @@
     </x:row>
     <x:row r="8" spans="1:9">
       <x:c r="A8" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B8" s="2" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="B8" s="2" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
         <x:v>7</x:v>
@@ -2016,15 +2013,15 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
       <x:c r="A9" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B9" s="2" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="B9" s="2" t="s">
-        <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
         <x:v>7</x:v>
@@ -2039,15 +2036,15 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G9" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="B10" s="2" t="s">
-        <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
         <x:v>7</x:v>
@@ -2062,7 +2059,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G10" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -2082,4978 +2079,4978 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F11" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G11" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>45</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>63</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>99</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>101</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>107</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>109</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>111</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
         <x:v>112</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>115</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>117</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>119</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>125</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
         <x:v>126</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>127</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G56" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>131</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G57" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>133</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G58" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G59" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>137</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G60" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>139</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G61" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G62" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G63" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>145</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G64" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>147</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G65" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
         <x:v>148</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>149</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G66" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>151</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G67" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>153</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G68" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
         <x:v>154</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>155</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G69" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
         <x:v>156</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G70" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
         <x:v>158</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>159</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G71" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>161</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G72" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
         <x:v>162</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>163</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G73" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>165</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G74" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
         <x:v>166</x:v>
-      </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>167</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G75" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
         <x:v>168</x:v>
-      </x:c>
-      <x:c r="B76" s="0" t="s">
-        <x:v>169</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G76" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
         <x:v>170</x:v>
-      </x:c>
-      <x:c r="B77" s="0" t="s">
-        <x:v>171</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G77" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
         <x:v>172</x:v>
-      </x:c>
-      <x:c r="B78" s="0" t="s">
-        <x:v>173</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G78" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="B79" s="0" t="s">
-        <x:v>175</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G79" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
         <x:v>176</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>177</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G80" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>179</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G81" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
         <x:v>180</x:v>
-      </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>181</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G82" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
         <x:v>182</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>183</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G83" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>185</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G84" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
         <x:v>186</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>187</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G85" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
         <x:v>188</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>189</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G86" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
         <x:v>190</x:v>
-      </x:c>
-      <x:c r="B87" s="0" t="s">
-        <x:v>191</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G87" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G88" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
         <x:v>194</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>195</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G89" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
         <x:v>196</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>197</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G90" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="B91" s="0" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G91" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
         <x:v>200</x:v>
-      </x:c>
-      <x:c r="B92" s="0" t="s">
-        <x:v>201</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G92" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
         <x:v>202</x:v>
-      </x:c>
-      <x:c r="B93" s="0" t="s">
-        <x:v>203</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G93" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
         <x:v>204</x:v>
-      </x:c>
-      <x:c r="B94" s="0" t="s">
-        <x:v>205</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G94" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
         <x:v>206</x:v>
-      </x:c>
-      <x:c r="B95" s="0" t="s">
-        <x:v>207</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G95" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
         <x:v>208</x:v>
-      </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>209</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G96" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>211</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G97" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
         <x:v>212</x:v>
-      </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>213</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G98" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="B99" s="0" t="s">
-        <x:v>215</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G99" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
         <x:v>216</x:v>
-      </x:c>
-      <x:c r="B100" s="0" t="s">
-        <x:v>217</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G100" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
         <x:v>218</x:v>
-      </x:c>
-      <x:c r="B101" s="0" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G101" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="B102" s="0" t="s">
-        <x:v>221</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G102" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="B103" s="0" t="s">
-        <x:v>223</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G103" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
         <x:v>224</x:v>
-      </x:c>
-      <x:c r="B104" s="0" t="s">
-        <x:v>225</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G104" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="B105" s="0" t="s">
-        <x:v>227</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G105" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="B106" s="0" t="s">
-        <x:v>229</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G106" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
         <x:v>230</x:v>
-      </x:c>
-      <x:c r="B107" s="0" t="s">
-        <x:v>231</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G107" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="B108" s="0" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G108" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
         <x:v>234</x:v>
-      </x:c>
-      <x:c r="B109" s="0" t="s">
-        <x:v>235</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G109" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="B110" s="0" t="s">
-        <x:v>237</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G110" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
         <x:v>238</x:v>
-      </x:c>
-      <x:c r="B111" s="0" t="s">
-        <x:v>239</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G111" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
         <x:v>240</x:v>
-      </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>241</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G112" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>243</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G113" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
         <x:v>244</x:v>
-      </x:c>
-      <x:c r="B114" s="0" t="s">
-        <x:v>245</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G114" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
         <x:v>246</x:v>
-      </x:c>
-      <x:c r="B115" s="0" t="s">
-        <x:v>247</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G115" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>249</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G116" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>251</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G117" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
         <x:v>252</x:v>
-      </x:c>
-      <x:c r="B118" s="0" t="s">
-        <x:v>253</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G118" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
         <x:v>254</x:v>
-      </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>255</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G119" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
         <x:v>256</x:v>
-      </x:c>
-      <x:c r="B120" s="0" t="s">
-        <x:v>257</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G120" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
         <x:v>258</x:v>
-      </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>259</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G121" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="B122" s="0" t="s">
-        <x:v>261</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G122" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
         <x:v>262</x:v>
-      </x:c>
-      <x:c r="B123" s="0" t="s">
-        <x:v>263</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G123" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
         <x:v>264</x:v>
-      </x:c>
-      <x:c r="B124" s="0" t="s">
-        <x:v>265</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G124" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
         <x:v>266</x:v>
-      </x:c>
-      <x:c r="B125" s="0" t="s">
-        <x:v>267</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G125" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="B126" s="0" t="s">
-        <x:v>269</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G126" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
         <x:v>270</x:v>
-      </x:c>
-      <x:c r="B127" s="0" t="s">
-        <x:v>271</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G127" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
         <x:v>272</x:v>
-      </x:c>
-      <x:c r="B128" s="0" t="s">
-        <x:v>273</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G128" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
         <x:v>274</x:v>
-      </x:c>
-      <x:c r="B129" s="0" t="s">
-        <x:v>275</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G129" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
         <x:v>276</x:v>
-      </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>277</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G130" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
         <x:v>278</x:v>
-      </x:c>
-      <x:c r="B131" s="0" t="s">
-        <x:v>279</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G131" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
         <x:v>280</x:v>
-      </x:c>
-      <x:c r="B132" s="0" t="s">
-        <x:v>281</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G132" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
         <x:v>282</x:v>
-      </x:c>
-      <x:c r="B133" s="0" t="s">
-        <x:v>283</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G133" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
         <x:v>284</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>285</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G134" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
         <x:v>286</x:v>
-      </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>287</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G135" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
         <x:v>288</x:v>
-      </x:c>
-      <x:c r="B136" s="0" t="s">
-        <x:v>289</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G136" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
         <x:v>290</x:v>
-      </x:c>
-      <x:c r="B137" s="0" t="s">
-        <x:v>291</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G137" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
         <x:v>292</x:v>
-      </x:c>
-      <x:c r="B138" s="0" t="s">
-        <x:v>293</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G138" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
         <x:v>294</x:v>
-      </x:c>
-      <x:c r="B139" s="0" t="s">
-        <x:v>295</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G139" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
         <x:v>296</x:v>
-      </x:c>
-      <x:c r="B140" s="0" t="s">
-        <x:v>297</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G140" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
         <x:v>298</x:v>
-      </x:c>
-      <x:c r="B141" s="0" t="s">
-        <x:v>299</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G141" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="B142" s="0" t="s">
-        <x:v>301</x:v>
-      </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G142" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
         <x:v>302</x:v>
       </x:c>
-      <x:c r="B143" s="0" t="s">
-        <x:v>303</x:v>
-      </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G143" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
         <x:v>304</x:v>
       </x:c>
-      <x:c r="B144" s="0" t="s">
-        <x:v>305</x:v>
-      </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G144" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
         <x:v>306</x:v>
       </x:c>
-      <x:c r="B145" s="0" t="s">
-        <x:v>307</x:v>
-      </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G145" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
         <x:v>308</x:v>
       </x:c>
-      <x:c r="B146" s="0" t="s">
-        <x:v>309</x:v>
-      </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G146" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="B147" s="0" t="s">
-        <x:v>311</x:v>
-      </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G147" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
         <x:v>312</x:v>
       </x:c>
-      <x:c r="B148" s="0" t="s">
-        <x:v>313</x:v>
-      </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G148" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
         <x:v>314</x:v>
       </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>315</x:v>
-      </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G149" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
         <x:v>316</x:v>
       </x:c>
-      <x:c r="B150" s="0" t="s">
-        <x:v>317</x:v>
-      </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G150" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
         <x:v>318</x:v>
       </x:c>
-      <x:c r="B151" s="0" t="s">
-        <x:v>319</x:v>
-      </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G151" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
         <x:v>320</x:v>
       </x:c>
-      <x:c r="B152" s="0" t="s">
-        <x:v>321</x:v>
-      </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G152" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
         <x:v>322</x:v>
       </x:c>
-      <x:c r="B153" s="0" t="s">
-        <x:v>323</x:v>
-      </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G153" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
         <x:v>324</x:v>
       </x:c>
-      <x:c r="B154" s="0" t="s">
-        <x:v>325</x:v>
-      </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G154" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:9">
       <x:c r="A155" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="B155" s="0" t="s">
-        <x:v>327</x:v>
-      </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G155" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:9">
       <x:c r="A156" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="B156" s="0" t="s">
-        <x:v>329</x:v>
-      </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G156" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:9">
       <x:c r="A157" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="B157" s="0" t="s">
-        <x:v>331</x:v>
-      </x:c>
       <x:c r="C157" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G157" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:9">
       <x:c r="A158" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
         <x:v>332</x:v>
       </x:c>
-      <x:c r="B158" s="0" t="s">
-        <x:v>333</x:v>
-      </x:c>
       <x:c r="C158" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G158" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:9">
       <x:c r="A159" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
         <x:v>334</x:v>
       </x:c>
-      <x:c r="B159" s="0" t="s">
-        <x:v>335</x:v>
-      </x:c>
       <x:c r="C159" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G159" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:9">
       <x:c r="A160" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="B160" s="0" t="s">
-        <x:v>337</x:v>
-      </x:c>
       <x:c r="C160" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G160" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="B161" s="0" t="s">
-        <x:v>339</x:v>
-      </x:c>
       <x:c r="C161" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E161" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G161" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="B162" s="0" t="s">
-        <x:v>341</x:v>
-      </x:c>
       <x:c r="C162" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E162" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G162" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
         <x:v>342</x:v>
       </x:c>
-      <x:c r="B163" s="0" t="s">
-        <x:v>343</x:v>
-      </x:c>
       <x:c r="C163" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E163" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G163" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:9">
       <x:c r="A164" s="0" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="B164" s="0" t="s">
-        <x:v>345</x:v>
-      </x:c>
       <x:c r="C164" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E164" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G164" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="B165" s="0" t="s">
-        <x:v>347</x:v>
-      </x:c>
       <x:c r="C165" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E165" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G165" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="B166" s="0" t="s">
-        <x:v>349</x:v>
-      </x:c>
       <x:c r="C166" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E166" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G166" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="B167" s="0" t="s">
-        <x:v>351</x:v>
-      </x:c>
       <x:c r="C167" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E167" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G167" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:9">
       <x:c r="A168" s="0" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="B168" s="0" t="s">
-        <x:v>353</x:v>
-      </x:c>
       <x:c r="C168" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E168" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G168" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:9">
       <x:c r="A169" s="0" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="B169" s="0" t="s">
-        <x:v>355</x:v>
-      </x:c>
       <x:c r="C169" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E169" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G169" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:9">
       <x:c r="A170" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
         <x:v>356</x:v>
       </x:c>
-      <x:c r="B170" s="0" t="s">
-        <x:v>357</x:v>
-      </x:c>
       <x:c r="C170" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E170" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F170" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G170" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:9">
       <x:c r="A171" s="0" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
         <x:v>358</x:v>
       </x:c>
-      <x:c r="B171" s="0" t="s">
-        <x:v>359</x:v>
-      </x:c>
       <x:c r="C171" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E171" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F171" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G171" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:9">
       <x:c r="A172" s="0" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="B172" s="0" t="s">
-        <x:v>361</x:v>
-      </x:c>
       <x:c r="C172" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E172" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F172" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G172" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:9">
       <x:c r="A173" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="B173" s="0" t="s">
-        <x:v>363</x:v>
-      </x:c>
       <x:c r="C173" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E173" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F173" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G173" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:9">
       <x:c r="A174" s="0" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="B174" s="0" t="s">
         <x:v>364</x:v>
       </x:c>
-      <x:c r="B174" s="0" t="s">
-        <x:v>365</x:v>
-      </x:c>
       <x:c r="C174" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E174" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F174" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G174" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:9">
       <x:c r="A175" s="0" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="B175" s="0" t="s">
-        <x:v>367</x:v>
-      </x:c>
       <x:c r="C175" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E175" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F175" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G175" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:9">
       <x:c r="A176" s="0" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
         <x:v>368</x:v>
       </x:c>
-      <x:c r="B176" s="0" t="s">
-        <x:v>369</x:v>
-      </x:c>
       <x:c r="C176" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E176" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F176" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G176" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:9">
       <x:c r="A177" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="B177" s="0" t="s">
         <x:v>370</x:v>
       </x:c>
-      <x:c r="B177" s="0" t="s">
-        <x:v>371</x:v>
-      </x:c>
       <x:c r="C177" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E177" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F177" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G177" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:9">
       <x:c r="A178" s="0" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="B178" s="0" t="s">
-        <x:v>373</x:v>
-      </x:c>
       <x:c r="C178" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E178" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F178" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G178" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:9">
       <x:c r="A179" s="0" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="B179" s="0" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="B179" s="0" t="s">
-        <x:v>375</x:v>
-      </x:c>
       <x:c r="C179" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E179" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F179" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G179" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:9">
       <x:c r="A180" s="0" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="B180" s="0" t="s">
         <x:v>376</x:v>
       </x:c>
-      <x:c r="B180" s="0" t="s">
-        <x:v>377</x:v>
-      </x:c>
       <x:c r="C180" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E180" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F180" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G180" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:9">
       <x:c r="A181" s="0" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="B181" s="0" t="s">
         <x:v>378</x:v>
       </x:c>
-      <x:c r="B181" s="0" t="s">
-        <x:v>379</x:v>
-      </x:c>
       <x:c r="C181" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E181" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F181" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G181" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:9">
       <x:c r="A182" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="B182" s="0" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="B182" s="0" t="s">
-        <x:v>381</x:v>
-      </x:c>
       <x:c r="C182" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E182" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F182" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G182" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:9">
       <x:c r="A183" s="0" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="B183" s="0" t="s">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="B183" s="0" t="s">
-        <x:v>383</x:v>
-      </x:c>
       <x:c r="C183" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E183" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F183" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G183" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:9">
       <x:c r="A184" s="0" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
         <x:v>384</x:v>
       </x:c>
-      <x:c r="B184" s="0" t="s">
-        <x:v>385</x:v>
-      </x:c>
       <x:c r="C184" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E184" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F184" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G184" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:9">
       <x:c r="A185" s="0" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="B185" s="0" t="s">
         <x:v>386</x:v>
       </x:c>
-      <x:c r="B185" s="0" t="s">
-        <x:v>387</x:v>
-      </x:c>
       <x:c r="C185" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E185" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F185" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G185" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:9">
       <x:c r="A186" s="0" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="B186" s="0" t="s">
         <x:v>388</x:v>
       </x:c>
-      <x:c r="B186" s="0" t="s">
-        <x:v>389</x:v>
-      </x:c>
       <x:c r="C186" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E186" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F186" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G186" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:9">
       <x:c r="A187" s="0" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="B187" s="0" t="s">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="B187" s="0" t="s">
-        <x:v>391</x:v>
-      </x:c>
       <x:c r="C187" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E187" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F187" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G187" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:9">
       <x:c r="A188" s="0" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B188" s="0" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="B188" s="0" t="s">
-        <x:v>393</x:v>
-      </x:c>
       <x:c r="C188" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E188" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F188" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G188" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:9">
       <x:c r="A189" s="0" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="B189" s="0" t="s">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="B189" s="0" t="s">
-        <x:v>395</x:v>
-      </x:c>
       <x:c r="C189" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E189" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F189" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G189" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:9">
       <x:c r="A190" s="0" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="B190" s="0" t="s">
-        <x:v>397</x:v>
-      </x:c>
       <x:c r="C190" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D190" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E190" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F190" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G190" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:9">
       <x:c r="A191" s="0" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="B191" s="0" t="s">
         <x:v>398</x:v>
       </x:c>
-      <x:c r="B191" s="0" t="s">
-        <x:v>399</x:v>
-      </x:c>
       <x:c r="C191" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D191" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E191" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F191" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G191" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:9">
       <x:c r="A192" s="0" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="B192" s="0" t="s">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="B192" s="0" t="s">
-        <x:v>401</x:v>
-      </x:c>
       <x:c r="C192" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D192" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E192" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F192" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G192" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:9">
       <x:c r="A193" s="0" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
         <x:v>402</x:v>
       </x:c>
-      <x:c r="B193" s="0" t="s">
-        <x:v>403</x:v>
-      </x:c>
       <x:c r="C193" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D193" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E193" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F193" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G193" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:9">
       <x:c r="A194" s="0" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="B194" s="0" t="s">
         <x:v>404</x:v>
       </x:c>
-      <x:c r="B194" s="0" t="s">
-        <x:v>405</x:v>
-      </x:c>
       <x:c r="C194" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D194" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E194" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F194" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G194" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:9">
       <x:c r="A195" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="B195" s="0" t="s">
         <x:v>406</x:v>
       </x:c>
-      <x:c r="B195" s="0" t="s">
-        <x:v>407</x:v>
-      </x:c>
       <x:c r="C195" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D195" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E195" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F195" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G195" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:9">
       <x:c r="A196" s="0" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
         <x:v>408</x:v>
       </x:c>
-      <x:c r="B196" s="0" t="s">
-        <x:v>409</x:v>
-      </x:c>
       <x:c r="C196" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D196" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E196" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F196" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G196" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:9">
       <x:c r="A197" s="0" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="B197" s="0" t="s">
         <x:v>410</x:v>
       </x:c>
-      <x:c r="B197" s="0" t="s">
-        <x:v>411</x:v>
-      </x:c>
       <x:c r="C197" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D197" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E197" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F197" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G197" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:9">
       <x:c r="A198" s="0" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="B198" s="0" t="s">
         <x:v>412</x:v>
       </x:c>
-      <x:c r="B198" s="0" t="s">
-        <x:v>413</x:v>
-      </x:c>
       <x:c r="C198" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D198" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E198" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F198" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G198" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:9">
       <x:c r="A199" s="0" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B199" s="0" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="B199" s="0" t="s">
-        <x:v>415</x:v>
-      </x:c>
       <x:c r="C199" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D199" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E199" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F199" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G199" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:9">
       <x:c r="A200" s="0" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="B200" s="0" t="s">
         <x:v>416</x:v>
       </x:c>
-      <x:c r="B200" s="0" t="s">
-        <x:v>417</x:v>
-      </x:c>
       <x:c r="C200" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D200" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E200" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F200" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G200" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:9">
       <x:c r="A201" s="0" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="B201" s="0" t="s">
         <x:v>418</x:v>
       </x:c>
-      <x:c r="B201" s="0" t="s">
-        <x:v>419</x:v>
-      </x:c>
       <x:c r="C201" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E201" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F201" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G201" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:9">
       <x:c r="A202" s="0" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="B202" s="0" t="s">
         <x:v>420</x:v>
       </x:c>
-      <x:c r="B202" s="0" t="s">
-        <x:v>421</x:v>
-      </x:c>
       <x:c r="C202" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D202" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E202" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F202" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G202" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:9">
       <x:c r="A203" s="0" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="B203" s="0" t="s">
         <x:v>422</x:v>
       </x:c>
-      <x:c r="B203" s="0" t="s">
-        <x:v>423</x:v>
-      </x:c>
       <x:c r="C203" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E203" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F203" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G203" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:9">
       <x:c r="A204" s="0" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="B204" s="0" t="s">
         <x:v>424</x:v>
       </x:c>
-      <x:c r="B204" s="0" t="s">
-        <x:v>425</x:v>
-      </x:c>
       <x:c r="C204" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D204" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E204" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F204" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G204" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:9">
       <x:c r="A205" s="0" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="B205" s="0" t="s">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="B205" s="0" t="s">
-        <x:v>427</x:v>
-      </x:c>
       <x:c r="C205" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D205" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E205" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F205" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G205" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="206" spans="1:9">
       <x:c r="A206" s="0" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="B206" s="0" t="s">
         <x:v>428</x:v>
       </x:c>
-      <x:c r="B206" s="0" t="s">
-        <x:v>429</x:v>
-      </x:c>
       <x:c r="C206" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D206" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E206" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F206" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G206" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:9">
       <x:c r="A207" s="0" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="B207" s="0" t="s">
         <x:v>430</x:v>
       </x:c>
-      <x:c r="B207" s="0" t="s">
-        <x:v>431</x:v>
-      </x:c>
       <x:c r="C207" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D207" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E207" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F207" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G207" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:9">
       <x:c r="A208" s="0" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="B208" s="0" t="s">
         <x:v>432</x:v>
       </x:c>
-      <x:c r="B208" s="0" t="s">
-        <x:v>433</x:v>
-      </x:c>
       <x:c r="C208" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D208" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E208" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F208" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G208" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:9">
       <x:c r="A209" s="0" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B209" s="0" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="B209" s="0" t="s">
-        <x:v>435</x:v>
-      </x:c>
       <x:c r="C209" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D209" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E209" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F209" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G209" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:9">
       <x:c r="A210" s="0" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="B210" s="0" t="s">
         <x:v>436</x:v>
       </x:c>
-      <x:c r="B210" s="0" t="s">
-        <x:v>437</x:v>
-      </x:c>
       <x:c r="C210" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D210" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E210" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F210" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G210" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="211" spans="1:9">
       <x:c r="A211" s="0" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="B211" s="0" t="s">
         <x:v>438</x:v>
       </x:c>
-      <x:c r="B211" s="0" t="s">
-        <x:v>439</x:v>
-      </x:c>
       <x:c r="C211" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D211" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E211" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F211" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G211" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="212" spans="1:9">
       <x:c r="A212" s="0" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="B212" s="0" t="s">
         <x:v>440</x:v>
       </x:c>
-      <x:c r="B212" s="0" t="s">
-        <x:v>441</x:v>
-      </x:c>
       <x:c r="C212" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D212" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E212" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F212" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G212" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="213" spans="1:9">
       <x:c r="A213" s="0" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="B213" s="0" t="s">
         <x:v>442</x:v>
       </x:c>
-      <x:c r="B213" s="0" t="s">
-        <x:v>443</x:v>
-      </x:c>
       <x:c r="C213" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D213" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E213" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F213" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G213" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:9">
       <x:c r="A214" s="0" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="B214" s="0" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="B214" s="0" t="s">
-        <x:v>445</x:v>
-      </x:c>
       <x:c r="C214" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D214" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E214" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F214" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G214" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:9">
       <x:c r="A215" s="0" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="B215" s="0" t="s">
         <x:v>446</x:v>
       </x:c>
-      <x:c r="B215" s="0" t="s">
-        <x:v>447</x:v>
-      </x:c>
       <x:c r="C215" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D215" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E215" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F215" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G215" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:9">
       <x:c r="A216" s="0" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="B216" s="0" t="s">
         <x:v>448</x:v>
       </x:c>
-      <x:c r="B216" s="0" t="s">
-        <x:v>449</x:v>
-      </x:c>
       <x:c r="C216" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E216" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F216" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G216" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="217" spans="1:9">
       <x:c r="A217" s="0" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="B217" s="0" t="s">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="B217" s="0" t="s">
-        <x:v>451</x:v>
-      </x:c>
       <x:c r="C217" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E217" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F217" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G217" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:9">
       <x:c r="A218" s="0" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="B218" s="0" t="s">
         <x:v>452</x:v>
       </x:c>
-      <x:c r="B218" s="0" t="s">
-        <x:v>453</x:v>
-      </x:c>
       <x:c r="C218" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E218" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F218" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G218" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:9">
       <x:c r="A219" s="0" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="B219" s="0" t="s">
         <x:v>454</x:v>
       </x:c>
-      <x:c r="B219" s="0" t="s">
-        <x:v>455</x:v>
-      </x:c>
       <x:c r="C219" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E219" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F219" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G219" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="220" spans="1:9">
       <x:c r="A220" s="0" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="B220" s="0" t="s">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="B220" s="0" t="s">
-        <x:v>457</x:v>
-      </x:c>
       <x:c r="C220" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D220" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E220" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F220" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G220" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="221" spans="1:9">
       <x:c r="A221" s="0" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="B221" s="0" t="s">
         <x:v>458</x:v>
       </x:c>
-      <x:c r="B221" s="0" t="s">
-        <x:v>459</x:v>
-      </x:c>
       <x:c r="C221" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D221" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E221" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F221" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G221" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="222" spans="1:9">
       <x:c r="A222" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="B222" s="0" t="s">
         <x:v>460</x:v>
       </x:c>
-      <x:c r="B222" s="0" t="s">
-        <x:v>461</x:v>
-      </x:c>
       <x:c r="C222" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D222" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E222" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F222" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G222" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:9">
       <x:c r="A223" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="B223" s="0" t="s">
         <x:v>462</x:v>
       </x:c>
-      <x:c r="B223" s="0" t="s">
-        <x:v>463</x:v>
-      </x:c>
       <x:c r="C223" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D223" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E223" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F223" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G223" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="224" spans="1:9">
       <x:c r="A224" s="0" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="B224" s="0" t="s">
         <x:v>464</x:v>
       </x:c>
-      <x:c r="B224" s="0" t="s">
-        <x:v>465</x:v>
-      </x:c>
       <x:c r="C224" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D224" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E224" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F224" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G224" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:9">
       <x:c r="A225" s="0" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B225" s="0" t="s">
         <x:v>466</x:v>
       </x:c>
-      <x:c r="B225" s="0" t="s">
-        <x:v>467</x:v>
-      </x:c>
       <x:c r="C225" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D225" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E225" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F225" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G225" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="226" spans="1:9">
       <x:c r="A226" s="0" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="B226" s="0" t="s">
         <x:v>468</x:v>
       </x:c>
-      <x:c r="B226" s="0" t="s">
-        <x:v>469</x:v>
-      </x:c>
       <x:c r="C226" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D226" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E226" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F226" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G226" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:9">
       <x:c r="A227" s="0" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="B227" s="0" t="s">
         <x:v>470</x:v>
       </x:c>
-      <x:c r="B227" s="0" t="s">
-        <x:v>471</x:v>
-      </x:c>
       <x:c r="C227" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E227" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F227" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G227" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:09:48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08-12-2025 12:12:39</x:t>
+    <x:t>08-12-2025 12:50:46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 12:53:26</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -61,7 +61,7 @@
     <x:t>anlpvhe187047</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:12:40</x:t>
+    <x:t>08-12-2025 12:53:39</x:t>
   </x:si>
   <x:si>
     <x:t>3</x:t>
@@ -70,7 +70,7 @@
     <x:t>cuongnvhe181200</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:12:36</x:t>
+    <x:t>08-12-2025 12:53:35</x:t>
   </x:si>
   <x:si>
     <x:t>4</x:t>
@@ -79,7 +79,7 @@
     <x:t>ducnthe180869</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:10:52</x:t>
+    <x:t>08-12-2025 12:51:50</x:t>
   </x:si>
   <x:si>
     <x:t>5</x:t>
@@ -88,7 +88,7 @@
     <x:t>dungdvhe181404</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:12:37</x:t>
+    <x:t>08-12-2025 12:53:40</x:t>
   </x:si>
   <x:si>
     <x:t>6</x:t>
@@ -97,15 +97,18 @@
     <x:t>dungtdhe186461</x:t>
   </x:si>
   <x:si>
+    <x:t>Not Run</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
     <x:t>7</x:t>
   </x:si>
   <x:si>
     <x:t>duongnthe186310</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:12:26</x:t>
-  </x:si>
-  <x:si>
     <x:t>8</x:t>
   </x:si>
   <x:si>
@@ -118,27 +121,21 @@
     <x:t>duyldhe176352</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:12:48</x:t>
-  </x:si>
-  <x:si>
     <x:t>10</x:t>
   </x:si>
   <x:si>
     <x:t>duynthe180374</x:t>
   </x:si>
   <x:si>
+    <x:t>08-12-2025 12:53:38</x:t>
+  </x:si>
+  <x:si>
     <x:t>11</x:t>
   </x:si>
   <x:si>
     <x:t>GiangPTHE171781</x:t>
   </x:si>
   <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
     <x:t>12</x:t>
   </x:si>
   <x:si>
@@ -1429,10 +1426,10 @@
     <x:t>vietddhe161942</x:t>
   </x:si>
   <x:si>
-    <x:t>2025-12-08 12:12:48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.17s</x:t>
+    <x:t>14.31s</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2025-12-08 12:53:40</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1875,7 +1872,7 @@
         <x:v>471</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>472</x:v>
+        <x:v>470</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -1971,34 +1968,34 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
-      <x:c r="A7" s="2" t="s">
+      <x:c r="A7" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B7" s="2" t="s">
+      <x:c r="B7" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C7" s="2" t="s">
+      <x:c r="C7" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D7" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E7" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F7" s="2" t="s">
+      <x:c r="D7" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G7" s="2" t="s">
-        <x:v>18</x:v>
+      <x:c r="G7" s="0" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
       <x:c r="A8" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B8" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C8" s="2" t="s">
         <x:v>7</x:v>
@@ -2013,15 +2010,15 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G8" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
       <x:c r="A9" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="2" t="s">
         <x:v>7</x:v>
@@ -2036,15 +2033,15 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G9" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
         <x:v>7</x:v>
@@ -2059,7 +2056,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G10" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -2082,4975 +2079,4975 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="G11" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
         <x:v>41</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>44</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>58</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>66</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>70</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>74</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>76</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>84</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>86</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>88</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>90</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
         <x:v>91</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>92</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>94</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
         <x:v>95</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>96</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>100</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>102</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
         <x:v>103</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>104</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>106</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
         <x:v>109</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>110</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>112</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>114</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
         <x:v>115</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>116</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>118</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>120</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
         <x:v>121</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>122</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>124</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>126</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
         <x:v>127</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>128</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G56" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
         <x:v>129</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>130</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G57" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>132</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G58" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
         <x:v>133</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>134</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G59" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>136</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G60" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
         <x:v>137</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>138</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G61" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
         <x:v>139</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>140</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G62" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
         <x:v>141</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>142</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G63" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>144</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G64" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
         <x:v>145</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>146</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G65" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
         <x:v>147</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>148</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G66" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
         <x:v>149</x:v>
-      </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>150</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G67" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
         <x:v>151</x:v>
-      </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>152</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G68" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
         <x:v>153</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>154</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G69" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>156</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G70" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
         <x:v>157</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>158</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G71" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
         <x:v>159</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>160</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G72" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
         <x:v>161</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>162</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G73" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
         <x:v>163</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>164</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G74" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
         <x:v>165</x:v>
-      </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>166</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G75" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
         <x:v>167</x:v>
-      </x:c>
-      <x:c r="B76" s="0" t="s">
-        <x:v>168</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G76" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
         <x:v>169</x:v>
-      </x:c>
-      <x:c r="B77" s="0" t="s">
-        <x:v>170</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G77" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
         <x:v>171</x:v>
-      </x:c>
-      <x:c r="B78" s="0" t="s">
-        <x:v>172</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G78" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
         <x:v>173</x:v>
-      </x:c>
-      <x:c r="B79" s="0" t="s">
-        <x:v>174</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G79" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
         <x:v>175</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>176</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G80" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
         <x:v>177</x:v>
-      </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>178</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G81" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
         <x:v>179</x:v>
-      </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>180</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G82" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
         <x:v>181</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>182</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G83" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
         <x:v>183</x:v>
-      </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>184</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G84" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
         <x:v>185</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>186</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G85" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
         <x:v>187</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>188</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G86" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
         <x:v>189</x:v>
-      </x:c>
-      <x:c r="B87" s="0" t="s">
-        <x:v>190</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G87" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
         <x:v>191</x:v>
-      </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>192</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G88" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
         <x:v>193</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>194</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G89" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
         <x:v>195</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>196</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G90" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
         <x:v>197</x:v>
-      </x:c>
-      <x:c r="B91" s="0" t="s">
-        <x:v>198</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G91" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
         <x:v>199</x:v>
-      </x:c>
-      <x:c r="B92" s="0" t="s">
-        <x:v>200</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G92" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
         <x:v>201</x:v>
-      </x:c>
-      <x:c r="B93" s="0" t="s">
-        <x:v>202</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G93" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
         <x:v>203</x:v>
-      </x:c>
-      <x:c r="B94" s="0" t="s">
-        <x:v>204</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G94" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
         <x:v>205</x:v>
-      </x:c>
-      <x:c r="B95" s="0" t="s">
-        <x:v>206</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G95" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
         <x:v>207</x:v>
-      </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>208</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G96" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
         <x:v>209</x:v>
-      </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>210</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G97" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
         <x:v>211</x:v>
-      </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>212</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G98" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
         <x:v>213</x:v>
-      </x:c>
-      <x:c r="B99" s="0" t="s">
-        <x:v>214</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G99" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
         <x:v>215</x:v>
-      </x:c>
-      <x:c r="B100" s="0" t="s">
-        <x:v>216</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G100" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
         <x:v>217</x:v>
-      </x:c>
-      <x:c r="B101" s="0" t="s">
-        <x:v>218</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G101" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
         <x:v>219</x:v>
-      </x:c>
-      <x:c r="B102" s="0" t="s">
-        <x:v>220</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G102" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
         <x:v>221</x:v>
-      </x:c>
-      <x:c r="B103" s="0" t="s">
-        <x:v>222</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G103" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
         <x:v>223</x:v>
-      </x:c>
-      <x:c r="B104" s="0" t="s">
-        <x:v>224</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G104" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
         <x:v>225</x:v>
-      </x:c>
-      <x:c r="B105" s="0" t="s">
-        <x:v>226</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G105" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
         <x:v>227</x:v>
-      </x:c>
-      <x:c r="B106" s="0" t="s">
-        <x:v>228</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G106" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
         <x:v>229</x:v>
-      </x:c>
-      <x:c r="B107" s="0" t="s">
-        <x:v>230</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G107" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
         <x:v>231</x:v>
-      </x:c>
-      <x:c r="B108" s="0" t="s">
-        <x:v>232</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G108" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
         <x:v>233</x:v>
-      </x:c>
-      <x:c r="B109" s="0" t="s">
-        <x:v>234</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G109" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
         <x:v>235</x:v>
-      </x:c>
-      <x:c r="B110" s="0" t="s">
-        <x:v>236</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G110" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
         <x:v>237</x:v>
-      </x:c>
-      <x:c r="B111" s="0" t="s">
-        <x:v>238</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G111" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
         <x:v>239</x:v>
-      </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>240</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G112" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
         <x:v>241</x:v>
-      </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>242</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G113" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
         <x:v>243</x:v>
-      </x:c>
-      <x:c r="B114" s="0" t="s">
-        <x:v>244</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G114" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="B115" s="0" t="s">
-        <x:v>246</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G115" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
         <x:v>247</x:v>
-      </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>248</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G116" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
         <x:v>249</x:v>
-      </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>250</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G117" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
         <x:v>251</x:v>
-      </x:c>
-      <x:c r="B118" s="0" t="s">
-        <x:v>252</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G118" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
         <x:v>253</x:v>
-      </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>254</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G119" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
         <x:v>255</x:v>
-      </x:c>
-      <x:c r="B120" s="0" t="s">
-        <x:v>256</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G120" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
         <x:v>257</x:v>
-      </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>258</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G121" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
         <x:v>259</x:v>
-      </x:c>
-      <x:c r="B122" s="0" t="s">
-        <x:v>260</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G122" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
         <x:v>261</x:v>
-      </x:c>
-      <x:c r="B123" s="0" t="s">
-        <x:v>262</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G123" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
         <x:v>263</x:v>
-      </x:c>
-      <x:c r="B124" s="0" t="s">
-        <x:v>264</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G124" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
         <x:v>265</x:v>
-      </x:c>
-      <x:c r="B125" s="0" t="s">
-        <x:v>266</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G125" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
         <x:v>267</x:v>
-      </x:c>
-      <x:c r="B126" s="0" t="s">
-        <x:v>268</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G126" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
         <x:v>269</x:v>
-      </x:c>
-      <x:c r="B127" s="0" t="s">
-        <x:v>270</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G127" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
         <x:v>271</x:v>
-      </x:c>
-      <x:c r="B128" s="0" t="s">
-        <x:v>272</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G128" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
         <x:v>273</x:v>
-      </x:c>
-      <x:c r="B129" s="0" t="s">
-        <x:v>274</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G129" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
         <x:v>275</x:v>
-      </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>276</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G130" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
         <x:v>277</x:v>
-      </x:c>
-      <x:c r="B131" s="0" t="s">
-        <x:v>278</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G131" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
         <x:v>279</x:v>
-      </x:c>
-      <x:c r="B132" s="0" t="s">
-        <x:v>280</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G132" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
         <x:v>281</x:v>
-      </x:c>
-      <x:c r="B133" s="0" t="s">
-        <x:v>282</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G133" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
         <x:v>283</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>284</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G134" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
         <x:v>285</x:v>
-      </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>286</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G135" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
         <x:v>287</x:v>
-      </x:c>
-      <x:c r="B136" s="0" t="s">
-        <x:v>288</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G136" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
         <x:v>289</x:v>
-      </x:c>
-      <x:c r="B137" s="0" t="s">
-        <x:v>290</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G137" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
         <x:v>291</x:v>
-      </x:c>
-      <x:c r="B138" s="0" t="s">
-        <x:v>292</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G138" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
         <x:v>293</x:v>
-      </x:c>
-      <x:c r="B139" s="0" t="s">
-        <x:v>294</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G139" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
         <x:v>295</x:v>
-      </x:c>
-      <x:c r="B140" s="0" t="s">
-        <x:v>296</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G140" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
         <x:v>297</x:v>
-      </x:c>
-      <x:c r="B141" s="0" t="s">
-        <x:v>298</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G141" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
         <x:v>299</x:v>
-      </x:c>
-      <x:c r="B142" s="0" t="s">
-        <x:v>300</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G142" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
         <x:v>301</x:v>
-      </x:c>
-      <x:c r="B143" s="0" t="s">
-        <x:v>302</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G143" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
         <x:v>303</x:v>
-      </x:c>
-      <x:c r="B144" s="0" t="s">
-        <x:v>304</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G144" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
         <x:v>305</x:v>
-      </x:c>
-      <x:c r="B145" s="0" t="s">
-        <x:v>306</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G145" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
         <x:v>307</x:v>
-      </x:c>
-      <x:c r="B146" s="0" t="s">
-        <x:v>308</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G146" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
         <x:v>309</x:v>
-      </x:c>
-      <x:c r="B147" s="0" t="s">
-        <x:v>310</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G147" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
         <x:v>311</x:v>
-      </x:c>
-      <x:c r="B148" s="0" t="s">
-        <x:v>312</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G148" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
         <x:v>313</x:v>
-      </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>314</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G149" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
         <x:v>315</x:v>
-      </x:c>
-      <x:c r="B150" s="0" t="s">
-        <x:v>316</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G150" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
         <x:v>317</x:v>
-      </x:c>
-      <x:c r="B151" s="0" t="s">
-        <x:v>318</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G151" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
         <x:v>319</x:v>
-      </x:c>
-      <x:c r="B152" s="0" t="s">
-        <x:v>320</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G152" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
         <x:v>321</x:v>
-      </x:c>
-      <x:c r="B153" s="0" t="s">
-        <x:v>322</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G153" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
         <x:v>323</x:v>
-      </x:c>
-      <x:c r="B154" s="0" t="s">
-        <x:v>324</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G154" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:9">
       <x:c r="A155" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
         <x:v>325</x:v>
-      </x:c>
-      <x:c r="B155" s="0" t="s">
-        <x:v>326</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G155" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:9">
       <x:c r="A156" s="0" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
         <x:v>327</x:v>
-      </x:c>
-      <x:c r="B156" s="0" t="s">
-        <x:v>328</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G156" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:9">
       <x:c r="A157" s="0" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
         <x:v>329</x:v>
-      </x:c>
-      <x:c r="B157" s="0" t="s">
-        <x:v>330</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G157" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:9">
       <x:c r="A158" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
         <x:v>331</x:v>
-      </x:c>
-      <x:c r="B158" s="0" t="s">
-        <x:v>332</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G158" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:9">
       <x:c r="A159" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
         <x:v>333</x:v>
-      </x:c>
-      <x:c r="B159" s="0" t="s">
-        <x:v>334</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G159" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:9">
       <x:c r="A160" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
         <x:v>335</x:v>
-      </x:c>
-      <x:c r="B160" s="0" t="s">
-        <x:v>336</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G160" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
         <x:v>337</x:v>
-      </x:c>
-      <x:c r="B161" s="0" t="s">
-        <x:v>338</x:v>
       </x:c>
       <x:c r="C161" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E161" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G161" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
         <x:v>339</x:v>
-      </x:c>
-      <x:c r="B162" s="0" t="s">
-        <x:v>340</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E162" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G162" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
         <x:v>341</x:v>
-      </x:c>
-      <x:c r="B163" s="0" t="s">
-        <x:v>342</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E163" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G163" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:9">
       <x:c r="A164" s="0" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
         <x:v>343</x:v>
-      </x:c>
-      <x:c r="B164" s="0" t="s">
-        <x:v>344</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E164" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G164" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
         <x:v>345</x:v>
-      </x:c>
-      <x:c r="B165" s="0" t="s">
-        <x:v>346</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E165" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G165" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
         <x:v>347</x:v>
-      </x:c>
-      <x:c r="B166" s="0" t="s">
-        <x:v>348</x:v>
       </x:c>
       <x:c r="C166" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E166" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G166" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
         <x:v>349</x:v>
-      </x:c>
-      <x:c r="B167" s="0" t="s">
-        <x:v>350</x:v>
       </x:c>
       <x:c r="C167" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E167" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G167" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:9">
       <x:c r="A168" s="0" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="B168" s="0" t="s">
-        <x:v>352</x:v>
-      </x:c>
       <x:c r="C168" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E168" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G168" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:9">
       <x:c r="A169" s="0" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="B169" s="0" t="s">
-        <x:v>354</x:v>
-      </x:c>
       <x:c r="C169" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E169" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G169" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:9">
       <x:c r="A170" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
         <x:v>355</x:v>
       </x:c>
-      <x:c r="B170" s="0" t="s">
-        <x:v>356</x:v>
-      </x:c>
       <x:c r="C170" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E170" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F170" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G170" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:9">
       <x:c r="A171" s="0" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
         <x:v>357</x:v>
       </x:c>
-      <x:c r="B171" s="0" t="s">
-        <x:v>358</x:v>
-      </x:c>
       <x:c r="C171" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E171" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F171" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G171" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:9">
       <x:c r="A172" s="0" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="B172" s="0" t="s">
-        <x:v>360</x:v>
-      </x:c>
       <x:c r="C172" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E172" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F172" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G172" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:9">
       <x:c r="A173" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
         <x:v>361</x:v>
       </x:c>
-      <x:c r="B173" s="0" t="s">
-        <x:v>362</x:v>
-      </x:c>
       <x:c r="C173" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E173" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F173" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G173" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:9">
       <x:c r="A174" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="B174" s="0" t="s">
         <x:v>363</x:v>
       </x:c>
-      <x:c r="B174" s="0" t="s">
-        <x:v>364</x:v>
-      </x:c>
       <x:c r="C174" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E174" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F174" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G174" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:9">
       <x:c r="A175" s="0" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="B175" s="0" t="s">
-        <x:v>366</x:v>
-      </x:c>
       <x:c r="C175" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E175" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F175" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G175" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:9">
       <x:c r="A176" s="0" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
         <x:v>367</x:v>
       </x:c>
-      <x:c r="B176" s="0" t="s">
-        <x:v>368</x:v>
-      </x:c>
       <x:c r="C176" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E176" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F176" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G176" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:9">
       <x:c r="A177" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="B177" s="0" t="s">
         <x:v>369</x:v>
       </x:c>
-      <x:c r="B177" s="0" t="s">
-        <x:v>370</x:v>
-      </x:c>
       <x:c r="C177" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E177" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F177" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G177" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:9">
       <x:c r="A178" s="0" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="B178" s="0" t="s">
-        <x:v>372</x:v>
-      </x:c>
       <x:c r="C178" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E178" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F178" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G178" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:9">
       <x:c r="A179" s="0" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="B179" s="0" t="s">
         <x:v>373</x:v>
       </x:c>
-      <x:c r="B179" s="0" t="s">
-        <x:v>374</x:v>
-      </x:c>
       <x:c r="C179" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E179" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F179" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G179" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:9">
       <x:c r="A180" s="0" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="B180" s="0" t="s">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="B180" s="0" t="s">
-        <x:v>376</x:v>
-      </x:c>
       <x:c r="C180" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E180" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F180" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G180" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:9">
       <x:c r="A181" s="0" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="B181" s="0" t="s">
         <x:v>377</x:v>
       </x:c>
-      <x:c r="B181" s="0" t="s">
-        <x:v>378</x:v>
-      </x:c>
       <x:c r="C181" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E181" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F181" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G181" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:9">
       <x:c r="A182" s="0" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="B182" s="0" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="B182" s="0" t="s">
-        <x:v>380</x:v>
-      </x:c>
       <x:c r="C182" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E182" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F182" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G182" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:9">
       <x:c r="A183" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="B183" s="0" t="s">
         <x:v>381</x:v>
       </x:c>
-      <x:c r="B183" s="0" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="C183" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E183" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F183" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G183" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:9">
       <x:c r="A184" s="0" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
         <x:v>383</x:v>
       </x:c>
-      <x:c r="B184" s="0" t="s">
-        <x:v>384</x:v>
-      </x:c>
       <x:c r="C184" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E184" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F184" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G184" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:9">
       <x:c r="A185" s="0" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="B185" s="0" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="B185" s="0" t="s">
-        <x:v>386</x:v>
-      </x:c>
       <x:c r="C185" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E185" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F185" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G185" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:9">
       <x:c r="A186" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B186" s="0" t="s">
         <x:v>387</x:v>
       </x:c>
-      <x:c r="B186" s="0" t="s">
-        <x:v>388</x:v>
-      </x:c>
       <x:c r="C186" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E186" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F186" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G186" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:9">
       <x:c r="A187" s="0" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B187" s="0" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="B187" s="0" t="s">
-        <x:v>390</x:v>
-      </x:c>
       <x:c r="C187" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E187" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F187" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G187" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:9">
       <x:c r="A188" s="0" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="B188" s="0" t="s">
         <x:v>391</x:v>
       </x:c>
-      <x:c r="B188" s="0" t="s">
-        <x:v>392</x:v>
-      </x:c>
       <x:c r="C188" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E188" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F188" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G188" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:9">
       <x:c r="A189" s="0" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="B189" s="0" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="B189" s="0" t="s">
-        <x:v>394</x:v>
-      </x:c>
       <x:c r="C189" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E189" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F189" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G189" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:9">
       <x:c r="A190" s="0" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
         <x:v>395</x:v>
       </x:c>
-      <x:c r="B190" s="0" t="s">
-        <x:v>396</x:v>
-      </x:c>
       <x:c r="C190" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D190" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E190" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F190" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G190" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:9">
       <x:c r="A191" s="0" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="B191" s="0" t="s">
         <x:v>397</x:v>
       </x:c>
-      <x:c r="B191" s="0" t="s">
-        <x:v>398</x:v>
-      </x:c>
       <x:c r="C191" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D191" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E191" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F191" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G191" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:9">
       <x:c r="A192" s="0" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="B192" s="0" t="s">
         <x:v>399</x:v>
       </x:c>
-      <x:c r="B192" s="0" t="s">
-        <x:v>400</x:v>
-      </x:c>
       <x:c r="C192" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D192" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E192" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F192" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G192" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:9">
       <x:c r="A193" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
         <x:v>401</x:v>
       </x:c>
-      <x:c r="B193" s="0" t="s">
-        <x:v>402</x:v>
-      </x:c>
       <x:c r="C193" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D193" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E193" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F193" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G193" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:9">
       <x:c r="A194" s="0" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="B194" s="0" t="s">
         <x:v>403</x:v>
       </x:c>
-      <x:c r="B194" s="0" t="s">
-        <x:v>404</x:v>
-      </x:c>
       <x:c r="C194" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D194" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E194" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F194" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G194" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:9">
       <x:c r="A195" s="0" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="B195" s="0" t="s">
         <x:v>405</x:v>
       </x:c>
-      <x:c r="B195" s="0" t="s">
-        <x:v>406</x:v>
-      </x:c>
       <x:c r="C195" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D195" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E195" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F195" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G195" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:9">
       <x:c r="A196" s="0" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
         <x:v>407</x:v>
       </x:c>
-      <x:c r="B196" s="0" t="s">
-        <x:v>408</x:v>
-      </x:c>
       <x:c r="C196" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D196" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E196" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F196" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G196" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:9">
       <x:c r="A197" s="0" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="B197" s="0" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="B197" s="0" t="s">
-        <x:v>410</x:v>
-      </x:c>
       <x:c r="C197" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D197" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E197" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F197" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G197" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:9">
       <x:c r="A198" s="0" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B198" s="0" t="s">
         <x:v>411</x:v>
       </x:c>
-      <x:c r="B198" s="0" t="s">
-        <x:v>412</x:v>
-      </x:c>
       <x:c r="C198" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D198" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E198" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F198" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G198" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:9">
       <x:c r="A199" s="0" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="B199" s="0" t="s">
         <x:v>413</x:v>
       </x:c>
-      <x:c r="B199" s="0" t="s">
-        <x:v>414</x:v>
-      </x:c>
       <x:c r="C199" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D199" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E199" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F199" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G199" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:9">
       <x:c r="A200" s="0" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="B200" s="0" t="s">
         <x:v>415</x:v>
       </x:c>
-      <x:c r="B200" s="0" t="s">
-        <x:v>416</x:v>
-      </x:c>
       <x:c r="C200" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D200" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E200" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F200" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G200" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:9">
       <x:c r="A201" s="0" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="B201" s="0" t="s">
         <x:v>417</x:v>
       </x:c>
-      <x:c r="B201" s="0" t="s">
-        <x:v>418</x:v>
-      </x:c>
       <x:c r="C201" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E201" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F201" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G201" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:9">
       <x:c r="A202" s="0" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="B202" s="0" t="s">
         <x:v>419</x:v>
       </x:c>
-      <x:c r="B202" s="0" t="s">
-        <x:v>420</x:v>
-      </x:c>
       <x:c r="C202" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D202" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E202" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F202" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G202" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:9">
       <x:c r="A203" s="0" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="B203" s="0" t="s">
         <x:v>421</x:v>
       </x:c>
-      <x:c r="B203" s="0" t="s">
-        <x:v>422</x:v>
-      </x:c>
       <x:c r="C203" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E203" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F203" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G203" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:9">
       <x:c r="A204" s="0" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="B204" s="0" t="s">
         <x:v>423</x:v>
       </x:c>
-      <x:c r="B204" s="0" t="s">
-        <x:v>424</x:v>
-      </x:c>
       <x:c r="C204" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D204" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E204" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F204" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G204" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:9">
       <x:c r="A205" s="0" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="B205" s="0" t="s">
         <x:v>425</x:v>
       </x:c>
-      <x:c r="B205" s="0" t="s">
-        <x:v>426</x:v>
-      </x:c>
       <x:c r="C205" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D205" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E205" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F205" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G205" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="206" spans="1:9">
       <x:c r="A206" s="0" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="B206" s="0" t="s">
         <x:v>427</x:v>
       </x:c>
-      <x:c r="B206" s="0" t="s">
-        <x:v>428</x:v>
-      </x:c>
       <x:c r="C206" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D206" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E206" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F206" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G206" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:9">
       <x:c r="A207" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="B207" s="0" t="s">
         <x:v>429</x:v>
       </x:c>
-      <x:c r="B207" s="0" t="s">
-        <x:v>430</x:v>
-      </x:c>
       <x:c r="C207" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D207" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E207" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F207" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G207" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:9">
       <x:c r="A208" s="0" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="B208" s="0" t="s">
         <x:v>431</x:v>
       </x:c>
-      <x:c r="B208" s="0" t="s">
-        <x:v>432</x:v>
-      </x:c>
       <x:c r="C208" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D208" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E208" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F208" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G208" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:9">
       <x:c r="A209" s="0" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="B209" s="0" t="s">
         <x:v>433</x:v>
       </x:c>
-      <x:c r="B209" s="0" t="s">
-        <x:v>434</x:v>
-      </x:c>
       <x:c r="C209" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D209" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E209" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F209" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G209" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:9">
       <x:c r="A210" s="0" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="B210" s="0" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="B210" s="0" t="s">
-        <x:v>436</x:v>
-      </x:c>
       <x:c r="C210" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D210" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E210" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F210" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G210" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="211" spans="1:9">
       <x:c r="A211" s="0" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="B211" s="0" t="s">
         <x:v>437</x:v>
       </x:c>
-      <x:c r="B211" s="0" t="s">
-        <x:v>438</x:v>
-      </x:c>
       <x:c r="C211" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D211" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E211" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F211" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G211" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="212" spans="1:9">
       <x:c r="A212" s="0" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="B212" s="0" t="s">
         <x:v>439</x:v>
       </x:c>
-      <x:c r="B212" s="0" t="s">
-        <x:v>440</x:v>
-      </x:c>
       <x:c r="C212" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D212" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E212" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F212" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G212" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="213" spans="1:9">
       <x:c r="A213" s="0" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="B213" s="0" t="s">
         <x:v>441</x:v>
       </x:c>
-      <x:c r="B213" s="0" t="s">
-        <x:v>442</x:v>
-      </x:c>
       <x:c r="C213" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D213" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E213" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F213" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G213" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:9">
       <x:c r="A214" s="0" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="B214" s="0" t="s">
         <x:v>443</x:v>
       </x:c>
-      <x:c r="B214" s="0" t="s">
-        <x:v>444</x:v>
-      </x:c>
       <x:c r="C214" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D214" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E214" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F214" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G214" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:9">
       <x:c r="A215" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="B215" s="0" t="s">
         <x:v>445</x:v>
       </x:c>
-      <x:c r="B215" s="0" t="s">
-        <x:v>446</x:v>
-      </x:c>
       <x:c r="C215" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D215" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E215" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F215" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G215" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:9">
       <x:c r="A216" s="0" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="B216" s="0" t="s">
         <x:v>447</x:v>
       </x:c>
-      <x:c r="B216" s="0" t="s">
-        <x:v>448</x:v>
-      </x:c>
       <x:c r="C216" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E216" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F216" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G216" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="217" spans="1:9">
       <x:c r="A217" s="0" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="B217" s="0" t="s">
         <x:v>449</x:v>
       </x:c>
-      <x:c r="B217" s="0" t="s">
-        <x:v>450</x:v>
-      </x:c>
       <x:c r="C217" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E217" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F217" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G217" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:9">
       <x:c r="A218" s="0" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="B218" s="0" t="s">
         <x:v>451</x:v>
       </x:c>
-      <x:c r="B218" s="0" t="s">
-        <x:v>452</x:v>
-      </x:c>
       <x:c r="C218" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E218" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F218" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G218" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:9">
       <x:c r="A219" s="0" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="B219" s="0" t="s">
         <x:v>453</x:v>
       </x:c>
-      <x:c r="B219" s="0" t="s">
-        <x:v>454</x:v>
-      </x:c>
       <x:c r="C219" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E219" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F219" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G219" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="220" spans="1:9">
       <x:c r="A220" s="0" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="B220" s="0" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="B220" s="0" t="s">
-        <x:v>456</x:v>
-      </x:c>
       <x:c r="C220" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D220" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E220" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F220" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G220" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="221" spans="1:9">
       <x:c r="A221" s="0" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="B221" s="0" t="s">
         <x:v>457</x:v>
       </x:c>
-      <x:c r="B221" s="0" t="s">
-        <x:v>458</x:v>
-      </x:c>
       <x:c r="C221" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D221" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E221" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F221" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G221" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="222" spans="1:9">
       <x:c r="A222" s="0" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="B222" s="0" t="s">
         <x:v>459</x:v>
       </x:c>
-      <x:c r="B222" s="0" t="s">
-        <x:v>460</x:v>
-      </x:c>
       <x:c r="C222" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D222" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E222" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F222" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G222" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:9">
       <x:c r="A223" s="0" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="B223" s="0" t="s">
         <x:v>461</x:v>
       </x:c>
-      <x:c r="B223" s="0" t="s">
-        <x:v>462</x:v>
-      </x:c>
       <x:c r="C223" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D223" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E223" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F223" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G223" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="224" spans="1:9">
       <x:c r="A224" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B224" s="0" t="s">
         <x:v>463</x:v>
       </x:c>
-      <x:c r="B224" s="0" t="s">
-        <x:v>464</x:v>
-      </x:c>
       <x:c r="C224" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D224" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E224" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F224" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G224" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:9">
       <x:c r="A225" s="0" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="B225" s="0" t="s">
         <x:v>465</x:v>
       </x:c>
-      <x:c r="B225" s="0" t="s">
-        <x:v>466</x:v>
-      </x:c>
       <x:c r="C225" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D225" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E225" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F225" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G225" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="226" spans="1:9">
       <x:c r="A226" s="0" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="B226" s="0" t="s">
         <x:v>467</x:v>
       </x:c>
-      <x:c r="B226" s="0" t="s">
-        <x:v>468</x:v>
-      </x:c>
       <x:c r="C226" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D226" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E226" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F226" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G226" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:9">
       <x:c r="A227" s="0" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B227" s="0" t="s">
         <x:v>469</x:v>
       </x:c>
-      <x:c r="B227" s="0" t="s">
-        <x:v>470</x:v>
-      </x:c>
       <x:c r="C227" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E227" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F227" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G227" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:50:46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08-12-2025 12:53:26</x:t>
+    <x:t>08-12-2025 13:30:56</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08-12-2025 13:32:39</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -61,7 +61,10 @@
     <x:t>anlpvhe187047</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:53:39</x:t>
+    <x:t>Not Run</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
   </x:si>
   <x:si>
     <x:t>3</x:t>
@@ -70,37 +73,25 @@
     <x:t>cuongnvhe181200</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:53:35</x:t>
-  </x:si>
-  <x:si>
     <x:t>4</x:t>
   </x:si>
   <x:si>
     <x:t>ducnthe180869</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:51:50</x:t>
-  </x:si>
-  <x:si>
     <x:t>5</x:t>
   </x:si>
   <x:si>
     <x:t>dungdvhe181404</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:53:40</x:t>
-  </x:si>
-  <x:si>
     <x:t>6</x:t>
   </x:si>
   <x:si>
     <x:t>dungtdhe186461</x:t>
   </x:si>
   <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
+    <x:t>08-12-2025 13:32:49</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>
@@ -127,9 +118,6 @@
     <x:t>duynthe180374</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 12:53:38</x:t>
-  </x:si>
-  <x:si>
     <x:t>11</x:t>
   </x:si>
   <x:si>
@@ -1426,10 +1414,10 @@
     <x:t>vietddhe161942</x:t>
   </x:si>
   <x:si>
-    <x:t>14.31s</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2025-12-08 12:53:40</x:t>
+    <x:t>2025-12-08 13:32:49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.48s</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1869,5185 +1857,5185 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>471</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>470</x:v>
+        <x:v>467</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="A3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
+      <x:c r="B3" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s">
+      <x:c r="C3" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D3" s="2" t="s">
+      <x:c r="D3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9">
+      <x:c r="A4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:9">
+      <x:c r="A5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9">
+      <x:c r="A6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9">
+      <x:c r="A7" s="2" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B7" s="2" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
+      <x:c r="E7" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G3" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:9">
-      <x:c r="A4" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C4" s="2" t="s">
+      <x:c r="G7" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
+      <x:c r="A8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D4" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G4" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:9">
-      <x:c r="A5" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B5" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C5" s="2" t="s">
+      <x:c r="D8" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9">
+      <x:c r="A9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D5" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E5" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F5" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G5" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:9">
-      <x:c r="A6" s="2" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C6" s="2" t="s">
+      <x:c r="D9" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9">
+      <x:c r="A10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D6" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E6" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F6" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G6" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:9">
-      <x:c r="A7" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
+      <x:c r="D10" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:9">
+      <x:c r="A11" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:9">
-      <x:c r="A8" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B8" s="2" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C8" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E8" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F8" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G8" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:9">
-      <x:c r="A9" s="2" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B9" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C9" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E9" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F9" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G9" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:9">
-      <x:c r="A10" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="B10" s="2" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C10" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D10" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E10" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F10" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G10" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:9">
-      <x:c r="A11" s="2" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B11" s="2" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C11" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E11" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F11" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G11" s="2" t="s">
-        <x:v>37</x:v>
+      <x:c r="D11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G56" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G57" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G58" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
       <x:c r="A59" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G59" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G60" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G61" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G62" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G63" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G64" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G65" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G66" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G67" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G68" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
       <x:c r="A69" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G69" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G70" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G71" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
       <x:c r="A72" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G72" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G73" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G74" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G75" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
       <x:c r="A76" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G76" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G77" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G78" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G79" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G80" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G81" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G82" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G83" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G84" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G85" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G86" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
       <x:c r="A87" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G87" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:9">
       <x:c r="A88" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G88" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G89" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G90" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G91" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G92" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G93" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G94" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G95" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G96" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G97" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G98" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G99" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G100" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:9">
       <x:c r="A101" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G101" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:9">
       <x:c r="A102" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G102" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:9">
       <x:c r="A103" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G103" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:9">
       <x:c r="A104" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G104" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:9">
       <x:c r="A105" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G105" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:9">
       <x:c r="A106" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G106" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:9">
       <x:c r="A107" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G107" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:9">
       <x:c r="A108" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G108" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:9">
       <x:c r="A109" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G109" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:9">
       <x:c r="A110" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G110" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:9">
       <x:c r="A111" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G111" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:9">
       <x:c r="A112" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G112" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:9">
       <x:c r="A113" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G113" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:9">
       <x:c r="A114" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G114" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:9">
       <x:c r="A115" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G115" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:9">
       <x:c r="A116" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G116" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:9">
       <x:c r="A117" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G117" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:9">
       <x:c r="A118" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G118" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:9">
       <x:c r="A119" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G119" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:9">
       <x:c r="A120" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G120" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:9">
       <x:c r="A121" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G121" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:9">
       <x:c r="A122" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G122" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:9">
       <x:c r="A123" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G123" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:9">
       <x:c r="A124" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G124" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:9">
       <x:c r="A125" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G125" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:9">
       <x:c r="A126" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G126" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:9">
       <x:c r="A127" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G127" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:9">
       <x:c r="A128" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G128" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:9">
       <x:c r="A129" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G129" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:9">
       <x:c r="A130" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G130" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:9">
       <x:c r="A131" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G131" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:9">
       <x:c r="A132" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G132" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:9">
       <x:c r="A133" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G133" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:9">
       <x:c r="A134" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G134" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:9">
       <x:c r="A135" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G135" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:9">
       <x:c r="A136" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G136" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:9">
       <x:c r="A137" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G137" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:9">
       <x:c r="A138" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G138" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:9">
       <x:c r="A139" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G139" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:9">
       <x:c r="A140" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G140" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:9">
       <x:c r="A141" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G141" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:9">
       <x:c r="A142" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G142" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:9">
       <x:c r="A143" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G143" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:9">
       <x:c r="A144" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G144" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:9">
       <x:c r="A145" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G145" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:9">
       <x:c r="A146" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G146" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:9">
       <x:c r="A147" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G147" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:9">
       <x:c r="A148" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G148" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:9">
       <x:c r="A149" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G149" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:9">
       <x:c r="A150" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G150" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:9">
       <x:c r="A151" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G151" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:9">
       <x:c r="A152" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G152" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:9">
       <x:c r="A153" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G153" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:9">
       <x:c r="A154" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G154" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:9">
       <x:c r="A155" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G155" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:9">
       <x:c r="A156" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G156" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:9">
       <x:c r="A157" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G157" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:9">
       <x:c r="A158" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G158" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:9">
       <x:c r="A159" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G159" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:9">
       <x:c r="A160" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G160" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:9">
       <x:c r="A161" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="C161" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E161" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G161" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:9">
       <x:c r="A162" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E162" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G162" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:9">
       <x:c r="A163" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E163" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G163" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:9">
       <x:c r="A164" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E164" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G164" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:9">
       <x:c r="A165" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E165" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G165" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:9">
       <x:c r="A166" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C166" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E166" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G166" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:9">
       <x:c r="A167" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="C167" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E167" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G167" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:9">
       <x:c r="A168" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="C168" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E168" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G168" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:9">
       <x:c r="A169" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="C169" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E169" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G169" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:9">
       <x:c r="A170" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="C170" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E170" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F170" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G170" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:9">
       <x:c r="A171" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="C171" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E171" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F171" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G171" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:9">
       <x:c r="A172" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="C172" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E172" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F172" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G172" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:9">
       <x:c r="A173" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="C173" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E173" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F173" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G173" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:9">
       <x:c r="A174" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="C174" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E174" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F174" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G174" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:9">
       <x:c r="A175" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="C175" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E175" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F175" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G175" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:9">
       <x:c r="A176" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="C176" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E176" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F176" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G176" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:9">
       <x:c r="A177" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="C177" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E177" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F177" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G177" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:9">
       <x:c r="A178" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C178" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E178" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F178" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G178" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:9">
       <x:c r="A179" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="C179" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E179" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F179" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G179" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:9">
       <x:c r="A180" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="C180" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E180" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F180" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G180" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:9">
       <x:c r="A181" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="C181" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E181" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F181" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G181" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:9">
       <x:c r="A182" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C182" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E182" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F182" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G182" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:9">
       <x:c r="A183" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="C183" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E183" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F183" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G183" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:9">
       <x:c r="A184" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="C184" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E184" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F184" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G184" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:9">
       <x:c r="A185" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="C185" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E185" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F185" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G185" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:9">
       <x:c r="A186" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="C186" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E186" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F186" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G186" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:9">
       <x:c r="A187" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="C187" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E187" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F187" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G187" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:9">
       <x:c r="A188" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="C188" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E188" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F188" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G188" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:9">
       <x:c r="A189" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="C189" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E189" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F189" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G189" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:9">
       <x:c r="A190" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="C190" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D190" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E190" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F190" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G190" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:9">
       <x:c r="A191" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="C191" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D191" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E191" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F191" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G191" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:9">
       <x:c r="A192" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="C192" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D192" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E192" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F192" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G192" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:9">
       <x:c r="A193" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="C193" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D193" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E193" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F193" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G193" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:9">
       <x:c r="A194" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="C194" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D194" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E194" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F194" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G194" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:9">
       <x:c r="A195" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="C195" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D195" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E195" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F195" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G195" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:9">
       <x:c r="A196" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="C196" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D196" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E196" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F196" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G196" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:9">
       <x:c r="A197" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="C197" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D197" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E197" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F197" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G197" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:9">
       <x:c r="A198" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="C198" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D198" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E198" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F198" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G198" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:9">
       <x:c r="A199" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="C199" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D199" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E199" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F199" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G199" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:9">
       <x:c r="A200" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="C200" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D200" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E200" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F200" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G200" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:9">
       <x:c r="A201" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="C201" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E201" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F201" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G201" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:9">
       <x:c r="A202" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="C202" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D202" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E202" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F202" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G202" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:9">
       <x:c r="A203" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="C203" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E203" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F203" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G203" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:9">
       <x:c r="A204" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="C204" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D204" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E204" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F204" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G204" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:9">
       <x:c r="A205" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="C205" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D205" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E205" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F205" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G205" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="206" spans="1:9">
       <x:c r="A206" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="C206" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D206" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E206" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F206" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G206" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:9">
       <x:c r="A207" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="C207" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D207" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E207" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F207" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G207" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:9">
       <x:c r="A208" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="C208" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D208" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E208" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F208" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G208" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:9">
       <x:c r="A209" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="C209" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D209" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E209" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F209" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G209" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:9">
       <x:c r="A210" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="C210" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D210" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E210" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F210" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G210" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="211" spans="1:9">
       <x:c r="A211" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C211" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D211" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E211" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F211" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G211" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="212" spans="1:9">
       <x:c r="A212" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="C212" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D212" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E212" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F212" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G212" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="213" spans="1:9">
       <x:c r="A213" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="C213" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D213" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E213" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F213" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G213" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:9">
       <x:c r="A214" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="C214" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D214" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E214" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F214" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G214" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:9">
       <x:c r="A215" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="C215" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D215" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E215" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F215" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G215" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:9">
       <x:c r="A216" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C216" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E216" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F216" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G216" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="217" spans="1:9">
       <x:c r="A217" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="C217" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E217" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F217" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G217" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:9">
       <x:c r="A218" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="C218" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E218" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F218" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G218" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:9">
       <x:c r="A219" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="C219" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E219" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F219" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G219" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="220" spans="1:9">
       <x:c r="A220" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="C220" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D220" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E220" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F220" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G220" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="221" spans="1:9">
       <x:c r="A221" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="C221" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D221" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E221" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F221" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G221" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="222" spans="1:9">
       <x:c r="A222" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="C222" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D222" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E222" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F222" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G222" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:9">
       <x:c r="A223" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C223" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D223" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E223" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F223" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G223" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="224" spans="1:9">
       <x:c r="A224" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C224" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D224" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E224" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F224" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G224" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:9">
       <x:c r="A225" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="C225" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D225" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E225" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F225" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G225" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="226" spans="1:9">
       <x:c r="A226" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="C226" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D226" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E226" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F226" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G226" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:9">
       <x:c r="A227" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="C227" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E227" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F227" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G227" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -43,16 +43,16 @@
     <x:t>AnhDThe187386</x:t>
   </x:si>
   <x:si>
-    <x:t>Failed</x:t>
+    <x:t>Success</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 13:30:56</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08-12-2025 13:32:39</x:t>
+    <x:t>09-12-2025 15:59:20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09-12-2025 16:01:02</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -91,9 +91,6 @@
     <x:t>dungtdhe186461</x:t>
   </x:si>
   <x:si>
-    <x:t>08-12-2025 13:32:49</x:t>
-  </x:si>
-  <x:si>
     <x:t>7</x:t>
   </x:si>
   <x:si>
@@ -1412,12 +1409,6 @@
   </x:si>
   <x:si>
     <x:t>vietddhe161942</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2025-12-08 13:32:49</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10.48s</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1458,7 +1449,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FF90EE90"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -1811,7 +1802,7 @@
     <x:col min="6" max="7" width="18.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:9" s="1" customFormat="1">
+    <x:row r="1" spans="1:7" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1834,7 +1825,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:9" s="2" customFormat="1">
+    <x:row r="2" spans="1:7">
       <x:c r="A2" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1851,19 +1842,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>466</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>467</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:9">
+    </x:row>
+    <x:row r="3" spans="1:7">
       <x:c r="A3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
@@ -1886,7 +1871,7 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:9">
+    <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1909,7 +1894,7 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:9">
+    <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
@@ -1932,7 +1917,7 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:9">
+    <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
@@ -1955,35 +1940,35 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:9">
-      <x:c r="A7" s="2" t="s">
+    <x:row r="7" spans="1:7">
+      <x:c r="A7" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B7" s="2" t="s">
+      <x:c r="B7" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C7" s="2" t="s">
+      <x:c r="C7" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D7" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E7" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F7" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G7" s="2" t="s">
+      <x:c r="D7" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:7">
+      <x:c r="A8" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" spans="1:9">
-      <x:c r="A8" s="0" t="s">
+      <x:c r="B8" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>7</x:v>
@@ -2001,12 +1986,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:9">
+    <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>7</x:v>
@@ -2024,12 +2009,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:9">
+    <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>7</x:v>
@@ -2047,12 +2032,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:9">
+    <x:row r="11" spans="1:7">
       <x:c r="A11" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>7</x:v>
@@ -2070,12 +2055,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:9">
+    <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
@@ -2093,12 +2078,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:9">
+    <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
@@ -2116,12 +2101,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:9">
+    <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
@@ -2139,12 +2124,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:9">
+    <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
@@ -2162,12 +2147,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:9">
+    <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
@@ -2185,12 +2170,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:9">
+    <x:row r="17" spans="1:7">
       <x:c r="A17" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>45</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
@@ -2208,12 +2193,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:9">
+    <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
@@ -2231,12 +2216,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:9">
+    <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
@@ -2254,12 +2239,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:9">
+    <x:row r="20" spans="1:7">
       <x:c r="A20" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>7</x:v>
@@ -2277,12 +2262,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:9">
+    <x:row r="21" spans="1:7">
       <x:c r="A21" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>7</x:v>
@@ -2300,12 +2285,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:9">
+    <x:row r="22" spans="1:7">
       <x:c r="A22" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>7</x:v>
@@ -2323,12 +2308,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:9">
+    <x:row r="23" spans="1:7">
       <x:c r="A23" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>7</x:v>
@@ -2346,12 +2331,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:9">
+    <x:row r="24" spans="1:7">
       <x:c r="A24" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>7</x:v>
@@ -2369,12 +2354,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:9">
+    <x:row r="25" spans="1:7">
       <x:c r="A25" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>7</x:v>
@@ -2392,12 +2377,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:9">
+    <x:row r="26" spans="1:7">
       <x:c r="A26" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>63</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>7</x:v>
@@ -2415,12 +2400,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:9">
+    <x:row r="27" spans="1:7">
       <x:c r="A27" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>13</x:v>
@@ -2438,12 +2423,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:9">
+    <x:row r="28" spans="1:7">
       <x:c r="A28" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>13</x:v>
@@ -2461,12 +2446,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:9">
+    <x:row r="29" spans="1:7">
       <x:c r="A29" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>13</x:v>
@@ -2484,12 +2469,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:9">
+    <x:row r="30" spans="1:7">
       <x:c r="A30" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>13</x:v>
@@ -2507,12 +2492,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:9">
+    <x:row r="31" spans="1:7">
       <x:c r="A31" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>13</x:v>
@@ -2530,12 +2515,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:9">
+    <x:row r="32" spans="1:7">
       <x:c r="A32" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>13</x:v>
@@ -2553,12 +2538,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:9">
+    <x:row r="33" spans="1:7">
       <x:c r="A33" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>13</x:v>
@@ -2576,12 +2561,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:9">
+    <x:row r="34" spans="1:7">
       <x:c r="A34" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>13</x:v>
@@ -2599,12 +2584,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:9">
+    <x:row r="35" spans="1:7">
       <x:c r="A35" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>13</x:v>
@@ -2622,12 +2607,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:9">
+    <x:row r="36" spans="1:7">
       <x:c r="A36" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>13</x:v>
@@ -2645,12 +2630,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:9">
+    <x:row r="37" spans="1:7">
       <x:c r="A37" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>13</x:v>
@@ -2668,12 +2653,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:9">
+    <x:row r="38" spans="1:7">
       <x:c r="A38" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>13</x:v>
@@ -2691,12 +2676,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:9">
+    <x:row r="39" spans="1:7">
       <x:c r="A39" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>13</x:v>
@@ -2714,12 +2699,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" spans="1:9">
+    <x:row r="40" spans="1:7">
       <x:c r="A40" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>13</x:v>
@@ -2737,12 +2722,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:9">
+    <x:row r="41" spans="1:7">
       <x:c r="A41" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>13</x:v>
@@ -2760,12 +2745,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:9">
+    <x:row r="42" spans="1:7">
       <x:c r="A42" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>13</x:v>
@@ -2783,12 +2768,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:9">
+    <x:row r="43" spans="1:7">
       <x:c r="A43" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>13</x:v>
@@ -2806,12 +2791,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" spans="1:9">
+    <x:row r="44" spans="1:7">
       <x:c r="A44" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>99</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>13</x:v>
@@ -2829,12 +2814,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" spans="1:9">
+    <x:row r="45" spans="1:7">
       <x:c r="A45" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>101</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>13</x:v>
@@ -2852,12 +2837,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" spans="1:9">
+    <x:row r="46" spans="1:7">
       <x:c r="A46" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>13</x:v>
@@ -2875,12 +2860,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" spans="1:9">
+    <x:row r="47" spans="1:7">
       <x:c r="A47" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>13</x:v>
@@ -2898,12 +2883,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" spans="1:9">
+    <x:row r="48" spans="1:7">
       <x:c r="A48" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>107</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>13</x:v>
@@ -2921,12 +2906,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:9">
+    <x:row r="49" spans="1:7">
       <x:c r="A49" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>109</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>13</x:v>
@@ -2944,12 +2929,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:9">
+    <x:row r="50" spans="1:7">
       <x:c r="A50" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>111</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>13</x:v>
@@ -2967,12 +2952,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:9">
+    <x:row r="51" spans="1:7">
       <x:c r="A51" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
         <x:v>112</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>13</x:v>
@@ -2990,12 +2975,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:9">
+    <x:row r="52" spans="1:7">
       <x:c r="A52" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>115</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>13</x:v>
@@ -3013,12 +2998,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" spans="1:9">
+    <x:row r="53" spans="1:7">
       <x:c r="A53" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>117</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>13</x:v>
@@ -3036,12 +3021,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" spans="1:9">
+    <x:row r="54" spans="1:7">
       <x:c r="A54" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>119</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>13</x:v>
@@ -3059,12 +3044,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" spans="1:9">
+    <x:row r="55" spans="1:7">
       <x:c r="A55" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>13</x:v>
@@ -3082,12 +3067,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" spans="1:9">
+    <x:row r="56" spans="1:7">
       <x:c r="A56" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>17</x:v>
@@ -3105,12 +3090,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" spans="1:9">
+    <x:row r="57" spans="1:7">
       <x:c r="A57" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>125</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>17</x:v>
@@ -3128,12 +3113,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" spans="1:9">
+    <x:row r="58" spans="1:7">
       <x:c r="A58" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
         <x:v>126</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>127</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>17</x:v>
@@ -3151,12 +3136,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" spans="1:9">
+    <x:row r="59" spans="1:7">
       <x:c r="A59" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>17</x:v>
@@ -3174,12 +3159,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:9">
+    <x:row r="60" spans="1:7">
       <x:c r="A60" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>131</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>17</x:v>
@@ -3197,12 +3182,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" spans="1:9">
+    <x:row r="61" spans="1:7">
       <x:c r="A61" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>133</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>17</x:v>
@@ -3220,12 +3205,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" spans="1:9">
+    <x:row r="62" spans="1:7">
       <x:c r="A62" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
         <x:v>17</x:v>
@@ -3243,12 +3228,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" spans="1:9">
+    <x:row r="63" spans="1:7">
       <x:c r="A63" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>137</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
         <x:v>17</x:v>
@@ -3266,12 +3251,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" spans="1:9">
+    <x:row r="64" spans="1:7">
       <x:c r="A64" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>139</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
         <x:v>17</x:v>
@@ -3289,12 +3274,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" spans="1:9">
+    <x:row r="65" spans="1:7">
       <x:c r="A65" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>17</x:v>
@@ -3312,12 +3297,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" spans="1:9">
+    <x:row r="66" spans="1:7">
       <x:c r="A66" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>17</x:v>
@@ -3335,12 +3320,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" spans="1:9">
+    <x:row r="67" spans="1:7">
       <x:c r="A67" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>145</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>17</x:v>
@@ -3358,12 +3343,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" spans="1:9">
+    <x:row r="68" spans="1:7">
       <x:c r="A68" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>147</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>17</x:v>
@@ -3381,12 +3366,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" spans="1:9">
+    <x:row r="69" spans="1:7">
       <x:c r="A69" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
         <x:v>148</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>149</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>17</x:v>
@@ -3404,12 +3389,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" spans="1:9">
+    <x:row r="70" spans="1:7">
       <x:c r="A70" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>151</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
         <x:v>17</x:v>
@@ -3427,12 +3412,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" spans="1:9">
+    <x:row r="71" spans="1:7">
       <x:c r="A71" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>153</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
         <x:v>17</x:v>
@@ -3450,12 +3435,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" spans="1:9">
+    <x:row r="72" spans="1:7">
       <x:c r="A72" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
         <x:v>154</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>155</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
         <x:v>17</x:v>
@@ -3473,12 +3458,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" spans="1:9">
+    <x:row r="73" spans="1:7">
       <x:c r="A73" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
         <x:v>156</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>17</x:v>
@@ -3496,12 +3481,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" spans="1:9">
+    <x:row r="74" spans="1:7">
       <x:c r="A74" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
         <x:v>158</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>159</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>17</x:v>
@@ -3519,12 +3504,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" spans="1:9">
+    <x:row r="75" spans="1:7">
       <x:c r="A75" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>161</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>17</x:v>
@@ -3542,12 +3527,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" spans="1:9">
+    <x:row r="76" spans="1:7">
       <x:c r="A76" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
         <x:v>162</x:v>
-      </x:c>
-      <x:c r="B76" s="0" t="s">
-        <x:v>163</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
         <x:v>17</x:v>
@@ -3565,12 +3550,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" spans="1:9">
+    <x:row r="77" spans="1:7">
       <x:c r="A77" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="B77" s="0" t="s">
-        <x:v>165</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>17</x:v>
@@ -3588,12 +3573,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" spans="1:9">
+    <x:row r="78" spans="1:7">
       <x:c r="A78" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
         <x:v>166</x:v>
-      </x:c>
-      <x:c r="B78" s="0" t="s">
-        <x:v>167</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>17</x:v>
@@ -3611,12 +3596,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" spans="1:9">
+    <x:row r="79" spans="1:7">
       <x:c r="A79" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
         <x:v>168</x:v>
-      </x:c>
-      <x:c r="B79" s="0" t="s">
-        <x:v>169</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>17</x:v>
@@ -3634,12 +3619,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" spans="1:9">
+    <x:row r="80" spans="1:7">
       <x:c r="A80" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
         <x:v>170</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>171</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
         <x:v>17</x:v>
@@ -3657,12 +3642,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" spans="1:9">
+    <x:row r="81" spans="1:7">
       <x:c r="A81" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
         <x:v>172</x:v>
-      </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>173</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
         <x:v>17</x:v>
@@ -3680,12 +3665,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" spans="1:9">
+    <x:row r="82" spans="1:7">
       <x:c r="A82" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>175</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
         <x:v>17</x:v>
@@ -3703,12 +3688,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" spans="1:9">
+    <x:row r="83" spans="1:7">
       <x:c r="A83" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
         <x:v>176</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>177</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
         <x:v>17</x:v>
@@ -3726,12 +3711,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" spans="1:9">
+    <x:row r="84" spans="1:7">
       <x:c r="A84" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>179</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
         <x:v>17</x:v>
@@ -3749,12 +3734,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" spans="1:9">
+    <x:row r="85" spans="1:7">
       <x:c r="A85" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
         <x:v>180</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>181</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>19</x:v>
@@ -3772,12 +3757,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" spans="1:9">
+    <x:row r="86" spans="1:7">
       <x:c r="A86" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
         <x:v>182</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>183</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>19</x:v>
@@ -3795,12 +3780,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" spans="1:9">
+    <x:row r="87" spans="1:7">
       <x:c r="A87" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="B87" s="0" t="s">
-        <x:v>185</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>19</x:v>
@@ -3818,12 +3803,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" spans="1:9">
+    <x:row r="88" spans="1:7">
       <x:c r="A88" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
         <x:v>186</x:v>
-      </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>187</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
         <x:v>19</x:v>
@@ -3841,12 +3826,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" spans="1:9">
+    <x:row r="89" spans="1:7">
       <x:c r="A89" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
         <x:v>188</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>189</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
         <x:v>19</x:v>
@@ -3864,12 +3849,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" spans="1:9">
+    <x:row r="90" spans="1:7">
       <x:c r="A90" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
         <x:v>190</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>191</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>19</x:v>
@@ -3887,12 +3872,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" spans="1:9">
+    <x:row r="91" spans="1:7">
       <x:c r="A91" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="B91" s="0" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>19</x:v>
@@ -3910,12 +3895,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" spans="1:9">
+    <x:row r="92" spans="1:7">
       <x:c r="A92" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
         <x:v>194</x:v>
-      </x:c>
-      <x:c r="B92" s="0" t="s">
-        <x:v>195</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
         <x:v>19</x:v>
@@ -3933,12 +3918,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" spans="1:9">
+    <x:row r="93" spans="1:7">
       <x:c r="A93" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
         <x:v>196</x:v>
-      </x:c>
-      <x:c r="B93" s="0" t="s">
-        <x:v>197</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>19</x:v>
@@ -3956,12 +3941,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" spans="1:9">
+    <x:row r="94" spans="1:7">
       <x:c r="A94" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="B94" s="0" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>19</x:v>
@@ -3979,12 +3964,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" spans="1:9">
+    <x:row r="95" spans="1:7">
       <x:c r="A95" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
         <x:v>200</x:v>
-      </x:c>
-      <x:c r="B95" s="0" t="s">
-        <x:v>201</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>19</x:v>
@@ -4002,12 +3987,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" spans="1:9">
+    <x:row r="96" spans="1:7">
       <x:c r="A96" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
         <x:v>202</x:v>
-      </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>203</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>19</x:v>
@@ -4025,12 +4010,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" spans="1:9">
+    <x:row r="97" spans="1:7">
       <x:c r="A97" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
         <x:v>204</x:v>
-      </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>205</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>19</x:v>
@@ -4048,12 +4033,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" spans="1:9">
+    <x:row r="98" spans="1:7">
       <x:c r="A98" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
         <x:v>206</x:v>
-      </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>207</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>19</x:v>
@@ -4071,12 +4056,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" spans="1:9">
+    <x:row r="99" spans="1:7">
       <x:c r="A99" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
         <x:v>208</x:v>
-      </x:c>
-      <x:c r="B99" s="0" t="s">
-        <x:v>209</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>19</x:v>
@@ -4094,12 +4079,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" spans="1:9">
+    <x:row r="100" spans="1:7">
       <x:c r="A100" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="B100" s="0" t="s">
-        <x:v>211</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>19</x:v>
@@ -4117,12 +4102,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" spans="1:9">
+    <x:row r="101" spans="1:7">
       <x:c r="A101" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
         <x:v>212</x:v>
-      </x:c>
-      <x:c r="B101" s="0" t="s">
-        <x:v>213</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>19</x:v>
@@ -4140,12 +4125,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" spans="1:9">
+    <x:row r="102" spans="1:7">
       <x:c r="A102" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="B102" s="0" t="s">
-        <x:v>215</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>19</x:v>
@@ -4163,12 +4148,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" spans="1:9">
+    <x:row r="103" spans="1:7">
       <x:c r="A103" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
         <x:v>216</x:v>
-      </x:c>
-      <x:c r="B103" s="0" t="s">
-        <x:v>217</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>19</x:v>
@@ -4186,12 +4171,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" spans="1:9">
+    <x:row r="104" spans="1:7">
       <x:c r="A104" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
         <x:v>218</x:v>
-      </x:c>
-      <x:c r="B104" s="0" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
         <x:v>19</x:v>
@@ -4209,12 +4194,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" spans="1:9">
+    <x:row r="105" spans="1:7">
       <x:c r="A105" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="B105" s="0" t="s">
-        <x:v>221</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>19</x:v>
@@ -4232,12 +4217,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" spans="1:9">
+    <x:row r="106" spans="1:7">
       <x:c r="A106" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="B106" s="0" t="s">
-        <x:v>223</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>19</x:v>
@@ -4255,12 +4240,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" spans="1:9">
+    <x:row r="107" spans="1:7">
       <x:c r="A107" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
         <x:v>224</x:v>
-      </x:c>
-      <x:c r="B107" s="0" t="s">
-        <x:v>225</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>19</x:v>
@@ -4278,12 +4263,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" spans="1:9">
+    <x:row r="108" spans="1:7">
       <x:c r="A108" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="B108" s="0" t="s">
-        <x:v>227</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>19</x:v>
@@ -4301,12 +4286,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" spans="1:9">
+    <x:row r="109" spans="1:7">
       <x:c r="A109" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="B109" s="0" t="s">
-        <x:v>229</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>19</x:v>
@@ -4324,12 +4309,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" spans="1:9">
+    <x:row r="110" spans="1:7">
       <x:c r="A110" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
         <x:v>230</x:v>
-      </x:c>
-      <x:c r="B110" s="0" t="s">
-        <x:v>231</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
         <x:v>19</x:v>
@@ -4347,12 +4332,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" spans="1:9">
+    <x:row r="111" spans="1:7">
       <x:c r="A111" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="B111" s="0" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>19</x:v>
@@ -4370,12 +4355,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" spans="1:9">
+    <x:row r="112" spans="1:7">
       <x:c r="A112" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
         <x:v>234</x:v>
-      </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>235</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
         <x:v>19</x:v>
@@ -4393,12 +4378,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" spans="1:9">
+    <x:row r="113" spans="1:7">
       <x:c r="A113" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>237</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>19</x:v>
@@ -4416,12 +4401,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" spans="1:9">
+    <x:row r="114" spans="1:7">
       <x:c r="A114" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
         <x:v>238</x:v>
-      </x:c>
-      <x:c r="B114" s="0" t="s">
-        <x:v>239</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>19</x:v>
@@ -4439,12 +4424,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" spans="1:9">
+    <x:row r="115" spans="1:7">
       <x:c r="A115" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
         <x:v>240</x:v>
-      </x:c>
-      <x:c r="B115" s="0" t="s">
-        <x:v>241</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
         <x:v>19</x:v>
@@ -4462,12 +4447,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" spans="1:9">
+    <x:row r="116" spans="1:7">
       <x:c r="A116" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>243</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>21</x:v>
@@ -4485,12 +4470,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" spans="1:9">
+    <x:row r="117" spans="1:7">
       <x:c r="A117" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
         <x:v>244</x:v>
-      </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>245</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>21</x:v>
@@ -4508,12 +4493,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" spans="1:9">
+    <x:row r="118" spans="1:7">
       <x:c r="A118" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
         <x:v>246</x:v>
-      </x:c>
-      <x:c r="B118" s="0" t="s">
-        <x:v>247</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>21</x:v>
@@ -4531,12 +4516,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" spans="1:9">
+    <x:row r="119" spans="1:7">
       <x:c r="A119" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>249</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>21</x:v>
@@ -4554,12 +4539,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" spans="1:9">
+    <x:row r="120" spans="1:7">
       <x:c r="A120" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="B120" s="0" t="s">
-        <x:v>251</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>21</x:v>
@@ -4577,12 +4562,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" spans="1:9">
+    <x:row r="121" spans="1:7">
       <x:c r="A121" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
         <x:v>252</x:v>
-      </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>253</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
         <x:v>21</x:v>
@@ -4600,12 +4585,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" spans="1:9">
+    <x:row r="122" spans="1:7">
       <x:c r="A122" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
         <x:v>254</x:v>
-      </x:c>
-      <x:c r="B122" s="0" t="s">
-        <x:v>255</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
         <x:v>21</x:v>
@@ -4623,12 +4608,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" spans="1:9">
+    <x:row r="123" spans="1:7">
       <x:c r="A123" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
         <x:v>256</x:v>
-      </x:c>
-      <x:c r="B123" s="0" t="s">
-        <x:v>257</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
         <x:v>21</x:v>
@@ -4646,12 +4631,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" spans="1:9">
+    <x:row r="124" spans="1:7">
       <x:c r="A124" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
         <x:v>258</x:v>
-      </x:c>
-      <x:c r="B124" s="0" t="s">
-        <x:v>259</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
         <x:v>21</x:v>
@@ -4669,12 +4654,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" spans="1:9">
+    <x:row r="125" spans="1:7">
       <x:c r="A125" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="B125" s="0" t="s">
-        <x:v>261</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
         <x:v>21</x:v>
@@ -4692,12 +4677,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" spans="1:9">
+    <x:row r="126" spans="1:7">
       <x:c r="A126" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
         <x:v>262</x:v>
-      </x:c>
-      <x:c r="B126" s="0" t="s">
-        <x:v>263</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
         <x:v>21</x:v>
@@ -4715,12 +4700,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" spans="1:9">
+    <x:row r="127" spans="1:7">
       <x:c r="A127" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
         <x:v>264</x:v>
-      </x:c>
-      <x:c r="B127" s="0" t="s">
-        <x:v>265</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>21</x:v>
@@ -4738,12 +4723,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" spans="1:9">
+    <x:row r="128" spans="1:7">
       <x:c r="A128" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
         <x:v>266</x:v>
-      </x:c>
-      <x:c r="B128" s="0" t="s">
-        <x:v>267</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>21</x:v>
@@ -4761,12 +4746,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" spans="1:9">
+    <x:row r="129" spans="1:7">
       <x:c r="A129" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="B129" s="0" t="s">
-        <x:v>269</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>21</x:v>
@@ -4784,12 +4769,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" spans="1:9">
+    <x:row r="130" spans="1:7">
       <x:c r="A130" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
         <x:v>270</x:v>
-      </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>271</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
         <x:v>21</x:v>
@@ -4807,12 +4792,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" spans="1:9">
+    <x:row r="131" spans="1:7">
       <x:c r="A131" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
         <x:v>272</x:v>
-      </x:c>
-      <x:c r="B131" s="0" t="s">
-        <x:v>273</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
         <x:v>21</x:v>
@@ -4830,12 +4815,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" spans="1:9">
+    <x:row r="132" spans="1:7">
       <x:c r="A132" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
         <x:v>274</x:v>
-      </x:c>
-      <x:c r="B132" s="0" t="s">
-        <x:v>275</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
         <x:v>21</x:v>
@@ -4853,12 +4838,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" spans="1:9">
+    <x:row r="133" spans="1:7">
       <x:c r="A133" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
         <x:v>276</x:v>
-      </x:c>
-      <x:c r="B133" s="0" t="s">
-        <x:v>277</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
         <x:v>21</x:v>
@@ -4876,12 +4861,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="134" spans="1:9">
+    <x:row r="134" spans="1:7">
       <x:c r="A134" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
         <x:v>278</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>279</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
         <x:v>21</x:v>
@@ -4899,12 +4884,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" spans="1:9">
+    <x:row r="135" spans="1:7">
       <x:c r="A135" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
         <x:v>280</x:v>
-      </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>281</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
         <x:v>21</x:v>
@@ -4922,12 +4907,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" spans="1:9">
+    <x:row r="136" spans="1:7">
       <x:c r="A136" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
         <x:v>282</x:v>
-      </x:c>
-      <x:c r="B136" s="0" t="s">
-        <x:v>283</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
         <x:v>21</x:v>
@@ -4945,12 +4930,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" spans="1:9">
+    <x:row r="137" spans="1:7">
       <x:c r="A137" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
         <x:v>284</x:v>
-      </x:c>
-      <x:c r="B137" s="0" t="s">
-        <x:v>285</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
         <x:v>21</x:v>
@@ -4968,12 +4953,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" spans="1:9">
+    <x:row r="138" spans="1:7">
       <x:c r="A138" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
         <x:v>286</x:v>
-      </x:c>
-      <x:c r="B138" s="0" t="s">
-        <x:v>287</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>21</x:v>
@@ -4991,12 +4976,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" spans="1:9">
+    <x:row r="139" spans="1:7">
       <x:c r="A139" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
         <x:v>288</x:v>
-      </x:c>
-      <x:c r="B139" s="0" t="s">
-        <x:v>289</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
         <x:v>21</x:v>
@@ -5014,12 +4999,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" spans="1:9">
+    <x:row r="140" spans="1:7">
       <x:c r="A140" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
         <x:v>290</x:v>
-      </x:c>
-      <x:c r="B140" s="0" t="s">
-        <x:v>291</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
         <x:v>21</x:v>
@@ -5037,12 +5022,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" spans="1:9">
+    <x:row r="141" spans="1:7">
       <x:c r="A141" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
         <x:v>292</x:v>
-      </x:c>
-      <x:c r="B141" s="0" t="s">
-        <x:v>293</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
         <x:v>21</x:v>
@@ -5060,12 +5045,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" spans="1:9">
+    <x:row r="142" spans="1:7">
       <x:c r="A142" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
         <x:v>294</x:v>
-      </x:c>
-      <x:c r="B142" s="0" t="s">
-        <x:v>295</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
         <x:v>23</x:v>
@@ -5083,12 +5068,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" spans="1:9">
+    <x:row r="143" spans="1:7">
       <x:c r="A143" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
         <x:v>296</x:v>
-      </x:c>
-      <x:c r="B143" s="0" t="s">
-        <x:v>297</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
         <x:v>23</x:v>
@@ -5106,12 +5091,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" spans="1:9">
+    <x:row r="144" spans="1:7">
       <x:c r="A144" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
         <x:v>298</x:v>
-      </x:c>
-      <x:c r="B144" s="0" t="s">
-        <x:v>299</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
         <x:v>23</x:v>
@@ -5129,12 +5114,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" spans="1:9">
+    <x:row r="145" spans="1:7">
       <x:c r="A145" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
         <x:v>300</x:v>
-      </x:c>
-      <x:c r="B145" s="0" t="s">
-        <x:v>301</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
         <x:v>23</x:v>
@@ -5152,12 +5137,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" spans="1:9">
+    <x:row r="146" spans="1:7">
       <x:c r="A146" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
         <x:v>302</x:v>
-      </x:c>
-      <x:c r="B146" s="0" t="s">
-        <x:v>303</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
         <x:v>23</x:v>
@@ -5175,12 +5160,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" spans="1:9">
+    <x:row r="147" spans="1:7">
       <x:c r="A147" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="B147" s="0" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
         <x:v>23</x:v>
@@ -5198,12 +5183,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" spans="1:9">
+    <x:row r="148" spans="1:7">
       <x:c r="A148" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
         <x:v>306</x:v>
-      </x:c>
-      <x:c r="B148" s="0" t="s">
-        <x:v>307</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
         <x:v>23</x:v>
@@ -5221,12 +5206,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" spans="1:9">
+    <x:row r="149" spans="1:7">
       <x:c r="A149" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
         <x:v>308</x:v>
-      </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>309</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
         <x:v>23</x:v>
@@ -5244,12 +5229,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" spans="1:9">
+    <x:row r="150" spans="1:7">
       <x:c r="A150" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="B150" s="0" t="s">
-        <x:v>311</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
         <x:v>23</x:v>
@@ -5267,12 +5252,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" spans="1:9">
+    <x:row r="151" spans="1:7">
       <x:c r="A151" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
         <x:v>312</x:v>
-      </x:c>
-      <x:c r="B151" s="0" t="s">
-        <x:v>313</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
         <x:v>23</x:v>
@@ -5290,12 +5275,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" spans="1:9">
+    <x:row r="152" spans="1:7">
       <x:c r="A152" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
         <x:v>314</x:v>
-      </x:c>
-      <x:c r="B152" s="0" t="s">
-        <x:v>315</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
         <x:v>23</x:v>
@@ -5313,12 +5298,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" spans="1:9">
+    <x:row r="153" spans="1:7">
       <x:c r="A153" s="0" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
         <x:v>316</x:v>
-      </x:c>
-      <x:c r="B153" s="0" t="s">
-        <x:v>317</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
         <x:v>23</x:v>
@@ -5336,12 +5321,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" spans="1:9">
+    <x:row r="154" spans="1:7">
       <x:c r="A154" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
         <x:v>318</x:v>
-      </x:c>
-      <x:c r="B154" s="0" t="s">
-        <x:v>319</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
         <x:v>23</x:v>
@@ -5359,12 +5344,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" spans="1:9">
+    <x:row r="155" spans="1:7">
       <x:c r="A155" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
         <x:v>320</x:v>
-      </x:c>
-      <x:c r="B155" s="0" t="s">
-        <x:v>321</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
         <x:v>23</x:v>
@@ -5382,12 +5367,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" spans="1:9">
+    <x:row r="156" spans="1:7">
       <x:c r="A156" s="0" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
         <x:v>322</x:v>
-      </x:c>
-      <x:c r="B156" s="0" t="s">
-        <x:v>323</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
         <x:v>23</x:v>
@@ -5405,12 +5390,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" spans="1:9">
+    <x:row r="157" spans="1:7">
       <x:c r="A157" s="0" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
         <x:v>324</x:v>
-      </x:c>
-      <x:c r="B157" s="0" t="s">
-        <x:v>325</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
         <x:v>23</x:v>
@@ -5428,12 +5413,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" spans="1:9">
+    <x:row r="158" spans="1:7">
       <x:c r="A158" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
         <x:v>326</x:v>
-      </x:c>
-      <x:c r="B158" s="0" t="s">
-        <x:v>327</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
         <x:v>23</x:v>
@@ -5451,12 +5436,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" spans="1:9">
+    <x:row r="159" spans="1:7">
       <x:c r="A159" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
         <x:v>328</x:v>
-      </x:c>
-      <x:c r="B159" s="0" t="s">
-        <x:v>329</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
         <x:v>23</x:v>
@@ -5474,12 +5459,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" spans="1:9">
+    <x:row r="160" spans="1:7">
       <x:c r="A160" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
         <x:v>330</x:v>
-      </x:c>
-      <x:c r="B160" s="0" t="s">
-        <x:v>331</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
         <x:v>23</x:v>
@@ -5497,12 +5482,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" spans="1:9">
+    <x:row r="161" spans="1:7">
       <x:c r="A161" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="B161" s="0" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="C161" s="0" t="s">
         <x:v>23</x:v>
@@ -5520,12 +5505,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" spans="1:9">
+    <x:row r="162" spans="1:7">
       <x:c r="A162" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
         <x:v>334</x:v>
-      </x:c>
-      <x:c r="B162" s="0" t="s">
-        <x:v>335</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
         <x:v>23</x:v>
@@ -5543,12 +5528,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" spans="1:9">
+    <x:row r="163" spans="1:7">
       <x:c r="A163" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
         <x:v>336</x:v>
-      </x:c>
-      <x:c r="B163" s="0" t="s">
-        <x:v>337</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
         <x:v>23</x:v>
@@ -5566,12 +5551,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" spans="1:9">
+    <x:row r="164" spans="1:7">
       <x:c r="A164" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
         <x:v>338</x:v>
-      </x:c>
-      <x:c r="B164" s="0" t="s">
-        <x:v>339</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
         <x:v>23</x:v>
@@ -5589,12 +5574,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" spans="1:9">
+    <x:row r="165" spans="1:7">
       <x:c r="A165" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
         <x:v>340</x:v>
-      </x:c>
-      <x:c r="B165" s="0" t="s">
-        <x:v>341</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
         <x:v>23</x:v>
@@ -5612,12 +5597,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" spans="1:9">
+    <x:row r="166" spans="1:7">
       <x:c r="A166" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
         <x:v>342</x:v>
-      </x:c>
-      <x:c r="B166" s="0" t="s">
-        <x:v>343</x:v>
       </x:c>
       <x:c r="C166" s="0" t="s">
         <x:v>23</x:v>
@@ -5635,12 +5620,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" spans="1:9">
+    <x:row r="167" spans="1:7">
       <x:c r="A167" s="0" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
         <x:v>344</x:v>
-      </x:c>
-      <x:c r="B167" s="0" t="s">
-        <x:v>345</x:v>
       </x:c>
       <x:c r="C167" s="0" t="s">
         <x:v>23</x:v>
@@ -5658,1372 +5643,1372 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" spans="1:9">
+    <x:row r="168" spans="1:7">
       <x:c r="A168" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="B168" s="0" t="s">
+      <x:c r="C168" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E168" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F168" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G168" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:7">
+      <x:c r="A169" s="0" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="C168" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D168" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E168" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F168" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G168" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" spans="1:9">
-      <x:c r="A169" s="0" t="s">
+      <x:c r="B169" s="0" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="B169" s="0" t="s">
+      <x:c r="C169" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E169" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F169" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G169" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:7">
+      <x:c r="A170" s="0" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="C169" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D169" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E169" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F169" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G169" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" spans="1:9">
-      <x:c r="A170" s="0" t="s">
+      <x:c r="B170" s="0" t="s">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="B170" s="0" t="s">
+      <x:c r="C170" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E170" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F170" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G170" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:7">
+      <x:c r="A171" s="0" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="C170" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D170" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E170" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F170" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G170" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" spans="1:9">
-      <x:c r="A171" s="0" t="s">
+      <x:c r="B171" s="0" t="s">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="B171" s="0" t="s">
+      <x:c r="C171" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E171" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F171" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G171" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:7">
+      <x:c r="A172" s="0" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="C171" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D171" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E171" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F171" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G171" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" spans="1:9">
-      <x:c r="A172" s="0" t="s">
+      <x:c r="B172" s="0" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="B172" s="0" t="s">
+      <x:c r="C172" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E172" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F172" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G172" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:7">
+      <x:c r="A173" s="0" t="s">
         <x:v>355</x:v>
       </x:c>
-      <x:c r="C172" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D172" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E172" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F172" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G172" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" spans="1:9">
-      <x:c r="A173" s="0" t="s">
+      <x:c r="B173" s="0" t="s">
         <x:v>356</x:v>
       </x:c>
-      <x:c r="B173" s="0" t="s">
+      <x:c r="C173" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E173" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F173" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G173" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:7">
+      <x:c r="A174" s="0" t="s">
         <x:v>357</x:v>
       </x:c>
-      <x:c r="C173" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D173" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E173" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F173" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G173" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174" spans="1:9">
-      <x:c r="A174" s="0" t="s">
+      <x:c r="B174" s="0" t="s">
         <x:v>358</x:v>
       </x:c>
-      <x:c r="B174" s="0" t="s">
+      <x:c r="C174" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D174" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E174" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F174" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G174" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:7">
+      <x:c r="A175" s="0" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="C174" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D174" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E174" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F174" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G174" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" spans="1:9">
-      <x:c r="A175" s="0" t="s">
+      <x:c r="B175" s="0" t="s">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="B175" s="0" t="s">
+      <x:c r="C175" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D175" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E175" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F175" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G175" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:7">
+      <x:c r="A176" s="0" t="s">
         <x:v>361</x:v>
       </x:c>
-      <x:c r="C175" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D175" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E175" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F175" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G175" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176" spans="1:9">
-      <x:c r="A176" s="0" t="s">
+      <x:c r="B176" s="0" t="s">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="B176" s="0" t="s">
+      <x:c r="C176" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D176" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E176" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F176" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G176" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:7">
+      <x:c r="A177" s="0" t="s">
         <x:v>363</x:v>
       </x:c>
-      <x:c r="C176" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D176" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E176" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F176" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G176" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="177" spans="1:9">
-      <x:c r="A177" s="0" t="s">
+      <x:c r="B177" s="0" t="s">
         <x:v>364</x:v>
       </x:c>
-      <x:c r="B177" s="0" t="s">
+      <x:c r="C177" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D177" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E177" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F177" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G177" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:7">
+      <x:c r="A178" s="0" t="s">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="C177" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D177" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E177" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F177" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G177" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="178" spans="1:9">
-      <x:c r="A178" s="0" t="s">
+      <x:c r="B178" s="0" t="s">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="B178" s="0" t="s">
+      <x:c r="C178" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D178" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E178" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F178" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G178" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:7">
+      <x:c r="A179" s="0" t="s">
         <x:v>367</x:v>
       </x:c>
-      <x:c r="C178" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D178" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E178" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F178" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G178" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179" spans="1:9">
-      <x:c r="A179" s="0" t="s">
+      <x:c r="B179" s="0" t="s">
         <x:v>368</x:v>
       </x:c>
-      <x:c r="B179" s="0" t="s">
+      <x:c r="C179" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D179" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E179" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F179" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G179" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:7">
+      <x:c r="A180" s="0" t="s">
         <x:v>369</x:v>
       </x:c>
-      <x:c r="C179" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D179" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E179" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F179" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G179" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="180" spans="1:9">
-      <x:c r="A180" s="0" t="s">
+      <x:c r="B180" s="0" t="s">
         <x:v>370</x:v>
       </x:c>
-      <x:c r="B180" s="0" t="s">
+      <x:c r="C180" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D180" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E180" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F180" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G180" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:7">
+      <x:c r="A181" s="0" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="C180" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D180" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E180" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F180" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G180" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="181" spans="1:9">
-      <x:c r="A181" s="0" t="s">
+      <x:c r="B181" s="0" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="B181" s="0" t="s">
+      <x:c r="C181" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D181" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E181" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F181" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G181" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:7">
+      <x:c r="A182" s="0" t="s">
         <x:v>373</x:v>
       </x:c>
-      <x:c r="C181" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D181" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E181" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F181" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G181" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="182" spans="1:9">
-      <x:c r="A182" s="0" t="s">
+      <x:c r="B182" s="0" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="B182" s="0" t="s">
+      <x:c r="C182" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D182" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E182" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F182" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G182" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:7">
+      <x:c r="A183" s="0" t="s">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="C182" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D182" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E182" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F182" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G182" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="183" spans="1:9">
-      <x:c r="A183" s="0" t="s">
+      <x:c r="B183" s="0" t="s">
         <x:v>376</x:v>
       </x:c>
-      <x:c r="B183" s="0" t="s">
+      <x:c r="C183" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D183" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E183" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F183" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G183" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:7">
+      <x:c r="A184" s="0" t="s">
         <x:v>377</x:v>
       </x:c>
-      <x:c r="C183" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D183" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E183" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F183" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G183" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="184" spans="1:9">
-      <x:c r="A184" s="0" t="s">
+      <x:c r="B184" s="0" t="s">
         <x:v>378</x:v>
       </x:c>
-      <x:c r="B184" s="0" t="s">
+      <x:c r="C184" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D184" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E184" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F184" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G184" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:7">
+      <x:c r="A185" s="0" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="C184" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D184" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E184" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F184" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G184" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="185" spans="1:9">
-      <x:c r="A185" s="0" t="s">
+      <x:c r="B185" s="0" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="B185" s="0" t="s">
+      <x:c r="C185" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D185" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E185" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F185" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G185" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:7">
+      <x:c r="A186" s="0" t="s">
         <x:v>381</x:v>
       </x:c>
-      <x:c r="C185" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D185" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E185" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F185" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G185" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="186" spans="1:9">
-      <x:c r="A186" s="0" t="s">
+      <x:c r="B186" s="0" t="s">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="B186" s="0" t="s">
+      <x:c r="C186" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D186" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E186" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F186" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G186" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:7">
+      <x:c r="A187" s="0" t="s">
         <x:v>383</x:v>
       </x:c>
-      <x:c r="C186" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D186" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E186" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F186" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G186" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="187" spans="1:9">
-      <x:c r="A187" s="0" t="s">
+      <x:c r="B187" s="0" t="s">
         <x:v>384</x:v>
       </x:c>
-      <x:c r="B187" s="0" t="s">
+      <x:c r="C187" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D187" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E187" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F187" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G187" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:7">
+      <x:c r="A188" s="0" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="C187" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D187" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E187" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F187" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G187" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="188" spans="1:9">
-      <x:c r="A188" s="0" t="s">
+      <x:c r="B188" s="0" t="s">
         <x:v>386</x:v>
       </x:c>
-      <x:c r="B188" s="0" t="s">
+      <x:c r="C188" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D188" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E188" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F188" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G188" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:7">
+      <x:c r="A189" s="0" t="s">
         <x:v>387</x:v>
       </x:c>
-      <x:c r="C188" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D188" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E188" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F188" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G188" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="189" spans="1:9">
-      <x:c r="A189" s="0" t="s">
+      <x:c r="B189" s="0" t="s">
         <x:v>388</x:v>
       </x:c>
-      <x:c r="B189" s="0" t="s">
+      <x:c r="C189" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D189" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E189" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F189" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G189" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:7">
+      <x:c r="A190" s="0" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="C189" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D189" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E189" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F189" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G189" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="190" spans="1:9">
-      <x:c r="A190" s="0" t="s">
+      <x:c r="B190" s="0" t="s">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="B190" s="0" t="s">
+      <x:c r="C190" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D190" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E190" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F190" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G190" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:7">
+      <x:c r="A191" s="0" t="s">
         <x:v>391</x:v>
       </x:c>
-      <x:c r="C190" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D190" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E190" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F190" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G190" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="191" spans="1:9">
-      <x:c r="A191" s="0" t="s">
+      <x:c r="B191" s="0" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="B191" s="0" t="s">
+      <x:c r="C191" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D191" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E191" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F191" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G191" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:7">
+      <x:c r="A192" s="0" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="C191" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D191" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E191" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F191" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G191" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="192" spans="1:9">
-      <x:c r="A192" s="0" t="s">
+      <x:c r="B192" s="0" t="s">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="B192" s="0" t="s">
+      <x:c r="C192" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D192" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E192" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F192" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G192" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:7">
+      <x:c r="A193" s="0" t="s">
         <x:v>395</x:v>
       </x:c>
-      <x:c r="C192" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D192" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E192" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F192" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G192" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="193" spans="1:9">
-      <x:c r="A193" s="0" t="s">
+      <x:c r="B193" s="0" t="s">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="B193" s="0" t="s">
+      <x:c r="C193" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D193" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E193" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F193" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G193" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:7">
+      <x:c r="A194" s="0" t="s">
         <x:v>397</x:v>
       </x:c>
-      <x:c r="C193" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D193" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E193" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F193" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G193" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="194" spans="1:9">
-      <x:c r="A194" s="0" t="s">
+      <x:c r="B194" s="0" t="s">
         <x:v>398</x:v>
       </x:c>
-      <x:c r="B194" s="0" t="s">
+      <x:c r="C194" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D194" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E194" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F194" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G194" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:7">
+      <x:c r="A195" s="0" t="s">
         <x:v>399</x:v>
       </x:c>
-      <x:c r="C194" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D194" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E194" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F194" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G194" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="195" spans="1:9">
-      <x:c r="A195" s="0" t="s">
+      <x:c r="B195" s="0" t="s">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="B195" s="0" t="s">
+      <x:c r="C195" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D195" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E195" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F195" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G195" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:7">
+      <x:c r="A196" s="0" t="s">
         <x:v>401</x:v>
       </x:c>
-      <x:c r="C195" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D195" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E195" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F195" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G195" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="196" spans="1:9">
-      <x:c r="A196" s="0" t="s">
+      <x:c r="B196" s="0" t="s">
         <x:v>402</x:v>
       </x:c>
-      <x:c r="B196" s="0" t="s">
+      <x:c r="C196" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D196" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E196" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F196" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G196" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:7">
+      <x:c r="A197" s="0" t="s">
         <x:v>403</x:v>
       </x:c>
-      <x:c r="C196" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D196" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E196" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F196" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G196" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="197" spans="1:9">
-      <x:c r="A197" s="0" t="s">
+      <x:c r="B197" s="0" t="s">
         <x:v>404</x:v>
       </x:c>
-      <x:c r="B197" s="0" t="s">
+      <x:c r="C197" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D197" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E197" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F197" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G197" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:7">
+      <x:c r="A198" s="0" t="s">
         <x:v>405</x:v>
       </x:c>
-      <x:c r="C197" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D197" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E197" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F197" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G197" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="198" spans="1:9">
-      <x:c r="A198" s="0" t="s">
+      <x:c r="B198" s="0" t="s">
         <x:v>406</x:v>
       </x:c>
-      <x:c r="B198" s="0" t="s">
+      <x:c r="C198" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D198" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E198" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F198" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G198" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:7">
+      <x:c r="A199" s="0" t="s">
         <x:v>407</x:v>
       </x:c>
-      <x:c r="C198" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D198" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E198" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F198" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G198" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="199" spans="1:9">
-      <x:c r="A199" s="0" t="s">
+      <x:c r="B199" s="0" t="s">
         <x:v>408</x:v>
       </x:c>
-      <x:c r="B199" s="0" t="s">
+      <x:c r="C199" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D199" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E199" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F199" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G199" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:7">
+      <x:c r="A200" s="0" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="C199" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D199" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E199" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F199" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G199" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="200" spans="1:9">
-      <x:c r="A200" s="0" t="s">
+      <x:c r="B200" s="0" t="s">
         <x:v>410</x:v>
       </x:c>
-      <x:c r="B200" s="0" t="s">
+      <x:c r="C200" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D200" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E200" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F200" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G200" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:7">
+      <x:c r="A201" s="0" t="s">
         <x:v>411</x:v>
       </x:c>
-      <x:c r="C200" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D200" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E200" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F200" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G200" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="201" spans="1:9">
-      <x:c r="A201" s="0" t="s">
+      <x:c r="B201" s="0" t="s">
         <x:v>412</x:v>
       </x:c>
-      <x:c r="B201" s="0" t="s">
+      <x:c r="C201" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D201" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E201" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F201" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G201" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:7">
+      <x:c r="A202" s="0" t="s">
         <x:v>413</x:v>
       </x:c>
-      <x:c r="C201" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D201" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E201" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F201" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G201" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="202" spans="1:9">
-      <x:c r="A202" s="0" t="s">
+      <x:c r="B202" s="0" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="B202" s="0" t="s">
+      <x:c r="C202" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D202" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E202" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F202" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G202" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" spans="1:7">
+      <x:c r="A203" s="0" t="s">
         <x:v>415</x:v>
       </x:c>
-      <x:c r="C202" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D202" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E202" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F202" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G202" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="203" spans="1:9">
-      <x:c r="A203" s="0" t="s">
+      <x:c r="B203" s="0" t="s">
         <x:v>416</x:v>
       </x:c>
-      <x:c r="B203" s="0" t="s">
+      <x:c r="C203" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D203" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E203" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F203" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G203" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:7">
+      <x:c r="A204" s="0" t="s">
         <x:v>417</x:v>
       </x:c>
-      <x:c r="C203" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D203" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E203" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F203" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G203" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204" spans="1:9">
-      <x:c r="A204" s="0" t="s">
+      <x:c r="B204" s="0" t="s">
         <x:v>418</x:v>
       </x:c>
-      <x:c r="B204" s="0" t="s">
+      <x:c r="C204" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D204" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E204" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F204" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G204" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" spans="1:7">
+      <x:c r="A205" s="0" t="s">
         <x:v>419</x:v>
       </x:c>
-      <x:c r="C204" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D204" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E204" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F204" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G204" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="205" spans="1:9">
-      <x:c r="A205" s="0" t="s">
+      <x:c r="B205" s="0" t="s">
         <x:v>420</x:v>
       </x:c>
-      <x:c r="B205" s="0" t="s">
+      <x:c r="C205" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D205" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E205" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F205" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G205" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" spans="1:7">
+      <x:c r="A206" s="0" t="s">
         <x:v>421</x:v>
       </x:c>
-      <x:c r="C205" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D205" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E205" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F205" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G205" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="206" spans="1:9">
-      <x:c r="A206" s="0" t="s">
+      <x:c r="B206" s="0" t="s">
         <x:v>422</x:v>
       </x:c>
-      <x:c r="B206" s="0" t="s">
+      <x:c r="C206" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D206" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E206" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F206" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G206" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" spans="1:7">
+      <x:c r="A207" s="0" t="s">
         <x:v>423</x:v>
       </x:c>
-      <x:c r="C206" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D206" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E206" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F206" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G206" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="207" spans="1:9">
-      <x:c r="A207" s="0" t="s">
+      <x:c r="B207" s="0" t="s">
         <x:v>424</x:v>
       </x:c>
-      <x:c r="B207" s="0" t="s">
+      <x:c r="C207" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D207" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E207" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F207" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G207" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" spans="1:7">
+      <x:c r="A208" s="0" t="s">
         <x:v>425</x:v>
       </x:c>
-      <x:c r="C207" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D207" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E207" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F207" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G207" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="208" spans="1:9">
-      <x:c r="A208" s="0" t="s">
+      <x:c r="B208" s="0" t="s">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="B208" s="0" t="s">
+      <x:c r="C208" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D208" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E208" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F208" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G208" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" spans="1:7">
+      <x:c r="A209" s="0" t="s">
         <x:v>427</x:v>
       </x:c>
-      <x:c r="C208" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D208" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E208" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F208" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G208" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="209" spans="1:9">
-      <x:c r="A209" s="0" t="s">
+      <x:c r="B209" s="0" t="s">
         <x:v>428</x:v>
       </x:c>
-      <x:c r="B209" s="0" t="s">
+      <x:c r="C209" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D209" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E209" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F209" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G209" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" spans="1:7">
+      <x:c r="A210" s="0" t="s">
         <x:v>429</x:v>
       </x:c>
-      <x:c r="C209" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D209" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E209" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F209" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G209" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="210" spans="1:9">
-      <x:c r="A210" s="0" t="s">
+      <x:c r="B210" s="0" t="s">
         <x:v>430</x:v>
       </x:c>
-      <x:c r="B210" s="0" t="s">
+      <x:c r="C210" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D210" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E210" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F210" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G210" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" spans="1:7">
+      <x:c r="A211" s="0" t="s">
         <x:v>431</x:v>
       </x:c>
-      <x:c r="C210" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D210" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E210" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F210" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G210" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="211" spans="1:9">
-      <x:c r="A211" s="0" t="s">
+      <x:c r="B211" s="0" t="s">
         <x:v>432</x:v>
       </x:c>
-      <x:c r="B211" s="0" t="s">
+      <x:c r="C211" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D211" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E211" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F211" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G211" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" spans="1:7">
+      <x:c r="A212" s="0" t="s">
         <x:v>433</x:v>
       </x:c>
-      <x:c r="C211" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D211" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E211" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F211" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G211" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="212" spans="1:9">
-      <x:c r="A212" s="0" t="s">
+      <x:c r="B212" s="0" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="B212" s="0" t="s">
+      <x:c r="C212" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D212" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E212" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F212" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G212" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" spans="1:7">
+      <x:c r="A213" s="0" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="C212" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D212" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E212" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F212" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G212" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="213" spans="1:9">
-      <x:c r="A213" s="0" t="s">
+      <x:c r="B213" s="0" t="s">
         <x:v>436</x:v>
       </x:c>
-      <x:c r="B213" s="0" t="s">
+      <x:c r="C213" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D213" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E213" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F213" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G213" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" spans="1:7">
+      <x:c r="A214" s="0" t="s">
         <x:v>437</x:v>
       </x:c>
-      <x:c r="C213" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D213" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E213" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F213" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G213" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="214" spans="1:9">
-      <x:c r="A214" s="0" t="s">
+      <x:c r="B214" s="0" t="s">
         <x:v>438</x:v>
       </x:c>
-      <x:c r="B214" s="0" t="s">
+      <x:c r="C214" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D214" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E214" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F214" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G214" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" spans="1:7">
+      <x:c r="A215" s="0" t="s">
         <x:v>439</x:v>
       </x:c>
-      <x:c r="C214" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D214" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E214" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F214" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G214" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="215" spans="1:9">
-      <x:c r="A215" s="0" t="s">
+      <x:c r="B215" s="0" t="s">
         <x:v>440</x:v>
       </x:c>
-      <x:c r="B215" s="0" t="s">
+      <x:c r="C215" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D215" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E215" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F215" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G215" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" spans="1:7">
+      <x:c r="A216" s="0" t="s">
         <x:v>441</x:v>
       </x:c>
-      <x:c r="C215" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D215" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E215" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F215" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G215" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="216" spans="1:9">
-      <x:c r="A216" s="0" t="s">
+      <x:c r="B216" s="0" t="s">
         <x:v>442</x:v>
       </x:c>
-      <x:c r="B216" s="0" t="s">
+      <x:c r="C216" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D216" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E216" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F216" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G216" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" spans="1:7">
+      <x:c r="A217" s="0" t="s">
         <x:v>443</x:v>
       </x:c>
-      <x:c r="C216" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D216" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E216" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F216" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G216" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="217" spans="1:9">
-      <x:c r="A217" s="0" t="s">
+      <x:c r="B217" s="0" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="B217" s="0" t="s">
+      <x:c r="C217" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D217" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E217" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F217" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G217" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" spans="1:7">
+      <x:c r="A218" s="0" t="s">
         <x:v>445</x:v>
       </x:c>
-      <x:c r="C217" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D217" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E217" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F217" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G217" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="218" spans="1:9">
-      <x:c r="A218" s="0" t="s">
+      <x:c r="B218" s="0" t="s">
         <x:v>446</x:v>
       </x:c>
-      <x:c r="B218" s="0" t="s">
+      <x:c r="C218" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D218" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E218" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F218" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G218" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" spans="1:7">
+      <x:c r="A219" s="0" t="s">
         <x:v>447</x:v>
       </x:c>
-      <x:c r="C218" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D218" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E218" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F218" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G218" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="219" spans="1:9">
-      <x:c r="A219" s="0" t="s">
+      <x:c r="B219" s="0" t="s">
         <x:v>448</x:v>
       </x:c>
-      <x:c r="B219" s="0" t="s">
+      <x:c r="C219" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D219" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E219" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F219" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G219" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" spans="1:7">
+      <x:c r="A220" s="0" t="s">
         <x:v>449</x:v>
       </x:c>
-      <x:c r="C219" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D219" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E219" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F219" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G219" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="220" spans="1:9">
-      <x:c r="A220" s="0" t="s">
+      <x:c r="B220" s="0" t="s">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="B220" s="0" t="s">
+      <x:c r="C220" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D220" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E220" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F220" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G220" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" spans="1:7">
+      <x:c r="A221" s="0" t="s">
         <x:v>451</x:v>
       </x:c>
-      <x:c r="C220" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D220" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E220" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F220" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G220" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="221" spans="1:9">
-      <x:c r="A221" s="0" t="s">
+      <x:c r="B221" s="0" t="s">
         <x:v>452</x:v>
       </x:c>
-      <x:c r="B221" s="0" t="s">
+      <x:c r="C221" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D221" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E221" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F221" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G221" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" spans="1:7">
+      <x:c r="A222" s="0" t="s">
         <x:v>453</x:v>
       </x:c>
-      <x:c r="C221" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D221" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E221" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F221" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G221" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="222" spans="1:9">
-      <x:c r="A222" s="0" t="s">
+      <x:c r="B222" s="0" t="s">
         <x:v>454</x:v>
       </x:c>
-      <x:c r="B222" s="0" t="s">
+      <x:c r="C222" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D222" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E222" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F222" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G222" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" spans="1:7">
+      <x:c r="A223" s="0" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="C222" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D222" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E222" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F222" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G222" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="223" spans="1:9">
-      <x:c r="A223" s="0" t="s">
+      <x:c r="B223" s="0" t="s">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="B223" s="0" t="s">
+      <x:c r="C223" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D223" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E223" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F223" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G223" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" spans="1:7">
+      <x:c r="A224" s="0" t="s">
         <x:v>457</x:v>
       </x:c>
-      <x:c r="C223" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D223" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E223" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F223" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G223" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="224" spans="1:9">
-      <x:c r="A224" s="0" t="s">
+      <x:c r="B224" s="0" t="s">
         <x:v>458</x:v>
       </x:c>
-      <x:c r="B224" s="0" t="s">
+      <x:c r="C224" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D224" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E224" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F224" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G224" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" spans="1:7">
+      <x:c r="A225" s="0" t="s">
         <x:v>459</x:v>
       </x:c>
-      <x:c r="C224" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D224" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E224" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F224" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G224" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="225" spans="1:9">
-      <x:c r="A225" s="0" t="s">
+      <x:c r="B225" s="0" t="s">
         <x:v>460</x:v>
       </x:c>
-      <x:c r="B225" s="0" t="s">
+      <x:c r="C225" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D225" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E225" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F225" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G225" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" spans="1:7">
+      <x:c r="A226" s="0" t="s">
         <x:v>461</x:v>
       </x:c>
-      <x:c r="C225" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D225" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E225" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F225" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G225" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="226" spans="1:9">
-      <x:c r="A226" s="0" t="s">
+      <x:c r="B226" s="0" t="s">
         <x:v>462</x:v>
       </x:c>
-      <x:c r="B226" s="0" t="s">
+      <x:c r="C226" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D226" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E226" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F226" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G226" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" spans="1:7">
+      <x:c r="A227" s="0" t="s">
         <x:v>463</x:v>
       </x:c>
-      <x:c r="C226" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D226" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E226" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F226" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G226" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="227" spans="1:9">
-      <x:c r="A227" s="0" t="s">
+      <x:c r="B227" s="0" t="s">
         <x:v>464</x:v>
       </x:c>
-      <x:c r="B227" s="0" t="s">
-        <x:v>465</x:v>
-      </x:c>
       <x:c r="C227" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
         <x:v>15</x:v>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -46,24 +46,27 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
+    <x:t>1.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09-12-2025 16:37:12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09-12-2025 16:39:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>anlpvhe187047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Not Run</x:t>
+  </x:si>
+  <x:si>
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>09-12-2025 15:59:20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09-12-2025 16:01:02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>anlpvhe187047</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
     <x:t/>
   </x:si>
   <x:si>
@@ -89,6 +92,9 @@
   </x:si>
   <x:si>
     <x:t>dungtdhe186461</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09-12-2025 16:41:18</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>
@@ -1862,21 +1868,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>7</x:v>
@@ -1885,21 +1891,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>7</x:v>
@@ -1908,21 +1914,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>7</x:v>
@@ -1931,44 +1937,44 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
-      <x:c r="A7" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="A7" s="2" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C7" s="0" t="s">
+      <x:c r="B7" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C7" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>16</x:v>
+      <x:c r="D7" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E7" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G7" s="2" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>7</x:v>
@@ -1977,21 +1983,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>7</x:v>
@@ -2000,21 +2006,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>7</x:v>
@@ -2023,21 +2029,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>7</x:v>
@@ -2046,21 +2052,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
@@ -2069,21 +2075,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
@@ -2092,21 +2098,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
@@ -2115,21 +2121,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
@@ -2138,21 +2144,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
@@ -2161,21 +2167,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
@@ -2184,21 +2190,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
@@ -2207,21 +2213,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
@@ -2230,21 +2236,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>7</x:v>
@@ -2253,21 +2259,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>7</x:v>
@@ -2276,21 +2282,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>7</x:v>
@@ -2299,21 +2305,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>7</x:v>
@@ -2322,21 +2328,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>7</x:v>
@@ -2345,21 +2351,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>7</x:v>
@@ -2368,21 +2374,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>7</x:v>
@@ -2391,21 +2397,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>13</x:v>
@@ -2414,21 +2420,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>13</x:v>
@@ -2437,21 +2443,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>13</x:v>
@@ -2460,21 +2466,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>13</x:v>
@@ -2483,21 +2489,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>13</x:v>
@@ -2506,21 +2512,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>13</x:v>
@@ -2529,21 +2535,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>13</x:v>
@@ -2552,21 +2558,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>13</x:v>
@@ -2575,21 +2581,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>13</x:v>
@@ -2598,21 +2604,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>13</x:v>
@@ -2621,21 +2627,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>13</x:v>
@@ -2644,21 +2650,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>13</x:v>
@@ -2667,21 +2673,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>13</x:v>
@@ -2690,21 +2696,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>13</x:v>
@@ -2713,21 +2719,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>13</x:v>
@@ -2736,21 +2742,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>13</x:v>
@@ -2759,21 +2765,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G42" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>13</x:v>
@@ -2782,21 +2788,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G43" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>13</x:v>
@@ -2805,21 +2811,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G44" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>13</x:v>
@@ -2828,21 +2834,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G45" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>13</x:v>
@@ -2851,21 +2857,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G46" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>13</x:v>
@@ -2874,21 +2880,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G47" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>13</x:v>
@@ -2897,21 +2903,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G48" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>13</x:v>
@@ -2920,21 +2926,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G49" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>13</x:v>
@@ -2943,21 +2949,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G50" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>13</x:v>
@@ -2966,21 +2972,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G51" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>13</x:v>
@@ -2989,21 +2995,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G52" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>13</x:v>
@@ -3012,21 +3018,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G53" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>13</x:v>
@@ -3035,21 +3041,21 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G54" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>13</x:v>
@@ -3058,3969 +3064,3969 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G55" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G56" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G57" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G58" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E59" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F59" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G59" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G60" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G61" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G62" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G63" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G64" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G65" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G66" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G67" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G68" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D69" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E69" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F69" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G69" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G70" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G71" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D72" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E72" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F72" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G72" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G73" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G74" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G75" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D76" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E76" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F76" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G76" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G77" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G78" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G79" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G80" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G81" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G82" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G83" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G84" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G85" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G86" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D87" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E87" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F87" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G87" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D88" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E88" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F88" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G88" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G89" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G90" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G91" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G92" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G93" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G94" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G95" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G96" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G97" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G98" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G99" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G100" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D101" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E101" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F101" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G101" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D102" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E102" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F102" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G102" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D103" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E103" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F103" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G103" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D104" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E104" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F104" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G104" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D105" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E105" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F105" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G105" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D106" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E106" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F106" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G106" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D107" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E107" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F107" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G107" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D108" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E108" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F108" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G108" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D109" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E109" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F109" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G109" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D110" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E110" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F110" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G110" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D111" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E111" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F111" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G111" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D112" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E112" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F112" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G112" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D113" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E113" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F113" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G113" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:7">
       <x:c r="A114" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D114" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E114" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F114" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G114" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:7">
       <x:c r="A115" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D115" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E115" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F115" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G115" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="116" spans="1:7">
       <x:c r="A116" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D116" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E116" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F116" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G116" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="117" spans="1:7">
       <x:c r="A117" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D117" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E117" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F117" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G117" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="118" spans="1:7">
       <x:c r="A118" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D118" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E118" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F118" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G118" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="119" spans="1:7">
       <x:c r="A119" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D119" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E119" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F119" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G119" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="120" spans="1:7">
       <x:c r="A120" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B120" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D120" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E120" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F120" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G120" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="121" spans="1:7">
       <x:c r="A121" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B121" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D121" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E121" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F121" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G121" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="122" spans="1:7">
       <x:c r="A122" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B122" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D122" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E122" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F122" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G122" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="123" spans="1:7">
       <x:c r="A123" s="0" t="s">
-        <x:v>255</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B123" s="0" t="s">
-        <x:v>256</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D123" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E123" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F123" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G123" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="124" spans="1:7">
       <x:c r="A124" s="0" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B124" s="0" t="s">
-        <x:v>258</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D124" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E124" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F124" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G124" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="125" spans="1:7">
       <x:c r="A125" s="0" t="s">
-        <x:v>259</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B125" s="0" t="s">
-        <x:v>260</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D125" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E125" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F125" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G125" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="126" spans="1:7">
       <x:c r="A126" s="0" t="s">
-        <x:v>261</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B126" s="0" t="s">
-        <x:v>262</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D126" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E126" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F126" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G126" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:7">
       <x:c r="A127" s="0" t="s">
-        <x:v>263</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B127" s="0" t="s">
-        <x:v>264</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D127" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E127" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F127" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G127" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="128" spans="1:7">
       <x:c r="A128" s="0" t="s">
-        <x:v>265</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B128" s="0" t="s">
-        <x:v>266</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D128" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E128" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F128" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G128" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="129" spans="1:7">
       <x:c r="A129" s="0" t="s">
-        <x:v>267</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B129" s="0" t="s">
-        <x:v>268</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D129" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E129" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F129" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G129" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="130" spans="1:7">
       <x:c r="A130" s="0" t="s">
-        <x:v>269</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B130" s="0" t="s">
-        <x:v>270</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D130" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E130" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F130" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G130" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="131" spans="1:7">
       <x:c r="A131" s="0" t="s">
-        <x:v>271</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B131" s="0" t="s">
-        <x:v>272</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D131" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E131" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F131" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G131" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="132" spans="1:7">
       <x:c r="A132" s="0" t="s">
-        <x:v>273</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B132" s="0" t="s">
-        <x:v>274</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D132" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E132" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F132" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G132" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="133" spans="1:7">
       <x:c r="A133" s="0" t="s">
-        <x:v>275</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B133" s="0" t="s">
-        <x:v>276</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D133" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E133" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F133" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G133" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="134" spans="1:7">
       <x:c r="A134" s="0" t="s">
-        <x:v>277</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B134" s="0" t="s">
-        <x:v>278</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D134" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E134" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F134" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G134" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="135" spans="1:7">
       <x:c r="A135" s="0" t="s">
-        <x:v>279</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B135" s="0" t="s">
-        <x:v>280</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D135" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E135" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F135" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G135" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="136" spans="1:7">
       <x:c r="A136" s="0" t="s">
-        <x:v>281</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B136" s="0" t="s">
-        <x:v>282</x:v>
+        <x:v>284</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D136" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E136" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F136" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G136" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="137" spans="1:7">
       <x:c r="A137" s="0" t="s">
-        <x:v>283</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B137" s="0" t="s">
-        <x:v>284</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D137" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E137" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F137" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G137" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="138" spans="1:7">
       <x:c r="A138" s="0" t="s">
-        <x:v>285</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B138" s="0" t="s">
-        <x:v>286</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D138" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E138" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F138" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G138" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="139" spans="1:7">
       <x:c r="A139" s="0" t="s">
-        <x:v>287</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B139" s="0" t="s">
-        <x:v>288</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D139" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E139" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F139" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G139" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="140" spans="1:7">
       <x:c r="A140" s="0" t="s">
-        <x:v>289</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B140" s="0" t="s">
-        <x:v>290</x:v>
+        <x:v>292</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D140" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E140" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F140" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G140" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="141" spans="1:7">
       <x:c r="A141" s="0" t="s">
-        <x:v>291</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B141" s="0" t="s">
-        <x:v>292</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D141" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E141" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F141" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G141" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="142" spans="1:7">
       <x:c r="A142" s="0" t="s">
-        <x:v>293</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B142" s="0" t="s">
-        <x:v>294</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D142" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E142" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F142" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G142" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="143" spans="1:7">
       <x:c r="A143" s="0" t="s">
-        <x:v>295</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B143" s="0" t="s">
-        <x:v>296</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D143" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E143" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F143" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G143" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="144" spans="1:7">
       <x:c r="A144" s="0" t="s">
-        <x:v>297</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B144" s="0" t="s">
-        <x:v>298</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D144" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E144" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F144" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G144" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="145" spans="1:7">
       <x:c r="A145" s="0" t="s">
-        <x:v>299</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B145" s="0" t="s">
-        <x:v>300</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D145" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E145" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F145" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G145" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="146" spans="1:7">
       <x:c r="A146" s="0" t="s">
-        <x:v>301</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B146" s="0" t="s">
-        <x:v>302</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D146" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E146" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F146" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G146" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="147" spans="1:7">
       <x:c r="A147" s="0" t="s">
-        <x:v>303</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B147" s="0" t="s">
-        <x:v>304</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D147" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E147" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F147" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G147" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="148" spans="1:7">
       <x:c r="A148" s="0" t="s">
-        <x:v>305</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B148" s="0" t="s">
-        <x:v>306</x:v>
+        <x:v>308</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D148" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E148" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F148" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G148" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:7">
       <x:c r="A149" s="0" t="s">
-        <x:v>307</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B149" s="0" t="s">
-        <x:v>308</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D149" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E149" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F149" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G149" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="150" spans="1:7">
       <x:c r="A150" s="0" t="s">
-        <x:v>309</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B150" s="0" t="s">
-        <x:v>310</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D150" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E150" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F150" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G150" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="151" spans="1:7">
       <x:c r="A151" s="0" t="s">
-        <x:v>311</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B151" s="0" t="s">
-        <x:v>312</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D151" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E151" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F151" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G151" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="152" spans="1:7">
       <x:c r="A152" s="0" t="s">
-        <x:v>313</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B152" s="0" t="s">
-        <x:v>314</x:v>
+        <x:v>316</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D152" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E152" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F152" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G152" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="153" spans="1:7">
       <x:c r="A153" s="0" t="s">
-        <x:v>315</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B153" s="0" t="s">
-        <x:v>316</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D153" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E153" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F153" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G153" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="154" spans="1:7">
       <x:c r="A154" s="0" t="s">
-        <x:v>317</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B154" s="0" t="s">
-        <x:v>318</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D154" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E154" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F154" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G154" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="155" spans="1:7">
       <x:c r="A155" s="0" t="s">
-        <x:v>319</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B155" s="0" t="s">
-        <x:v>320</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D155" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E155" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F155" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G155" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="156" spans="1:7">
       <x:c r="A156" s="0" t="s">
-        <x:v>321</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B156" s="0" t="s">
-        <x:v>322</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D156" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E156" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F156" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G156" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="157" spans="1:7">
       <x:c r="A157" s="0" t="s">
-        <x:v>323</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B157" s="0" t="s">
-        <x:v>324</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D157" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E157" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F157" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G157" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="158" spans="1:7">
       <x:c r="A158" s="0" t="s">
-        <x:v>325</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B158" s="0" t="s">
-        <x:v>326</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D158" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E158" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F158" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G158" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="159" spans="1:7">
       <x:c r="A159" s="0" t="s">
-        <x:v>327</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B159" s="0" t="s">
-        <x:v>328</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D159" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E159" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F159" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G159" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="160" spans="1:7">
       <x:c r="A160" s="0" t="s">
-        <x:v>329</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B160" s="0" t="s">
-        <x:v>330</x:v>
+        <x:v>332</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D160" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E160" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F160" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G160" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="161" spans="1:7">
       <x:c r="A161" s="0" t="s">
-        <x:v>331</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B161" s="0" t="s">
-        <x:v>332</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="C161" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D161" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E161" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F161" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G161" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="162" spans="1:7">
       <x:c r="A162" s="0" t="s">
-        <x:v>333</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B162" s="0" t="s">
-        <x:v>334</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D162" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E162" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F162" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G162" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="163" spans="1:7">
       <x:c r="A163" s="0" t="s">
-        <x:v>335</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B163" s="0" t="s">
-        <x:v>336</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D163" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E163" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F163" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G163" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="164" spans="1:7">
       <x:c r="A164" s="0" t="s">
-        <x:v>337</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B164" s="0" t="s">
-        <x:v>338</x:v>
+        <x:v>340</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D164" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E164" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F164" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G164" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="165" spans="1:7">
       <x:c r="A165" s="0" t="s">
-        <x:v>339</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B165" s="0" t="s">
-        <x:v>340</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D165" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E165" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F165" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G165" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="166" spans="1:7">
       <x:c r="A166" s="0" t="s">
-        <x:v>341</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B166" s="0" t="s">
-        <x:v>342</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="C166" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D166" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E166" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F166" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G166" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="167" spans="1:7">
       <x:c r="A167" s="0" t="s">
-        <x:v>343</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B167" s="0" t="s">
-        <x:v>344</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="C167" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D167" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E167" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F167" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G167" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="168" spans="1:7">
       <x:c r="A168" s="0" t="s">
-        <x:v>345</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B168" s="0" t="s">
-        <x:v>346</x:v>
+        <x:v>348</x:v>
       </x:c>
       <x:c r="C168" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D168" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E168" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F168" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G168" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="169" spans="1:7">
       <x:c r="A169" s="0" t="s">
-        <x:v>347</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B169" s="0" t="s">
-        <x:v>348</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="C169" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D169" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E169" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F169" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G169" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="170" spans="1:7">
       <x:c r="A170" s="0" t="s">
-        <x:v>349</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B170" s="0" t="s">
-        <x:v>350</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="C170" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D170" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E170" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F170" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G170" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="171" spans="1:7">
       <x:c r="A171" s="0" t="s">
-        <x:v>351</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B171" s="0" t="s">
-        <x:v>352</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="C171" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D171" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E171" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F171" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G171" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="172" spans="1:7">
       <x:c r="A172" s="0" t="s">
-        <x:v>353</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B172" s="0" t="s">
-        <x:v>354</x:v>
+        <x:v>356</x:v>
       </x:c>
       <x:c r="C172" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D172" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E172" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F172" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G172" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="173" spans="1:7">
       <x:c r="A173" s="0" t="s">
-        <x:v>355</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B173" s="0" t="s">
-        <x:v>356</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="C173" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D173" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E173" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F173" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G173" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="174" spans="1:7">
       <x:c r="A174" s="0" t="s">
-        <x:v>357</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B174" s="0" t="s">
-        <x:v>358</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="C174" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D174" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E174" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F174" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G174" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="175" spans="1:7">
       <x:c r="A175" s="0" t="s">
-        <x:v>359</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B175" s="0" t="s">
-        <x:v>360</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="C175" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D175" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E175" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F175" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G175" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="176" spans="1:7">
       <x:c r="A176" s="0" t="s">
-        <x:v>361</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B176" s="0" t="s">
-        <x:v>362</x:v>
+        <x:v>364</x:v>
       </x:c>
       <x:c r="C176" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D176" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E176" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F176" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G176" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="177" spans="1:7">
       <x:c r="A177" s="0" t="s">
-        <x:v>363</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B177" s="0" t="s">
-        <x:v>364</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="C177" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D177" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E177" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F177" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G177" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="178" spans="1:7">
       <x:c r="A178" s="0" t="s">
-        <x:v>365</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B178" s="0" t="s">
-        <x:v>366</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="C178" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D178" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E178" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F178" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G178" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="179" spans="1:7">
       <x:c r="A179" s="0" t="s">
-        <x:v>367</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B179" s="0" t="s">
-        <x:v>368</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="C179" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D179" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E179" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F179" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G179" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="180" spans="1:7">
       <x:c r="A180" s="0" t="s">
-        <x:v>369</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B180" s="0" t="s">
-        <x:v>370</x:v>
+        <x:v>372</x:v>
       </x:c>
       <x:c r="C180" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D180" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E180" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F180" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G180" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="181" spans="1:7">
       <x:c r="A181" s="0" t="s">
-        <x:v>371</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B181" s="0" t="s">
-        <x:v>372</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="C181" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D181" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E181" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F181" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G181" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="182" spans="1:7">
       <x:c r="A182" s="0" t="s">
-        <x:v>373</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B182" s="0" t="s">
-        <x:v>374</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="C182" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D182" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E182" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F182" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G182" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="183" spans="1:7">
       <x:c r="A183" s="0" t="s">
-        <x:v>375</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B183" s="0" t="s">
-        <x:v>376</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="C183" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D183" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E183" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F183" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G183" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="184" spans="1:7">
       <x:c r="A184" s="0" t="s">
-        <x:v>377</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B184" s="0" t="s">
-        <x:v>378</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="C184" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D184" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E184" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F184" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G184" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="185" spans="1:7">
       <x:c r="A185" s="0" t="s">
-        <x:v>379</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B185" s="0" t="s">
-        <x:v>380</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="C185" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D185" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E185" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F185" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G185" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="186" spans="1:7">
       <x:c r="A186" s="0" t="s">
-        <x:v>381</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="B186" s="0" t="s">
-        <x:v>382</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="C186" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D186" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E186" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F186" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G186" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="187" spans="1:7">
       <x:c r="A187" s="0" t="s">
-        <x:v>383</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="B187" s="0" t="s">
-        <x:v>384</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="C187" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D187" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E187" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F187" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G187" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="188" spans="1:7">
       <x:c r="A188" s="0" t="s">
-        <x:v>385</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="B188" s="0" t="s">
-        <x:v>386</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="C188" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D188" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E188" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F188" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G188" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="189" spans="1:7">
       <x:c r="A189" s="0" t="s">
-        <x:v>387</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B189" s="0" t="s">
-        <x:v>388</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="C189" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D189" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E189" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F189" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G189" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="190" spans="1:7">
       <x:c r="A190" s="0" t="s">
-        <x:v>389</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="B190" s="0" t="s">
-        <x:v>390</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="C190" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D190" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E190" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F190" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G190" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="191" spans="1:7">
       <x:c r="A191" s="0" t="s">
-        <x:v>391</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="B191" s="0" t="s">
-        <x:v>392</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="C191" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D191" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E191" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F191" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G191" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="192" spans="1:7">
       <x:c r="A192" s="0" t="s">
-        <x:v>393</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="B192" s="0" t="s">
-        <x:v>394</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="C192" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D192" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E192" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F192" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G192" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="193" spans="1:7">
       <x:c r="A193" s="0" t="s">
-        <x:v>395</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="B193" s="0" t="s">
-        <x:v>396</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="C193" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D193" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E193" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F193" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G193" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="194" spans="1:7">
       <x:c r="A194" s="0" t="s">
-        <x:v>397</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="B194" s="0" t="s">
-        <x:v>398</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="C194" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D194" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E194" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F194" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G194" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="195" spans="1:7">
       <x:c r="A195" s="0" t="s">
-        <x:v>399</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B195" s="0" t="s">
-        <x:v>400</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="C195" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D195" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E195" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F195" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G195" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="196" spans="1:7">
       <x:c r="A196" s="0" t="s">
-        <x:v>401</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B196" s="0" t="s">
-        <x:v>402</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="C196" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D196" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E196" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F196" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G196" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="197" spans="1:7">
       <x:c r="A197" s="0" t="s">
-        <x:v>403</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="B197" s="0" t="s">
-        <x:v>404</x:v>
+        <x:v>406</x:v>
       </x:c>
       <x:c r="C197" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D197" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E197" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F197" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G197" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="198" spans="1:7">
       <x:c r="A198" s="0" t="s">
-        <x:v>405</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B198" s="0" t="s">
-        <x:v>406</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="C198" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D198" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E198" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F198" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G198" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="199" spans="1:7">
       <x:c r="A199" s="0" t="s">
-        <x:v>407</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="B199" s="0" t="s">
-        <x:v>408</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="C199" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D199" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E199" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F199" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G199" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="200" spans="1:7">
       <x:c r="A200" s="0" t="s">
-        <x:v>409</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="B200" s="0" t="s">
-        <x:v>410</x:v>
+        <x:v>412</x:v>
       </x:c>
       <x:c r="C200" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D200" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E200" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F200" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G200" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="201" spans="1:7">
       <x:c r="A201" s="0" t="s">
-        <x:v>411</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="B201" s="0" t="s">
-        <x:v>412</x:v>
+        <x:v>414</x:v>
       </x:c>
       <x:c r="C201" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D201" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E201" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F201" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G201" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="202" spans="1:7">
       <x:c r="A202" s="0" t="s">
-        <x:v>413</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B202" s="0" t="s">
-        <x:v>414</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C202" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D202" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E202" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F202" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G202" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="203" spans="1:7">
       <x:c r="A203" s="0" t="s">
-        <x:v>415</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="B203" s="0" t="s">
-        <x:v>416</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="C203" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D203" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E203" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F203" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G203" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="204" spans="1:7">
       <x:c r="A204" s="0" t="s">
-        <x:v>417</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="B204" s="0" t="s">
-        <x:v>418</x:v>
+        <x:v>420</x:v>
       </x:c>
       <x:c r="C204" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D204" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E204" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F204" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G204" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="205" spans="1:7">
       <x:c r="A205" s="0" t="s">
-        <x:v>419</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="B205" s="0" t="s">
-        <x:v>420</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="C205" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D205" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E205" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F205" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G205" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="206" spans="1:7">
       <x:c r="A206" s="0" t="s">
-        <x:v>421</x:v>
+        <x:v>423</x:v>
       </x:c>
       <x:c r="B206" s="0" t="s">
-        <x:v>422</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="C206" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D206" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E206" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F206" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G206" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="207" spans="1:7">
       <x:c r="A207" s="0" t="s">
-        <x:v>423</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="B207" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="C207" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D207" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E207" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F207" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G207" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="208" spans="1:7">
       <x:c r="A208" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="B208" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="C208" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D208" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E208" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F208" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G208" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="209" spans="1:7">
       <x:c r="A209" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>429</x:v>
       </x:c>
       <x:c r="B209" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="C209" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D209" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E209" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F209" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G209" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="210" spans="1:7">
       <x:c r="A210" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>431</x:v>
       </x:c>
       <x:c r="B210" s="0" t="s">
-        <x:v>430</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="C210" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D210" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E210" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F210" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G210" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="211" spans="1:7">
       <x:c r="A211" s="0" t="s">
-        <x:v>431</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="B211" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="C211" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D211" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E211" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F211" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G211" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="212" spans="1:7">
       <x:c r="A212" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="B212" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="C212" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D212" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E212" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F212" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G212" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="213" spans="1:7">
       <x:c r="A213" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="B213" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="C213" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D213" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E213" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F213" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G213" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="214" spans="1:7">
       <x:c r="A214" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="B214" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="C214" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D214" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E214" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F214" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G214" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="215" spans="1:7">
       <x:c r="A215" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="B215" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="C215" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D215" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E215" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F215" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G215" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="216" spans="1:7">
       <x:c r="A216" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="B216" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="C216" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D216" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E216" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F216" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G216" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="217" spans="1:7">
       <x:c r="A217" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="B217" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="C217" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D217" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E217" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F217" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G217" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="218" spans="1:7">
       <x:c r="A218" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="B218" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="C218" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D218" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E218" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F218" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G218" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="219" spans="1:7">
       <x:c r="A219" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B219" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C219" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D219" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E219" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F219" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G219" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="220" spans="1:7">
       <x:c r="A220" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="B220" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="C220" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D220" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E220" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F220" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G220" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="221" spans="1:7">
       <x:c r="A221" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="B221" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="C221" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D221" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E221" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F221" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G221" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="222" spans="1:7">
       <x:c r="A222" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="B222" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="C222" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D222" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E222" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F222" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G222" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="223" spans="1:7">
       <x:c r="A223" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="B223" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="C223" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D223" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E223" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F223" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G223" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="224" spans="1:7">
       <x:c r="A224" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="B224" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="C224" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D224" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E224" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F224" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G224" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="225" spans="1:7">
       <x:c r="A225" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="B225" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="C225" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D225" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E225" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F225" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G225" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="226" spans="1:7">
       <x:c r="A226" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="B226" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="C226" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D226" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E226" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F226" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G226" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="227" spans="1:7">
       <x:c r="A227" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="B227" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="C227" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E227" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F227" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G227" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>09-12-2025 21:00:43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09-12-2025 21:02:41</x:t>
+    <x:t>09-12-2025 21:11:52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09-12-2025 21:13:34</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -91,9 +91,6 @@
     <x:t>dungtdhe186461</x:t>
   </x:si>
   <x:si>
-    <x:t>09-12-2025 21:02:55</x:t>
-  </x:si>
-  <x:si>
     <x:t>7</x:t>
   </x:si>
   <x:si>
@@ -1412,12 +1409,6 @@
   </x:si>
   <x:si>
     <x:t>vietddhe161942</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2025-12-09 21:02:55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14.66s</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1811,7 +1802,7 @@
     <x:col min="6" max="7" width="18.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:9" s="1" customFormat="1">
+    <x:row r="1" spans="1:7" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1834,7 +1825,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:9" s="2" customFormat="1">
+    <x:row r="2" spans="1:7">
       <x:c r="A2" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1851,19 +1842,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H2" s="2" t="s">
-        <x:v>466</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>467</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:9">
+    </x:row>
+    <x:row r="3" spans="1:7">
       <x:c r="A3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
@@ -1886,7 +1871,7 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:9">
+    <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
@@ -1909,7 +1894,7 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:9">
+    <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
@@ -1932,7 +1917,7 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:9">
+    <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
@@ -1955,35 +1940,35 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:9">
-      <x:c r="A7" s="2" t="s">
+    <x:row r="7" spans="1:7">
+      <x:c r="A7" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B7" s="2" t="s">
+      <x:c r="B7" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C7" s="2" t="s">
+      <x:c r="C7" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D7" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E7" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F7" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G7" s="2" t="s">
+      <x:c r="D7" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:7">
+      <x:c r="A8" s="0" t="s">
         <x:v>25</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8" spans="1:9">
-      <x:c r="A8" s="0" t="s">
+      <x:c r="B8" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>7</x:v>
@@ -2001,12 +1986,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:9">
+    <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>7</x:v>
@@ -2024,12 +2009,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:9">
+    <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>7</x:v>
@@ -2047,12 +2032,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:9">
+    <x:row r="11" spans="1:7">
       <x:c r="A11" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>7</x:v>
@@ -2070,12 +2055,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:9">
+    <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
         <x:v>34</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>7</x:v>
@@ -2093,12 +2078,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:9">
+    <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>7</x:v>
@@ -2116,12 +2101,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:9">
+    <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>7</x:v>
@@ -2139,12 +2124,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:9">
+    <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="B15" s="0" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>7</x:v>
@@ -2162,12 +2147,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:9">
+    <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>7</x:v>
@@ -2185,12 +2170,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:9">
+    <x:row r="17" spans="1:7">
       <x:c r="A17" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>45</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>7</x:v>
@@ -2208,12 +2193,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:9">
+    <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="B18" s="0" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>7</x:v>
@@ -2231,12 +2216,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:9">
+    <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="B19" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>7</x:v>
@@ -2254,12 +2239,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:9">
+    <x:row r="20" spans="1:7">
       <x:c r="A20" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="B20" s="0" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>7</x:v>
@@ -2277,12 +2262,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:9">
+    <x:row r="21" spans="1:7">
       <x:c r="A21" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="B21" s="0" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>7</x:v>
@@ -2300,12 +2285,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:9">
+    <x:row r="22" spans="1:7">
       <x:c r="A22" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="B22" s="0" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>7</x:v>
@@ -2323,12 +2308,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:9">
+    <x:row r="23" spans="1:7">
       <x:c r="A23" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="B23" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>7</x:v>
@@ -2346,12 +2331,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:9">
+    <x:row r="24" spans="1:7">
       <x:c r="A24" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>7</x:v>
@@ -2369,12 +2354,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:9">
+    <x:row r="25" spans="1:7">
       <x:c r="A25" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>7</x:v>
@@ -2392,12 +2377,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:9">
+    <x:row r="26" spans="1:7">
       <x:c r="A26" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="B26" s="0" t="s">
-        <x:v>63</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>7</x:v>
@@ -2415,12 +2400,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:9">
+    <x:row r="27" spans="1:7">
       <x:c r="A27" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="B27" s="0" t="s">
-        <x:v>65</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>13</x:v>
@@ -2438,12 +2423,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:9">
+    <x:row r="28" spans="1:7">
       <x:c r="A28" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="B28" s="0" t="s">
-        <x:v>67</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>13</x:v>
@@ -2461,12 +2446,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:9">
+    <x:row r="29" spans="1:7">
       <x:c r="A29" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="B29" s="0" t="s">
-        <x:v>69</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>13</x:v>
@@ -2484,12 +2469,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:9">
+    <x:row r="30" spans="1:7">
       <x:c r="A30" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>13</x:v>
@@ -2507,12 +2492,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" spans="1:9">
+    <x:row r="31" spans="1:7">
       <x:c r="A31" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
         <x:v>72</x:v>
-      </x:c>
-      <x:c r="B31" s="0" t="s">
-        <x:v>73</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>13</x:v>
@@ -2530,12 +2515,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:9">
+    <x:row r="32" spans="1:7">
       <x:c r="A32" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
         <x:v>74</x:v>
-      </x:c>
-      <x:c r="B32" s="0" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>13</x:v>
@@ -2553,12 +2538,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" spans="1:9">
+    <x:row r="33" spans="1:7">
       <x:c r="A33" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="B33" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>13</x:v>
@@ -2576,12 +2561,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:9">
+    <x:row r="34" spans="1:7">
       <x:c r="A34" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="B34" s="0" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>13</x:v>
@@ -2599,12 +2584,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:9">
+    <x:row r="35" spans="1:7">
       <x:c r="A35" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="B35" s="0" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>13</x:v>
@@ -2622,12 +2607,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:9">
+    <x:row r="36" spans="1:7">
       <x:c r="A36" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
         <x:v>82</x:v>
-      </x:c>
-      <x:c r="B36" s="0" t="s">
-        <x:v>83</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>13</x:v>
@@ -2645,12 +2630,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" spans="1:9">
+    <x:row r="37" spans="1:7">
       <x:c r="A37" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
         <x:v>84</x:v>
-      </x:c>
-      <x:c r="B37" s="0" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>13</x:v>
@@ -2668,12 +2653,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:9">
+    <x:row r="38" spans="1:7">
       <x:c r="A38" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="B38" s="0" t="s">
-        <x:v>87</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>13</x:v>
@@ -2691,12 +2676,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" spans="1:9">
+    <x:row r="39" spans="1:7">
       <x:c r="A39" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="B39" s="0" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>13</x:v>
@@ -2714,12 +2699,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" spans="1:9">
+    <x:row r="40" spans="1:7">
       <x:c r="A40" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="B40" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>13</x:v>
@@ -2737,12 +2722,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" spans="1:9">
+    <x:row r="41" spans="1:7">
       <x:c r="A41" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
         <x:v>92</x:v>
-      </x:c>
-      <x:c r="B41" s="0" t="s">
-        <x:v>93</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>13</x:v>
@@ -2760,12 +2745,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" spans="1:9">
+    <x:row r="42" spans="1:7">
       <x:c r="A42" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="B42" s="0" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>13</x:v>
@@ -2783,12 +2768,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" spans="1:9">
+    <x:row r="43" spans="1:7">
       <x:c r="A43" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="B43" s="0" t="s">
-        <x:v>97</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>13</x:v>
@@ -2806,12 +2791,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" spans="1:9">
+    <x:row r="44" spans="1:7">
       <x:c r="A44" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="B44" s="0" t="s">
-        <x:v>99</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>13</x:v>
@@ -2829,12 +2814,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" spans="1:9">
+    <x:row r="45" spans="1:7">
       <x:c r="A45" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
         <x:v>100</x:v>
-      </x:c>
-      <x:c r="B45" s="0" t="s">
-        <x:v>101</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>13</x:v>
@@ -2852,12 +2837,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" spans="1:9">
+    <x:row r="46" spans="1:7">
       <x:c r="A46" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="B46" s="0" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>13</x:v>
@@ -2875,12 +2860,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" spans="1:9">
+    <x:row r="47" spans="1:7">
       <x:c r="A47" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
         <x:v>104</x:v>
-      </x:c>
-      <x:c r="B47" s="0" t="s">
-        <x:v>105</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>13</x:v>
@@ -2898,12 +2883,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" spans="1:9">
+    <x:row r="48" spans="1:7">
       <x:c r="A48" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="B48" s="0" t="s">
-        <x:v>107</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>13</x:v>
@@ -2921,12 +2906,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" spans="1:9">
+    <x:row r="49" spans="1:7">
       <x:c r="A49" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="B49" s="0" t="s">
-        <x:v>109</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>13</x:v>
@@ -2944,12 +2929,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" spans="1:9">
+    <x:row r="50" spans="1:7">
       <x:c r="A50" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
         <x:v>110</x:v>
-      </x:c>
-      <x:c r="B50" s="0" t="s">
-        <x:v>111</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>13</x:v>
@@ -2967,12 +2952,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" spans="1:9">
+    <x:row r="51" spans="1:7">
       <x:c r="A51" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
         <x:v>112</x:v>
-      </x:c>
-      <x:c r="B51" s="0" t="s">
-        <x:v>113</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>13</x:v>
@@ -2990,12 +2975,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" spans="1:9">
+    <x:row r="52" spans="1:7">
       <x:c r="A52" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="B52" s="0" t="s">
-        <x:v>115</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>13</x:v>
@@ -3013,12 +2998,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" spans="1:9">
+    <x:row r="53" spans="1:7">
       <x:c r="A53" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
         <x:v>116</x:v>
-      </x:c>
-      <x:c r="B53" s="0" t="s">
-        <x:v>117</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>13</x:v>
@@ -3036,12 +3021,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" spans="1:9">
+    <x:row r="54" spans="1:7">
       <x:c r="A54" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
         <x:v>118</x:v>
-      </x:c>
-      <x:c r="B54" s="0" t="s">
-        <x:v>119</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>13</x:v>
@@ -3059,12 +3044,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" spans="1:9">
+    <x:row r="55" spans="1:7">
       <x:c r="A55" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
         <x:v>120</x:v>
-      </x:c>
-      <x:c r="B55" s="0" t="s">
-        <x:v>121</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>13</x:v>
@@ -3082,12 +3067,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" spans="1:9">
+    <x:row r="56" spans="1:7">
       <x:c r="A56" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="B56" s="0" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>17</x:v>
@@ -3105,12 +3090,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" spans="1:9">
+    <x:row r="57" spans="1:7">
       <x:c r="A57" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
         <x:v>124</x:v>
-      </x:c>
-      <x:c r="B57" s="0" t="s">
-        <x:v>125</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>17</x:v>
@@ -3128,12 +3113,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" spans="1:9">
+    <x:row r="58" spans="1:7">
       <x:c r="A58" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
         <x:v>126</x:v>
-      </x:c>
-      <x:c r="B58" s="0" t="s">
-        <x:v>127</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>17</x:v>
@@ -3151,12 +3136,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" spans="1:9">
+    <x:row r="59" spans="1:7">
       <x:c r="A59" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
         <x:v>128</x:v>
-      </x:c>
-      <x:c r="B59" s="0" t="s">
-        <x:v>129</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>17</x:v>
@@ -3174,12 +3159,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" spans="1:9">
+    <x:row r="60" spans="1:7">
       <x:c r="A60" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
         <x:v>130</x:v>
-      </x:c>
-      <x:c r="B60" s="0" t="s">
-        <x:v>131</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>17</x:v>
@@ -3197,12 +3182,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" spans="1:9">
+    <x:row r="61" spans="1:7">
       <x:c r="A61" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
         <x:v>132</x:v>
-      </x:c>
-      <x:c r="B61" s="0" t="s">
-        <x:v>133</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>17</x:v>
@@ -3220,12 +3205,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" spans="1:9">
+    <x:row r="62" spans="1:7">
       <x:c r="A62" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
         <x:v>134</x:v>
-      </x:c>
-      <x:c r="B62" s="0" t="s">
-        <x:v>135</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
         <x:v>17</x:v>
@@ -3243,12 +3228,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" spans="1:9">
+    <x:row r="63" spans="1:7">
       <x:c r="A63" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
         <x:v>136</x:v>
-      </x:c>
-      <x:c r="B63" s="0" t="s">
-        <x:v>137</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
         <x:v>17</x:v>
@@ -3266,12 +3251,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" spans="1:9">
+    <x:row r="64" spans="1:7">
       <x:c r="A64" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="B64" s="0" t="s">
-        <x:v>139</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
         <x:v>17</x:v>
@@ -3289,12 +3274,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" spans="1:9">
+    <x:row r="65" spans="1:7">
       <x:c r="A65" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
         <x:v>140</x:v>
-      </x:c>
-      <x:c r="B65" s="0" t="s">
-        <x:v>141</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>17</x:v>
@@ -3312,12 +3297,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" spans="1:9">
+    <x:row r="66" spans="1:7">
       <x:c r="A66" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
         <x:v>142</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>143</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>17</x:v>
@@ -3335,12 +3320,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" spans="1:9">
+    <x:row r="67" spans="1:7">
       <x:c r="A67" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>145</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>17</x:v>
@@ -3358,12 +3343,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" spans="1:9">
+    <x:row r="68" spans="1:7">
       <x:c r="A68" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
         <x:v>146</x:v>
-      </x:c>
-      <x:c r="B68" s="0" t="s">
-        <x:v>147</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>17</x:v>
@@ -3381,12 +3366,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" spans="1:9">
+    <x:row r="69" spans="1:7">
       <x:c r="A69" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
         <x:v>148</x:v>
-      </x:c>
-      <x:c r="B69" s="0" t="s">
-        <x:v>149</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>17</x:v>
@@ -3404,12 +3389,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" spans="1:9">
+    <x:row r="70" spans="1:7">
       <x:c r="A70" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="B70" s="0" t="s">
-        <x:v>151</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
         <x:v>17</x:v>
@@ -3427,12 +3412,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" spans="1:9">
+    <x:row r="71" spans="1:7">
       <x:c r="A71" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
         <x:v>152</x:v>
-      </x:c>
-      <x:c r="B71" s="0" t="s">
-        <x:v>153</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
         <x:v>17</x:v>
@@ -3450,12 +3435,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" spans="1:9">
+    <x:row r="72" spans="1:7">
       <x:c r="A72" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
         <x:v>154</x:v>
-      </x:c>
-      <x:c r="B72" s="0" t="s">
-        <x:v>155</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
         <x:v>17</x:v>
@@ -3473,12 +3458,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" spans="1:9">
+    <x:row r="73" spans="1:7">
       <x:c r="A73" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
         <x:v>156</x:v>
-      </x:c>
-      <x:c r="B73" s="0" t="s">
-        <x:v>157</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>17</x:v>
@@ -3496,12 +3481,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" spans="1:9">
+    <x:row r="74" spans="1:7">
       <x:c r="A74" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
         <x:v>158</x:v>
-      </x:c>
-      <x:c r="B74" s="0" t="s">
-        <x:v>159</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>17</x:v>
@@ -3519,12 +3504,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" spans="1:9">
+    <x:row r="75" spans="1:7">
       <x:c r="A75" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
         <x:v>160</x:v>
-      </x:c>
-      <x:c r="B75" s="0" t="s">
-        <x:v>161</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>17</x:v>
@@ -3542,12 +3527,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" spans="1:9">
+    <x:row r="76" spans="1:7">
       <x:c r="A76" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
         <x:v>162</x:v>
-      </x:c>
-      <x:c r="B76" s="0" t="s">
-        <x:v>163</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
         <x:v>17</x:v>
@@ -3565,12 +3550,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" spans="1:9">
+    <x:row r="77" spans="1:7">
       <x:c r="A77" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
         <x:v>164</x:v>
-      </x:c>
-      <x:c r="B77" s="0" t="s">
-        <x:v>165</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>17</x:v>
@@ -3588,12 +3573,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" spans="1:9">
+    <x:row r="78" spans="1:7">
       <x:c r="A78" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
         <x:v>166</x:v>
-      </x:c>
-      <x:c r="B78" s="0" t="s">
-        <x:v>167</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>17</x:v>
@@ -3611,12 +3596,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" spans="1:9">
+    <x:row r="79" spans="1:7">
       <x:c r="A79" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
         <x:v>168</x:v>
-      </x:c>
-      <x:c r="B79" s="0" t="s">
-        <x:v>169</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>17</x:v>
@@ -3634,12 +3619,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" spans="1:9">
+    <x:row r="80" spans="1:7">
       <x:c r="A80" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
         <x:v>170</x:v>
-      </x:c>
-      <x:c r="B80" s="0" t="s">
-        <x:v>171</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
         <x:v>17</x:v>
@@ -3657,12 +3642,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" spans="1:9">
+    <x:row r="81" spans="1:7">
       <x:c r="A81" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
         <x:v>172</x:v>
-      </x:c>
-      <x:c r="B81" s="0" t="s">
-        <x:v>173</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
         <x:v>17</x:v>
@@ -3680,12 +3665,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" spans="1:9">
+    <x:row r="82" spans="1:7">
       <x:c r="A82" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
         <x:v>174</x:v>
-      </x:c>
-      <x:c r="B82" s="0" t="s">
-        <x:v>175</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
         <x:v>17</x:v>
@@ -3703,12 +3688,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" spans="1:9">
+    <x:row r="83" spans="1:7">
       <x:c r="A83" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
         <x:v>176</x:v>
-      </x:c>
-      <x:c r="B83" s="0" t="s">
-        <x:v>177</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
         <x:v>17</x:v>
@@ -3726,12 +3711,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" spans="1:9">
+    <x:row r="84" spans="1:7">
       <x:c r="A84" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
         <x:v>178</x:v>
-      </x:c>
-      <x:c r="B84" s="0" t="s">
-        <x:v>179</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
         <x:v>17</x:v>
@@ -3749,12 +3734,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" spans="1:9">
+    <x:row r="85" spans="1:7">
       <x:c r="A85" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
         <x:v>180</x:v>
-      </x:c>
-      <x:c r="B85" s="0" t="s">
-        <x:v>181</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>19</x:v>
@@ -3772,12 +3757,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" spans="1:9">
+    <x:row r="86" spans="1:7">
       <x:c r="A86" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
         <x:v>182</x:v>
-      </x:c>
-      <x:c r="B86" s="0" t="s">
-        <x:v>183</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>19</x:v>
@@ -3795,12 +3780,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" spans="1:9">
+    <x:row r="87" spans="1:7">
       <x:c r="A87" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
         <x:v>184</x:v>
-      </x:c>
-      <x:c r="B87" s="0" t="s">
-        <x:v>185</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>19</x:v>
@@ -3818,12 +3803,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" spans="1:9">
+    <x:row r="88" spans="1:7">
       <x:c r="A88" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
         <x:v>186</x:v>
-      </x:c>
-      <x:c r="B88" s="0" t="s">
-        <x:v>187</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
         <x:v>19</x:v>
@@ -3841,12 +3826,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" spans="1:9">
+    <x:row r="89" spans="1:7">
       <x:c r="A89" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
         <x:v>188</x:v>
-      </x:c>
-      <x:c r="B89" s="0" t="s">
-        <x:v>189</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
         <x:v>19</x:v>
@@ -3864,12 +3849,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="90" spans="1:9">
+    <x:row r="90" spans="1:7">
       <x:c r="A90" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
         <x:v>190</x:v>
-      </x:c>
-      <x:c r="B90" s="0" t="s">
-        <x:v>191</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>19</x:v>
@@ -3887,12 +3872,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" spans="1:9">
+    <x:row r="91" spans="1:7">
       <x:c r="A91" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
         <x:v>192</x:v>
-      </x:c>
-      <x:c r="B91" s="0" t="s">
-        <x:v>193</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>19</x:v>
@@ -3910,12 +3895,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" spans="1:9">
+    <x:row r="92" spans="1:7">
       <x:c r="A92" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
         <x:v>194</x:v>
-      </x:c>
-      <x:c r="B92" s="0" t="s">
-        <x:v>195</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
         <x:v>19</x:v>
@@ -3933,12 +3918,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="93" spans="1:9">
+    <x:row r="93" spans="1:7">
       <x:c r="A93" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
         <x:v>196</x:v>
-      </x:c>
-      <x:c r="B93" s="0" t="s">
-        <x:v>197</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>19</x:v>
@@ -3956,12 +3941,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" spans="1:9">
+    <x:row r="94" spans="1:7">
       <x:c r="A94" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="B94" s="0" t="s">
-        <x:v>199</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>19</x:v>
@@ -3979,12 +3964,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" spans="1:9">
+    <x:row r="95" spans="1:7">
       <x:c r="A95" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
         <x:v>200</x:v>
-      </x:c>
-      <x:c r="B95" s="0" t="s">
-        <x:v>201</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>19</x:v>
@@ -4002,12 +3987,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" spans="1:9">
+    <x:row r="96" spans="1:7">
       <x:c r="A96" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
         <x:v>202</x:v>
-      </x:c>
-      <x:c r="B96" s="0" t="s">
-        <x:v>203</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>19</x:v>
@@ -4025,12 +4010,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" spans="1:9">
+    <x:row r="97" spans="1:7">
       <x:c r="A97" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
         <x:v>204</x:v>
-      </x:c>
-      <x:c r="B97" s="0" t="s">
-        <x:v>205</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>19</x:v>
@@ -4048,12 +4033,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" spans="1:9">
+    <x:row r="98" spans="1:7">
       <x:c r="A98" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
         <x:v>206</x:v>
-      </x:c>
-      <x:c r="B98" s="0" t="s">
-        <x:v>207</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>19</x:v>
@@ -4071,12 +4056,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" spans="1:9">
+    <x:row r="99" spans="1:7">
       <x:c r="A99" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
         <x:v>208</x:v>
-      </x:c>
-      <x:c r="B99" s="0" t="s">
-        <x:v>209</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>19</x:v>
@@ -4094,12 +4079,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" spans="1:9">
+    <x:row r="100" spans="1:7">
       <x:c r="A100" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
         <x:v>210</x:v>
-      </x:c>
-      <x:c r="B100" s="0" t="s">
-        <x:v>211</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>19</x:v>
@@ -4117,12 +4102,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" spans="1:9">
+    <x:row r="101" spans="1:7">
       <x:c r="A101" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
         <x:v>212</x:v>
-      </x:c>
-      <x:c r="B101" s="0" t="s">
-        <x:v>213</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>19</x:v>
@@ -4140,12 +4125,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" spans="1:9">
+    <x:row r="102" spans="1:7">
       <x:c r="A102" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
         <x:v>214</x:v>
-      </x:c>
-      <x:c r="B102" s="0" t="s">
-        <x:v>215</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>19</x:v>
@@ -4163,12 +4148,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" spans="1:9">
+    <x:row r="103" spans="1:7">
       <x:c r="A103" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
         <x:v>216</x:v>
-      </x:c>
-      <x:c r="B103" s="0" t="s">
-        <x:v>217</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>19</x:v>
@@ -4186,12 +4171,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" spans="1:9">
+    <x:row r="104" spans="1:7">
       <x:c r="A104" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
         <x:v>218</x:v>
-      </x:c>
-      <x:c r="B104" s="0" t="s">
-        <x:v>219</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
         <x:v>19</x:v>
@@ -4209,12 +4194,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" spans="1:9">
+    <x:row r="105" spans="1:7">
       <x:c r="A105" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
         <x:v>220</x:v>
-      </x:c>
-      <x:c r="B105" s="0" t="s">
-        <x:v>221</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>19</x:v>
@@ -4232,12 +4217,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" spans="1:9">
+    <x:row r="106" spans="1:7">
       <x:c r="A106" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
         <x:v>222</x:v>
-      </x:c>
-      <x:c r="B106" s="0" t="s">
-        <x:v>223</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>19</x:v>
@@ -4255,12 +4240,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" spans="1:9">
+    <x:row r="107" spans="1:7">
       <x:c r="A107" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
         <x:v>224</x:v>
-      </x:c>
-      <x:c r="B107" s="0" t="s">
-        <x:v>225</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>19</x:v>
@@ -4278,12 +4263,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" spans="1:9">
+    <x:row r="108" spans="1:7">
       <x:c r="A108" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="B108" s="0" t="s">
-        <x:v>227</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>19</x:v>
@@ -4301,12 +4286,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" spans="1:9">
+    <x:row r="109" spans="1:7">
       <x:c r="A109" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
         <x:v>228</x:v>
-      </x:c>
-      <x:c r="B109" s="0" t="s">
-        <x:v>229</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>19</x:v>
@@ -4324,12 +4309,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" spans="1:9">
+    <x:row r="110" spans="1:7">
       <x:c r="A110" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
         <x:v>230</x:v>
-      </x:c>
-      <x:c r="B110" s="0" t="s">
-        <x:v>231</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
         <x:v>19</x:v>
@@ -4347,12 +4332,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" spans="1:9">
+    <x:row r="111" spans="1:7">
       <x:c r="A111" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="B111" s="0" t="s">
-        <x:v>233</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>19</x:v>
@@ -4370,12 +4355,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" spans="1:9">
+    <x:row r="112" spans="1:7">
       <x:c r="A112" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
         <x:v>234</x:v>
-      </x:c>
-      <x:c r="B112" s="0" t="s">
-        <x:v>235</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
         <x:v>19</x:v>
@@ -4393,12 +4378,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" spans="1:9">
+    <x:row r="113" spans="1:7">
       <x:c r="A113" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
         <x:v>236</x:v>
-      </x:c>
-      <x:c r="B113" s="0" t="s">
-        <x:v>237</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>19</x:v>
@@ -4416,12 +4401,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" spans="1:9">
+    <x:row r="114" spans="1:7">
       <x:c r="A114" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
         <x:v>238</x:v>
-      </x:c>
-      <x:c r="B114" s="0" t="s">
-        <x:v>239</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>19</x:v>
@@ -4439,12 +4424,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" spans="1:9">
+    <x:row r="115" spans="1:7">
       <x:c r="A115" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
         <x:v>240</x:v>
-      </x:c>
-      <x:c r="B115" s="0" t="s">
-        <x:v>241</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
         <x:v>19</x:v>
@@ -4462,12 +4447,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" spans="1:9">
+    <x:row r="116" spans="1:7">
       <x:c r="A116" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
         <x:v>242</x:v>
-      </x:c>
-      <x:c r="B116" s="0" t="s">
-        <x:v>243</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>21</x:v>
@@ -4485,12 +4470,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" spans="1:9">
+    <x:row r="117" spans="1:7">
       <x:c r="A117" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
         <x:v>244</x:v>
-      </x:c>
-      <x:c r="B117" s="0" t="s">
-        <x:v>245</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>21</x:v>
@@ -4508,12 +4493,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" spans="1:9">
+    <x:row r="118" spans="1:7">
       <x:c r="A118" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
         <x:v>246</x:v>
-      </x:c>
-      <x:c r="B118" s="0" t="s">
-        <x:v>247</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>21</x:v>
@@ -4531,12 +4516,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" spans="1:9">
+    <x:row r="119" spans="1:7">
       <x:c r="A119" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
         <x:v>248</x:v>
-      </x:c>
-      <x:c r="B119" s="0" t="s">
-        <x:v>249</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>21</x:v>
@@ -4554,12 +4539,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" spans="1:9">
+    <x:row r="120" spans="1:7">
       <x:c r="A120" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="B120" s="0" t="s">
-        <x:v>251</x:v>
       </x:c>
       <x:c r="C120" s="0" t="s">
         <x:v>21</x:v>
@@ -4577,12 +4562,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" spans="1:9">
+    <x:row r="121" spans="1:7">
       <x:c r="A121" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
         <x:v>252</x:v>
-      </x:c>
-      <x:c r="B121" s="0" t="s">
-        <x:v>253</x:v>
       </x:c>
       <x:c r="C121" s="0" t="s">
         <x:v>21</x:v>
@@ -4600,12 +4585,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" spans="1:9">
+    <x:row r="122" spans="1:7">
       <x:c r="A122" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
         <x:v>254</x:v>
-      </x:c>
-      <x:c r="B122" s="0" t="s">
-        <x:v>255</x:v>
       </x:c>
       <x:c r="C122" s="0" t="s">
         <x:v>21</x:v>
@@ -4623,12 +4608,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" spans="1:9">
+    <x:row r="123" spans="1:7">
       <x:c r="A123" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
         <x:v>256</x:v>
-      </x:c>
-      <x:c r="B123" s="0" t="s">
-        <x:v>257</x:v>
       </x:c>
       <x:c r="C123" s="0" t="s">
         <x:v>21</x:v>
@@ -4646,12 +4631,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" spans="1:9">
+    <x:row r="124" spans="1:7">
       <x:c r="A124" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
         <x:v>258</x:v>
-      </x:c>
-      <x:c r="B124" s="0" t="s">
-        <x:v>259</x:v>
       </x:c>
       <x:c r="C124" s="0" t="s">
         <x:v>21</x:v>
@@ -4669,12 +4654,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" spans="1:9">
+    <x:row r="125" spans="1:7">
       <x:c r="A125" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
         <x:v>260</x:v>
-      </x:c>
-      <x:c r="B125" s="0" t="s">
-        <x:v>261</x:v>
       </x:c>
       <x:c r="C125" s="0" t="s">
         <x:v>21</x:v>
@@ -4692,12 +4677,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" spans="1:9">
+    <x:row r="126" spans="1:7">
       <x:c r="A126" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
         <x:v>262</x:v>
-      </x:c>
-      <x:c r="B126" s="0" t="s">
-        <x:v>263</x:v>
       </x:c>
       <x:c r="C126" s="0" t="s">
         <x:v>21</x:v>
@@ -4715,12 +4700,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" spans="1:9">
+    <x:row r="127" spans="1:7">
       <x:c r="A127" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
         <x:v>264</x:v>
-      </x:c>
-      <x:c r="B127" s="0" t="s">
-        <x:v>265</x:v>
       </x:c>
       <x:c r="C127" s="0" t="s">
         <x:v>21</x:v>
@@ -4738,12 +4723,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" spans="1:9">
+    <x:row r="128" spans="1:7">
       <x:c r="A128" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
         <x:v>266</x:v>
-      </x:c>
-      <x:c r="B128" s="0" t="s">
-        <x:v>267</x:v>
       </x:c>
       <x:c r="C128" s="0" t="s">
         <x:v>21</x:v>
@@ -4761,12 +4746,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" spans="1:9">
+    <x:row r="129" spans="1:7">
       <x:c r="A129" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
         <x:v>268</x:v>
-      </x:c>
-      <x:c r="B129" s="0" t="s">
-        <x:v>269</x:v>
       </x:c>
       <x:c r="C129" s="0" t="s">
         <x:v>21</x:v>
@@ -4784,12 +4769,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" spans="1:9">
+    <x:row r="130" spans="1:7">
       <x:c r="A130" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
         <x:v>270</x:v>
-      </x:c>
-      <x:c r="B130" s="0" t="s">
-        <x:v>271</x:v>
       </x:c>
       <x:c r="C130" s="0" t="s">
         <x:v>21</x:v>
@@ -4807,12 +4792,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" spans="1:9">
+    <x:row r="131" spans="1:7">
       <x:c r="A131" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
         <x:v>272</x:v>
-      </x:c>
-      <x:c r="B131" s="0" t="s">
-        <x:v>273</x:v>
       </x:c>
       <x:c r="C131" s="0" t="s">
         <x:v>21</x:v>
@@ -4830,12 +4815,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" spans="1:9">
+    <x:row r="132" spans="1:7">
       <x:c r="A132" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
         <x:v>274</x:v>
-      </x:c>
-      <x:c r="B132" s="0" t="s">
-        <x:v>275</x:v>
       </x:c>
       <x:c r="C132" s="0" t="s">
         <x:v>21</x:v>
@@ -4853,12 +4838,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="133" spans="1:9">
+    <x:row r="133" spans="1:7">
       <x:c r="A133" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
         <x:v>276</x:v>
-      </x:c>
-      <x:c r="B133" s="0" t="s">
-        <x:v>277</x:v>
       </x:c>
       <x:c r="C133" s="0" t="s">
         <x:v>21</x:v>
@@ -4876,12 +4861,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="134" spans="1:9">
+    <x:row r="134" spans="1:7">
       <x:c r="A134" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
         <x:v>278</x:v>
-      </x:c>
-      <x:c r="B134" s="0" t="s">
-        <x:v>279</x:v>
       </x:c>
       <x:c r="C134" s="0" t="s">
         <x:v>21</x:v>
@@ -4899,12 +4884,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="135" spans="1:9">
+    <x:row r="135" spans="1:7">
       <x:c r="A135" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
         <x:v>280</x:v>
-      </x:c>
-      <x:c r="B135" s="0" t="s">
-        <x:v>281</x:v>
       </x:c>
       <x:c r="C135" s="0" t="s">
         <x:v>21</x:v>
@@ -4922,12 +4907,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" spans="1:9">
+    <x:row r="136" spans="1:7">
       <x:c r="A136" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
         <x:v>282</x:v>
-      </x:c>
-      <x:c r="B136" s="0" t="s">
-        <x:v>283</x:v>
       </x:c>
       <x:c r="C136" s="0" t="s">
         <x:v>21</x:v>
@@ -4945,12 +4930,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="137" spans="1:9">
+    <x:row r="137" spans="1:7">
       <x:c r="A137" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
         <x:v>284</x:v>
-      </x:c>
-      <x:c r="B137" s="0" t="s">
-        <x:v>285</x:v>
       </x:c>
       <x:c r="C137" s="0" t="s">
         <x:v>21</x:v>
@@ -4968,12 +4953,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" spans="1:9">
+    <x:row r="138" spans="1:7">
       <x:c r="A138" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
         <x:v>286</x:v>
-      </x:c>
-      <x:c r="B138" s="0" t="s">
-        <x:v>287</x:v>
       </x:c>
       <x:c r="C138" s="0" t="s">
         <x:v>21</x:v>
@@ -4991,12 +4976,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" spans="1:9">
+    <x:row r="139" spans="1:7">
       <x:c r="A139" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
         <x:v>288</x:v>
-      </x:c>
-      <x:c r="B139" s="0" t="s">
-        <x:v>289</x:v>
       </x:c>
       <x:c r="C139" s="0" t="s">
         <x:v>21</x:v>
@@ -5014,12 +4999,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="140" spans="1:9">
+    <x:row r="140" spans="1:7">
       <x:c r="A140" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
         <x:v>290</x:v>
-      </x:c>
-      <x:c r="B140" s="0" t="s">
-        <x:v>291</x:v>
       </x:c>
       <x:c r="C140" s="0" t="s">
         <x:v>21</x:v>
@@ -5037,12 +5022,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" spans="1:9">
+    <x:row r="141" spans="1:7">
       <x:c r="A141" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
         <x:v>292</x:v>
-      </x:c>
-      <x:c r="B141" s="0" t="s">
-        <x:v>293</x:v>
       </x:c>
       <x:c r="C141" s="0" t="s">
         <x:v>21</x:v>
@@ -5060,12 +5045,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="142" spans="1:9">
+    <x:row r="142" spans="1:7">
       <x:c r="A142" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
         <x:v>294</x:v>
-      </x:c>
-      <x:c r="B142" s="0" t="s">
-        <x:v>295</x:v>
       </x:c>
       <x:c r="C142" s="0" t="s">
         <x:v>23</x:v>
@@ -5083,12 +5068,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="143" spans="1:9">
+    <x:row r="143" spans="1:7">
       <x:c r="A143" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
         <x:v>296</x:v>
-      </x:c>
-      <x:c r="B143" s="0" t="s">
-        <x:v>297</x:v>
       </x:c>
       <x:c r="C143" s="0" t="s">
         <x:v>23</x:v>
@@ -5106,12 +5091,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="144" spans="1:9">
+    <x:row r="144" spans="1:7">
       <x:c r="A144" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
         <x:v>298</x:v>
-      </x:c>
-      <x:c r="B144" s="0" t="s">
-        <x:v>299</x:v>
       </x:c>
       <x:c r="C144" s="0" t="s">
         <x:v>23</x:v>
@@ -5129,12 +5114,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="145" spans="1:9">
+    <x:row r="145" spans="1:7">
       <x:c r="A145" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
         <x:v>300</x:v>
-      </x:c>
-      <x:c r="B145" s="0" t="s">
-        <x:v>301</x:v>
       </x:c>
       <x:c r="C145" s="0" t="s">
         <x:v>23</x:v>
@@ -5152,12 +5137,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="146" spans="1:9">
+    <x:row r="146" spans="1:7">
       <x:c r="A146" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
         <x:v>302</x:v>
-      </x:c>
-      <x:c r="B146" s="0" t="s">
-        <x:v>303</x:v>
       </x:c>
       <x:c r="C146" s="0" t="s">
         <x:v>23</x:v>
@@ -5175,12 +5160,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="147" spans="1:9">
+    <x:row r="147" spans="1:7">
       <x:c r="A147" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
         <x:v>304</x:v>
-      </x:c>
-      <x:c r="B147" s="0" t="s">
-        <x:v>305</x:v>
       </x:c>
       <x:c r="C147" s="0" t="s">
         <x:v>23</x:v>
@@ -5198,12 +5183,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="148" spans="1:9">
+    <x:row r="148" spans="1:7">
       <x:c r="A148" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
         <x:v>306</x:v>
-      </x:c>
-      <x:c r="B148" s="0" t="s">
-        <x:v>307</x:v>
       </x:c>
       <x:c r="C148" s="0" t="s">
         <x:v>23</x:v>
@@ -5221,12 +5206,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="149" spans="1:9">
+    <x:row r="149" spans="1:7">
       <x:c r="A149" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
         <x:v>308</x:v>
-      </x:c>
-      <x:c r="B149" s="0" t="s">
-        <x:v>309</x:v>
       </x:c>
       <x:c r="C149" s="0" t="s">
         <x:v>23</x:v>
@@ -5244,12 +5229,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="150" spans="1:9">
+    <x:row r="150" spans="1:7">
       <x:c r="A150" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
         <x:v>310</x:v>
-      </x:c>
-      <x:c r="B150" s="0" t="s">
-        <x:v>311</x:v>
       </x:c>
       <x:c r="C150" s="0" t="s">
         <x:v>23</x:v>
@@ -5267,12 +5252,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="151" spans="1:9">
+    <x:row r="151" spans="1:7">
       <x:c r="A151" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
         <x:v>312</x:v>
-      </x:c>
-      <x:c r="B151" s="0" t="s">
-        <x:v>313</x:v>
       </x:c>
       <x:c r="C151" s="0" t="s">
         <x:v>23</x:v>
@@ -5290,12 +5275,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="152" spans="1:9">
+    <x:row r="152" spans="1:7">
       <x:c r="A152" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
         <x:v>314</x:v>
-      </x:c>
-      <x:c r="B152" s="0" t="s">
-        <x:v>315</x:v>
       </x:c>
       <x:c r="C152" s="0" t="s">
         <x:v>23</x:v>
@@ -5313,12 +5298,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="153" spans="1:9">
+    <x:row r="153" spans="1:7">
       <x:c r="A153" s="0" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
         <x:v>316</x:v>
-      </x:c>
-      <x:c r="B153" s="0" t="s">
-        <x:v>317</x:v>
       </x:c>
       <x:c r="C153" s="0" t="s">
         <x:v>23</x:v>
@@ -5336,12 +5321,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="154" spans="1:9">
+    <x:row r="154" spans="1:7">
       <x:c r="A154" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
         <x:v>318</x:v>
-      </x:c>
-      <x:c r="B154" s="0" t="s">
-        <x:v>319</x:v>
       </x:c>
       <x:c r="C154" s="0" t="s">
         <x:v>23</x:v>
@@ -5359,12 +5344,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="155" spans="1:9">
+    <x:row r="155" spans="1:7">
       <x:c r="A155" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
         <x:v>320</x:v>
-      </x:c>
-      <x:c r="B155" s="0" t="s">
-        <x:v>321</x:v>
       </x:c>
       <x:c r="C155" s="0" t="s">
         <x:v>23</x:v>
@@ -5382,12 +5367,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="156" spans="1:9">
+    <x:row r="156" spans="1:7">
       <x:c r="A156" s="0" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
         <x:v>322</x:v>
-      </x:c>
-      <x:c r="B156" s="0" t="s">
-        <x:v>323</x:v>
       </x:c>
       <x:c r="C156" s="0" t="s">
         <x:v>23</x:v>
@@ -5405,12 +5390,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="157" spans="1:9">
+    <x:row r="157" spans="1:7">
       <x:c r="A157" s="0" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
         <x:v>324</x:v>
-      </x:c>
-      <x:c r="B157" s="0" t="s">
-        <x:v>325</x:v>
       </x:c>
       <x:c r="C157" s="0" t="s">
         <x:v>23</x:v>
@@ -5428,12 +5413,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="158" spans="1:9">
+    <x:row r="158" spans="1:7">
       <x:c r="A158" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
         <x:v>326</x:v>
-      </x:c>
-      <x:c r="B158" s="0" t="s">
-        <x:v>327</x:v>
       </x:c>
       <x:c r="C158" s="0" t="s">
         <x:v>23</x:v>
@@ -5451,12 +5436,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="159" spans="1:9">
+    <x:row r="159" spans="1:7">
       <x:c r="A159" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
         <x:v>328</x:v>
-      </x:c>
-      <x:c r="B159" s="0" t="s">
-        <x:v>329</x:v>
       </x:c>
       <x:c r="C159" s="0" t="s">
         <x:v>23</x:v>
@@ -5474,12 +5459,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="160" spans="1:9">
+    <x:row r="160" spans="1:7">
       <x:c r="A160" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
         <x:v>330</x:v>
-      </x:c>
-      <x:c r="B160" s="0" t="s">
-        <x:v>331</x:v>
       </x:c>
       <x:c r="C160" s="0" t="s">
         <x:v>23</x:v>
@@ -5497,12 +5482,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="161" spans="1:9">
+    <x:row r="161" spans="1:7">
       <x:c r="A161" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
         <x:v>332</x:v>
-      </x:c>
-      <x:c r="B161" s="0" t="s">
-        <x:v>333</x:v>
       </x:c>
       <x:c r="C161" s="0" t="s">
         <x:v>23</x:v>
@@ -5520,12 +5505,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="162" spans="1:9">
+    <x:row r="162" spans="1:7">
       <x:c r="A162" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
         <x:v>334</x:v>
-      </x:c>
-      <x:c r="B162" s="0" t="s">
-        <x:v>335</x:v>
       </x:c>
       <x:c r="C162" s="0" t="s">
         <x:v>23</x:v>
@@ -5543,12 +5528,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="163" spans="1:9">
+    <x:row r="163" spans="1:7">
       <x:c r="A163" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
         <x:v>336</x:v>
-      </x:c>
-      <x:c r="B163" s="0" t="s">
-        <x:v>337</x:v>
       </x:c>
       <x:c r="C163" s="0" t="s">
         <x:v>23</x:v>
@@ -5566,12 +5551,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="164" spans="1:9">
+    <x:row r="164" spans="1:7">
       <x:c r="A164" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
         <x:v>338</x:v>
-      </x:c>
-      <x:c r="B164" s="0" t="s">
-        <x:v>339</x:v>
       </x:c>
       <x:c r="C164" s="0" t="s">
         <x:v>23</x:v>
@@ -5589,12 +5574,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="165" spans="1:9">
+    <x:row r="165" spans="1:7">
       <x:c r="A165" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
         <x:v>340</x:v>
-      </x:c>
-      <x:c r="B165" s="0" t="s">
-        <x:v>341</x:v>
       </x:c>
       <x:c r="C165" s="0" t="s">
         <x:v>23</x:v>
@@ -5612,12 +5597,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="166" spans="1:9">
+    <x:row r="166" spans="1:7">
       <x:c r="A166" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
         <x:v>342</x:v>
-      </x:c>
-      <x:c r="B166" s="0" t="s">
-        <x:v>343</x:v>
       </x:c>
       <x:c r="C166" s="0" t="s">
         <x:v>23</x:v>
@@ -5635,12 +5620,12 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="167" spans="1:9">
+    <x:row r="167" spans="1:7">
       <x:c r="A167" s="0" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
         <x:v>344</x:v>
-      </x:c>
-      <x:c r="B167" s="0" t="s">
-        <x:v>345</x:v>
       </x:c>
       <x:c r="C167" s="0" t="s">
         <x:v>23</x:v>
@@ -5658,1372 +5643,1372 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="168" spans="1:9">
+    <x:row r="168" spans="1:7">
       <x:c r="A168" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="B168" s="0" t="s">
+      <x:c r="C168" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E168" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F168" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G168" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:7">
+      <x:c r="A169" s="0" t="s">
         <x:v>347</x:v>
       </x:c>
-      <x:c r="C168" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D168" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E168" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F168" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G168" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="169" spans="1:9">
-      <x:c r="A169" s="0" t="s">
+      <x:c r="B169" s="0" t="s">
         <x:v>348</x:v>
       </x:c>
-      <x:c r="B169" s="0" t="s">
+      <x:c r="C169" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E169" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F169" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G169" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:7">
+      <x:c r="A170" s="0" t="s">
         <x:v>349</x:v>
       </x:c>
-      <x:c r="C169" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D169" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E169" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F169" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G169" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="170" spans="1:9">
-      <x:c r="A170" s="0" t="s">
+      <x:c r="B170" s="0" t="s">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="B170" s="0" t="s">
+      <x:c r="C170" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E170" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F170" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G170" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:7">
+      <x:c r="A171" s="0" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="C170" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D170" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E170" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F170" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G170" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="171" spans="1:9">
-      <x:c r="A171" s="0" t="s">
+      <x:c r="B171" s="0" t="s">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="B171" s="0" t="s">
+      <x:c r="C171" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E171" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F171" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G171" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:7">
+      <x:c r="A172" s="0" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="C171" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D171" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E171" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F171" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G171" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="172" spans="1:9">
-      <x:c r="A172" s="0" t="s">
+      <x:c r="B172" s="0" t="s">
         <x:v>354</x:v>
       </x:c>
-      <x:c r="B172" s="0" t="s">
+      <x:c r="C172" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E172" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F172" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G172" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:7">
+      <x:c r="A173" s="0" t="s">
         <x:v>355</x:v>
       </x:c>
-      <x:c r="C172" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D172" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E172" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F172" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G172" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="173" spans="1:9">
-      <x:c r="A173" s="0" t="s">
+      <x:c r="B173" s="0" t="s">
         <x:v>356</x:v>
       </x:c>
-      <x:c r="B173" s="0" t="s">
+      <x:c r="C173" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E173" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F173" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G173" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:7">
+      <x:c r="A174" s="0" t="s">
         <x:v>357</x:v>
       </x:c>
-      <x:c r="C173" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D173" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E173" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F173" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G173" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="174" spans="1:9">
-      <x:c r="A174" s="0" t="s">
+      <x:c r="B174" s="0" t="s">
         <x:v>358</x:v>
       </x:c>
-      <x:c r="B174" s="0" t="s">
+      <x:c r="C174" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D174" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E174" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F174" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G174" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:7">
+      <x:c r="A175" s="0" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="C174" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D174" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E174" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F174" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G174" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="175" spans="1:9">
-      <x:c r="A175" s="0" t="s">
+      <x:c r="B175" s="0" t="s">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="B175" s="0" t="s">
+      <x:c r="C175" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D175" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E175" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F175" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G175" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:7">
+      <x:c r="A176" s="0" t="s">
         <x:v>361</x:v>
       </x:c>
-      <x:c r="C175" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D175" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E175" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F175" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G175" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="176" spans="1:9">
-      <x:c r="A176" s="0" t="s">
+      <x:c r="B176" s="0" t="s">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="B176" s="0" t="s">
+      <x:c r="C176" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D176" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E176" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F176" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G176" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:7">
+      <x:c r="A177" s="0" t="s">
         <x:v>363</x:v>
       </x:c>
-      <x:c r="C176" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D176" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E176" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F176" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G176" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="177" spans="1:9">
-      <x:c r="A177" s="0" t="s">
+      <x:c r="B177" s="0" t="s">
         <x:v>364</x:v>
       </x:c>
-      <x:c r="B177" s="0" t="s">
+      <x:c r="C177" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D177" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E177" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F177" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G177" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:7">
+      <x:c r="A178" s="0" t="s">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="C177" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D177" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E177" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F177" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G177" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="178" spans="1:9">
-      <x:c r="A178" s="0" t="s">
+      <x:c r="B178" s="0" t="s">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="B178" s="0" t="s">
+      <x:c r="C178" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D178" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E178" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F178" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G178" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:7">
+      <x:c r="A179" s="0" t="s">
         <x:v>367</x:v>
       </x:c>
-      <x:c r="C178" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D178" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E178" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F178" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G178" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="179" spans="1:9">
-      <x:c r="A179" s="0" t="s">
+      <x:c r="B179" s="0" t="s">
         <x:v>368</x:v>
       </x:c>
-      <x:c r="B179" s="0" t="s">
+      <x:c r="C179" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D179" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E179" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F179" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G179" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:7">
+      <x:c r="A180" s="0" t="s">
         <x:v>369</x:v>
       </x:c>
-      <x:c r="C179" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D179" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E179" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F179" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G179" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="180" spans="1:9">
-      <x:c r="A180" s="0" t="s">
+      <x:c r="B180" s="0" t="s">
         <x:v>370</x:v>
       </x:c>
-      <x:c r="B180" s="0" t="s">
+      <x:c r="C180" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D180" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E180" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F180" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G180" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:7">
+      <x:c r="A181" s="0" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="C180" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D180" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E180" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F180" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G180" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="181" spans="1:9">
-      <x:c r="A181" s="0" t="s">
+      <x:c r="B181" s="0" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="B181" s="0" t="s">
+      <x:c r="C181" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D181" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E181" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F181" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G181" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:7">
+      <x:c r="A182" s="0" t="s">
         <x:v>373</x:v>
       </x:c>
-      <x:c r="C181" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D181" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E181" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F181" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G181" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="182" spans="1:9">
-      <x:c r="A182" s="0" t="s">
+      <x:c r="B182" s="0" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="B182" s="0" t="s">
+      <x:c r="C182" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D182" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E182" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F182" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G182" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:7">
+      <x:c r="A183" s="0" t="s">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="C182" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D182" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E182" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F182" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G182" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="183" spans="1:9">
-      <x:c r="A183" s="0" t="s">
+      <x:c r="B183" s="0" t="s">
         <x:v>376</x:v>
       </x:c>
-      <x:c r="B183" s="0" t="s">
+      <x:c r="C183" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D183" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E183" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F183" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G183" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:7">
+      <x:c r="A184" s="0" t="s">
         <x:v>377</x:v>
       </x:c>
-      <x:c r="C183" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D183" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E183" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F183" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G183" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="184" spans="1:9">
-      <x:c r="A184" s="0" t="s">
+      <x:c r="B184" s="0" t="s">
         <x:v>378</x:v>
       </x:c>
-      <x:c r="B184" s="0" t="s">
+      <x:c r="C184" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D184" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E184" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F184" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G184" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:7">
+      <x:c r="A185" s="0" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="C184" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D184" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E184" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F184" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G184" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="185" spans="1:9">
-      <x:c r="A185" s="0" t="s">
+      <x:c r="B185" s="0" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="B185" s="0" t="s">
+      <x:c r="C185" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D185" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E185" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F185" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G185" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:7">
+      <x:c r="A186" s="0" t="s">
         <x:v>381</x:v>
       </x:c>
-      <x:c r="C185" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D185" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E185" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F185" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G185" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="186" spans="1:9">
-      <x:c r="A186" s="0" t="s">
+      <x:c r="B186" s="0" t="s">
         <x:v>382</x:v>
       </x:c>
-      <x:c r="B186" s="0" t="s">
+      <x:c r="C186" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D186" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E186" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F186" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G186" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:7">
+      <x:c r="A187" s="0" t="s">
         <x:v>383</x:v>
       </x:c>
-      <x:c r="C186" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D186" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E186" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F186" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G186" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="187" spans="1:9">
-      <x:c r="A187" s="0" t="s">
+      <x:c r="B187" s="0" t="s">
         <x:v>384</x:v>
       </x:c>
-      <x:c r="B187" s="0" t="s">
+      <x:c r="C187" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D187" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E187" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F187" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G187" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:7">
+      <x:c r="A188" s="0" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="C187" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D187" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E187" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F187" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G187" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="188" spans="1:9">
-      <x:c r="A188" s="0" t="s">
+      <x:c r="B188" s="0" t="s">
         <x:v>386</x:v>
       </x:c>
-      <x:c r="B188" s="0" t="s">
+      <x:c r="C188" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D188" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E188" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F188" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G188" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:7">
+      <x:c r="A189" s="0" t="s">
         <x:v>387</x:v>
       </x:c>
-      <x:c r="C188" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D188" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E188" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F188" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G188" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="189" spans="1:9">
-      <x:c r="A189" s="0" t="s">
+      <x:c r="B189" s="0" t="s">
         <x:v>388</x:v>
       </x:c>
-      <x:c r="B189" s="0" t="s">
+      <x:c r="C189" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D189" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E189" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F189" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G189" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:7">
+      <x:c r="A190" s="0" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="C189" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D189" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E189" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F189" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G189" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="190" spans="1:9">
-      <x:c r="A190" s="0" t="s">
+      <x:c r="B190" s="0" t="s">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="B190" s="0" t="s">
+      <x:c r="C190" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D190" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E190" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F190" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G190" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:7">
+      <x:c r="A191" s="0" t="s">
         <x:v>391</x:v>
       </x:c>
-      <x:c r="C190" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D190" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E190" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F190" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G190" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="191" spans="1:9">
-      <x:c r="A191" s="0" t="s">
+      <x:c r="B191" s="0" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="B191" s="0" t="s">
+      <x:c r="C191" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D191" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E191" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F191" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G191" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:7">
+      <x:c r="A192" s="0" t="s">
         <x:v>393</x:v>
       </x:c>
-      <x:c r="C191" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D191" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E191" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F191" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G191" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="192" spans="1:9">
-      <x:c r="A192" s="0" t="s">
+      <x:c r="B192" s="0" t="s">
         <x:v>394</x:v>
       </x:c>
-      <x:c r="B192" s="0" t="s">
+      <x:c r="C192" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D192" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E192" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F192" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G192" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:7">
+      <x:c r="A193" s="0" t="s">
         <x:v>395</x:v>
       </x:c>
-      <x:c r="C192" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D192" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E192" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F192" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G192" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="193" spans="1:9">
-      <x:c r="A193" s="0" t="s">
+      <x:c r="B193" s="0" t="s">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="B193" s="0" t="s">
+      <x:c r="C193" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D193" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E193" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F193" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G193" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:7">
+      <x:c r="A194" s="0" t="s">
         <x:v>397</x:v>
       </x:c>
-      <x:c r="C193" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D193" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E193" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F193" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G193" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="194" spans="1:9">
-      <x:c r="A194" s="0" t="s">
+      <x:c r="B194" s="0" t="s">
         <x:v>398</x:v>
       </x:c>
-      <x:c r="B194" s="0" t="s">
+      <x:c r="C194" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D194" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E194" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F194" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G194" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:7">
+      <x:c r="A195" s="0" t="s">
         <x:v>399</x:v>
       </x:c>
-      <x:c r="C194" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D194" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E194" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F194" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G194" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="195" spans="1:9">
-      <x:c r="A195" s="0" t="s">
+      <x:c r="B195" s="0" t="s">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="B195" s="0" t="s">
+      <x:c r="C195" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D195" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E195" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F195" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G195" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:7">
+      <x:c r="A196" s="0" t="s">
         <x:v>401</x:v>
       </x:c>
-      <x:c r="C195" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D195" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E195" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F195" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G195" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="196" spans="1:9">
-      <x:c r="A196" s="0" t="s">
+      <x:c r="B196" s="0" t="s">
         <x:v>402</x:v>
       </x:c>
-      <x:c r="B196" s="0" t="s">
+      <x:c r="C196" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D196" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E196" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F196" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G196" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:7">
+      <x:c r="A197" s="0" t="s">
         <x:v>403</x:v>
       </x:c>
-      <x:c r="C196" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D196" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E196" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F196" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G196" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="197" spans="1:9">
-      <x:c r="A197" s="0" t="s">
+      <x:c r="B197" s="0" t="s">
         <x:v>404</x:v>
       </x:c>
-      <x:c r="B197" s="0" t="s">
+      <x:c r="C197" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D197" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E197" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F197" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G197" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:7">
+      <x:c r="A198" s="0" t="s">
         <x:v>405</x:v>
       </x:c>
-      <x:c r="C197" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D197" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E197" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F197" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G197" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="198" spans="1:9">
-      <x:c r="A198" s="0" t="s">
+      <x:c r="B198" s="0" t="s">
         <x:v>406</x:v>
       </x:c>
-      <x:c r="B198" s="0" t="s">
+      <x:c r="C198" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D198" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E198" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F198" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G198" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:7">
+      <x:c r="A199" s="0" t="s">
         <x:v>407</x:v>
       </x:c>
-      <x:c r="C198" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D198" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E198" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F198" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G198" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="199" spans="1:9">
-      <x:c r="A199" s="0" t="s">
+      <x:c r="B199" s="0" t="s">
         <x:v>408</x:v>
       </x:c>
-      <x:c r="B199" s="0" t="s">
+      <x:c r="C199" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D199" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E199" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F199" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G199" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:7">
+      <x:c r="A200" s="0" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="C199" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D199" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E199" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F199" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G199" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="200" spans="1:9">
-      <x:c r="A200" s="0" t="s">
+      <x:c r="B200" s="0" t="s">
         <x:v>410</x:v>
       </x:c>
-      <x:c r="B200" s="0" t="s">
+      <x:c r="C200" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D200" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E200" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F200" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G200" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:7">
+      <x:c r="A201" s="0" t="s">
         <x:v>411</x:v>
       </x:c>
-      <x:c r="C200" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D200" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E200" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F200" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G200" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="201" spans="1:9">
-      <x:c r="A201" s="0" t="s">
+      <x:c r="B201" s="0" t="s">
         <x:v>412</x:v>
       </x:c>
-      <x:c r="B201" s="0" t="s">
+      <x:c r="C201" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D201" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E201" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F201" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G201" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202" spans="1:7">
+      <x:c r="A202" s="0" t="s">
         <x:v>413</x:v>
       </x:c>
-      <x:c r="C201" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D201" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E201" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F201" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G201" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="202" spans="1:9">
-      <x:c r="A202" s="0" t="s">
+      <x:c r="B202" s="0" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="B202" s="0" t="s">
+      <x:c r="C202" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D202" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E202" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F202" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G202" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" spans="1:7">
+      <x:c r="A203" s="0" t="s">
         <x:v>415</x:v>
       </x:c>
-      <x:c r="C202" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D202" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E202" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F202" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G202" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="203" spans="1:9">
-      <x:c r="A203" s="0" t="s">
+      <x:c r="B203" s="0" t="s">
         <x:v>416</x:v>
       </x:c>
-      <x:c r="B203" s="0" t="s">
+      <x:c r="C203" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D203" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E203" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F203" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G203" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="204" spans="1:7">
+      <x:c r="A204" s="0" t="s">
         <x:v>417</x:v>
       </x:c>
-      <x:c r="C203" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D203" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E203" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F203" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G203" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="204" spans="1:9">
-      <x:c r="A204" s="0" t="s">
+      <x:c r="B204" s="0" t="s">
         <x:v>418</x:v>
       </x:c>
-      <x:c r="B204" s="0" t="s">
+      <x:c r="C204" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D204" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E204" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F204" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G204" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="205" spans="1:7">
+      <x:c r="A205" s="0" t="s">
         <x:v>419</x:v>
       </x:c>
-      <x:c r="C204" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D204" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E204" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F204" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G204" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="205" spans="1:9">
-      <x:c r="A205" s="0" t="s">
+      <x:c r="B205" s="0" t="s">
         <x:v>420</x:v>
       </x:c>
-      <x:c r="B205" s="0" t="s">
+      <x:c r="C205" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D205" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E205" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F205" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G205" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="206" spans="1:7">
+      <x:c r="A206" s="0" t="s">
         <x:v>421</x:v>
       </x:c>
-      <x:c r="C205" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D205" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E205" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F205" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G205" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="206" spans="1:9">
-      <x:c r="A206" s="0" t="s">
+      <x:c r="B206" s="0" t="s">
         <x:v>422</x:v>
       </x:c>
-      <x:c r="B206" s="0" t="s">
+      <x:c r="C206" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D206" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E206" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F206" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G206" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="207" spans="1:7">
+      <x:c r="A207" s="0" t="s">
         <x:v>423</x:v>
       </x:c>
-      <x:c r="C206" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D206" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E206" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F206" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G206" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="207" spans="1:9">
-      <x:c r="A207" s="0" t="s">
+      <x:c r="B207" s="0" t="s">
         <x:v>424</x:v>
       </x:c>
-      <x:c r="B207" s="0" t="s">
+      <x:c r="C207" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D207" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E207" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F207" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G207" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="208" spans="1:7">
+      <x:c r="A208" s="0" t="s">
         <x:v>425</x:v>
       </x:c>
-      <x:c r="C207" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D207" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E207" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F207" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G207" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="208" spans="1:9">
-      <x:c r="A208" s="0" t="s">
+      <x:c r="B208" s="0" t="s">
         <x:v>426</x:v>
       </x:c>
-      <x:c r="B208" s="0" t="s">
+      <x:c r="C208" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D208" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E208" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F208" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G208" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="209" spans="1:7">
+      <x:c r="A209" s="0" t="s">
         <x:v>427</x:v>
       </x:c>
-      <x:c r="C208" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D208" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E208" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F208" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G208" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="209" spans="1:9">
-      <x:c r="A209" s="0" t="s">
+      <x:c r="B209" s="0" t="s">
         <x:v>428</x:v>
       </x:c>
-      <x:c r="B209" s="0" t="s">
+      <x:c r="C209" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D209" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E209" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F209" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G209" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="210" spans="1:7">
+      <x:c r="A210" s="0" t="s">
         <x:v>429</x:v>
       </x:c>
-      <x:c r="C209" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D209" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E209" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F209" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G209" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="210" spans="1:9">
-      <x:c r="A210" s="0" t="s">
+      <x:c r="B210" s="0" t="s">
         <x:v>430</x:v>
       </x:c>
-      <x:c r="B210" s="0" t="s">
+      <x:c r="C210" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D210" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E210" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F210" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G210" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="211" spans="1:7">
+      <x:c r="A211" s="0" t="s">
         <x:v>431</x:v>
       </x:c>
-      <x:c r="C210" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D210" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E210" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F210" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G210" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="211" spans="1:9">
-      <x:c r="A211" s="0" t="s">
+      <x:c r="B211" s="0" t="s">
         <x:v>432</x:v>
       </x:c>
-      <x:c r="B211" s="0" t="s">
+      <x:c r="C211" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D211" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E211" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F211" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G211" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="212" spans="1:7">
+      <x:c r="A212" s="0" t="s">
         <x:v>433</x:v>
       </x:c>
-      <x:c r="C211" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D211" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E211" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F211" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G211" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="212" spans="1:9">
-      <x:c r="A212" s="0" t="s">
+      <x:c r="B212" s="0" t="s">
         <x:v>434</x:v>
       </x:c>
-      <x:c r="B212" s="0" t="s">
+      <x:c r="C212" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D212" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E212" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F212" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G212" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="213" spans="1:7">
+      <x:c r="A213" s="0" t="s">
         <x:v>435</x:v>
       </x:c>
-      <x:c r="C212" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D212" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E212" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F212" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G212" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="213" spans="1:9">
-      <x:c r="A213" s="0" t="s">
+      <x:c r="B213" s="0" t="s">
         <x:v>436</x:v>
       </x:c>
-      <x:c r="B213" s="0" t="s">
+      <x:c r="C213" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D213" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E213" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F213" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G213" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="214" spans="1:7">
+      <x:c r="A214" s="0" t="s">
         <x:v>437</x:v>
       </x:c>
-      <x:c r="C213" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D213" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E213" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F213" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G213" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="214" spans="1:9">
-      <x:c r="A214" s="0" t="s">
+      <x:c r="B214" s="0" t="s">
         <x:v>438</x:v>
       </x:c>
-      <x:c r="B214" s="0" t="s">
+      <x:c r="C214" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D214" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E214" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F214" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G214" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="215" spans="1:7">
+      <x:c r="A215" s="0" t="s">
         <x:v>439</x:v>
       </x:c>
-      <x:c r="C214" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D214" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E214" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F214" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G214" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="215" spans="1:9">
-      <x:c r="A215" s="0" t="s">
+      <x:c r="B215" s="0" t="s">
         <x:v>440</x:v>
       </x:c>
-      <x:c r="B215" s="0" t="s">
+      <x:c r="C215" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D215" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E215" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F215" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G215" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="216" spans="1:7">
+      <x:c r="A216" s="0" t="s">
         <x:v>441</x:v>
       </x:c>
-      <x:c r="C215" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D215" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E215" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F215" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G215" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="216" spans="1:9">
-      <x:c r="A216" s="0" t="s">
+      <x:c r="B216" s="0" t="s">
         <x:v>442</x:v>
       </x:c>
-      <x:c r="B216" s="0" t="s">
+      <x:c r="C216" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D216" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E216" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F216" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G216" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="217" spans="1:7">
+      <x:c r="A217" s="0" t="s">
         <x:v>443</x:v>
       </x:c>
-      <x:c r="C216" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D216" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E216" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F216" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G216" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="217" spans="1:9">
-      <x:c r="A217" s="0" t="s">
+      <x:c r="B217" s="0" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="B217" s="0" t="s">
+      <x:c r="C217" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D217" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E217" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F217" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G217" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="218" spans="1:7">
+      <x:c r="A218" s="0" t="s">
         <x:v>445</x:v>
       </x:c>
-      <x:c r="C217" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D217" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E217" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F217" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G217" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="218" spans="1:9">
-      <x:c r="A218" s="0" t="s">
+      <x:c r="B218" s="0" t="s">
         <x:v>446</x:v>
       </x:c>
-      <x:c r="B218" s="0" t="s">
+      <x:c r="C218" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D218" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E218" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F218" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G218" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="219" spans="1:7">
+      <x:c r="A219" s="0" t="s">
         <x:v>447</x:v>
       </x:c>
-      <x:c r="C218" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D218" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E218" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F218" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G218" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="219" spans="1:9">
-      <x:c r="A219" s="0" t="s">
+      <x:c r="B219" s="0" t="s">
         <x:v>448</x:v>
       </x:c>
-      <x:c r="B219" s="0" t="s">
+      <x:c r="C219" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D219" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E219" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F219" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G219" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="220" spans="1:7">
+      <x:c r="A220" s="0" t="s">
         <x:v>449</x:v>
       </x:c>
-      <x:c r="C219" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D219" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E219" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F219" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G219" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="220" spans="1:9">
-      <x:c r="A220" s="0" t="s">
+      <x:c r="B220" s="0" t="s">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="B220" s="0" t="s">
+      <x:c r="C220" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D220" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E220" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F220" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G220" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="221" spans="1:7">
+      <x:c r="A221" s="0" t="s">
         <x:v>451</x:v>
       </x:c>
-      <x:c r="C220" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D220" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E220" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F220" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G220" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="221" spans="1:9">
-      <x:c r="A221" s="0" t="s">
+      <x:c r="B221" s="0" t="s">
         <x:v>452</x:v>
       </x:c>
-      <x:c r="B221" s="0" t="s">
+      <x:c r="C221" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D221" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E221" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F221" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G221" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="222" spans="1:7">
+      <x:c r="A222" s="0" t="s">
         <x:v>453</x:v>
       </x:c>
-      <x:c r="C221" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D221" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E221" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F221" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G221" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="222" spans="1:9">
-      <x:c r="A222" s="0" t="s">
+      <x:c r="B222" s="0" t="s">
         <x:v>454</x:v>
       </x:c>
-      <x:c r="B222" s="0" t="s">
+      <x:c r="C222" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D222" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E222" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F222" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G222" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="223" spans="1:7">
+      <x:c r="A223" s="0" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="C222" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D222" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E222" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F222" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G222" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="223" spans="1:9">
-      <x:c r="A223" s="0" t="s">
+      <x:c r="B223" s="0" t="s">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="B223" s="0" t="s">
+      <x:c r="C223" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D223" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E223" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F223" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G223" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="224" spans="1:7">
+      <x:c r="A224" s="0" t="s">
         <x:v>457</x:v>
       </x:c>
-      <x:c r="C223" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D223" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E223" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F223" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G223" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="224" spans="1:9">
-      <x:c r="A224" s="0" t="s">
+      <x:c r="B224" s="0" t="s">
         <x:v>458</x:v>
       </x:c>
-      <x:c r="B224" s="0" t="s">
+      <x:c r="C224" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D224" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E224" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F224" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G224" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="225" spans="1:7">
+      <x:c r="A225" s="0" t="s">
         <x:v>459</x:v>
       </x:c>
-      <x:c r="C224" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D224" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E224" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F224" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G224" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="225" spans="1:9">
-      <x:c r="A225" s="0" t="s">
+      <x:c r="B225" s="0" t="s">
         <x:v>460</x:v>
       </x:c>
-      <x:c r="B225" s="0" t="s">
+      <x:c r="C225" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D225" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E225" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F225" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G225" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="226" spans="1:7">
+      <x:c r="A226" s="0" t="s">
         <x:v>461</x:v>
       </x:c>
-      <x:c r="C225" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D225" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E225" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F225" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G225" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="226" spans="1:9">
-      <x:c r="A226" s="0" t="s">
+      <x:c r="B226" s="0" t="s">
         <x:v>462</x:v>
       </x:c>
-      <x:c r="B226" s="0" t="s">
+      <x:c r="C226" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D226" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E226" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F226" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G226" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="227" spans="1:7">
+      <x:c r="A227" s="0" t="s">
         <x:v>463</x:v>
       </x:c>
-      <x:c r="C226" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D226" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E226" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F226" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G226" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="227" spans="1:9">
-      <x:c r="A227" s="0" t="s">
+      <x:c r="B227" s="0" t="s">
         <x:v>464</x:v>
       </x:c>
-      <x:c r="B227" s="0" t="s">
-        <x:v>465</x:v>
-      </x:c>
       <x:c r="C227" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D227" s="0" t="s">
         <x:v>15</x:v>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -43,16 +43,16 @@
     <x:t>AnhDThe187386</x:t>
   </x:si>
   <x:si>
-    <x:t>Success</x:t>
+    <x:t>Failed</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>09-12-2025 21:11:52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09-12-2025 21:13:34</x:t>
+    <x:t>09-12-2025 21:56:28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09-12-2025 21:56:30</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -1449,7 +1449,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -43,16 +43,16 @@
     <x:t>AnhDThe187386</x:t>
   </x:si>
   <x:si>
-    <x:t>Failed</x:t>
+    <x:t>Success</x:t>
   </x:si>
   <x:si>
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>09-12-2025 21:56:28</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09-12-2025 21:56:30</x:t>
+    <x:t>09-12-2025 22:03:12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09-12-2025 22:04:54</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -1449,7 +1449,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
+        <x:fgColor rgb="FF90EE90"/>
       </x:patternFill>
     </x:fill>
   </x:fills>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>09-12-2025 22:03:12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09-12-2025 22:04:54</x:t>
+    <x:t>09-12-2025 22:23:04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09-12-2025 22:24:48</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>09-12-2025 22:23:04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09-12-2025 22:24:48</x:t>
+    <x:t>09-12-2025 22:48:09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09-12-2025 22:49:51</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>

--- a/Run_Log/StudentsSolution.xlsx
+++ b/Run_Log/StudentsSolution.xlsx
@@ -49,10 +49,10 @@
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>09-12-2025 22:48:09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09-12-2025 22:49:51</x:t>
+    <x:t>09-12-2025 22:58:12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09-12-2025 22:59:55</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
